--- a/data/INDB.MI.xlsx
+++ b/data/INDB.MI.xlsx
@@ -54790,6 +54790,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2367">
+      <c r="A2367" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2367" t="n">
+        <v>257</v>
+      </c>
+      <c r="C2367" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2367" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="E2367" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2367" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="G2367" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/INDB.MI.xlsx
+++ b/data/INDB.MI.xlsx
@@ -54801,7 +54801,7 @@
         <v>19</v>
       </c>
       <c r="D2367" t="n">
-        <v>18.7000007629395</v>
+        <v>18.6000003814697</v>
       </c>
       <c r="E2367" t="n">
         <v>19</v>
@@ -54810,6 +54810,29 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G2367" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2368" t="n">
+        <v>818</v>
+      </c>
+      <c r="C2368" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="D2368" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="E2368" t="n">
+        <v>18.7000007629395</v>
+      </c>
+      <c r="F2368" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="G2368" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/INDB.MI.xlsx
+++ b/data/INDB.MI.xlsx
@@ -54836,6 +54836,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2369">
+      <c r="A2369" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2369" t="n">
+        <v>130</v>
+      </c>
+      <c r="C2369" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="D2369" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="E2369" t="n">
+        <v>18.6499996185303</v>
+      </c>
+      <c r="F2369" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="G2369" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/INDB.MI.xlsx
+++ b/data/INDB.MI.xlsx
@@ -54859,6 +54859,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2370">
+      <c r="A2370" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2370" t="n">
+        <v>909</v>
+      </c>
+      <c r="C2370" t="n">
+        <v>18.8999996185303</v>
+      </c>
+      <c r="D2370" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="E2370" t="n">
+        <v>18.6499996185303</v>
+      </c>
+      <c r="F2370" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="G2370" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/INDB.MI.xlsx
+++ b/data/INDB.MI.xlsx
@@ -54700,19 +54700,19 @@
     </row>
     <row r="2363">
       <c r="A2363" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2363" t="n">
-        <v>226</v>
+        <v>115</v>
       </c>
       <c r="C2363" t="n">
-        <v>19.2000007629395</v>
+        <v>19.1000003814697</v>
       </c>
       <c r="D2363" t="n">
         <v>18.9500007629395</v>
       </c>
       <c r="E2363" t="n">
-        <v>19.1499996185303</v>
+        <v>19.1000003814697</v>
       </c>
       <c r="F2363" t="n">
         <v>18.9500007629395</v>
@@ -54723,19 +54723,19 @@
     </row>
     <row r="2364">
       <c r="A2364" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2364" t="n">
-        <v>15</v>
+        <v>226</v>
       </c>
       <c r="C2364" t="n">
-        <v>18.9500007629395</v>
+        <v>19.2000007629395</v>
       </c>
       <c r="D2364" t="n">
         <v>18.9500007629395</v>
       </c>
       <c r="E2364" t="n">
-        <v>18.9500007629395</v>
+        <v>19.1499996185303</v>
       </c>
       <c r="F2364" t="n">
         <v>18.9500007629395</v>
@@ -54746,19 +54746,19 @@
     </row>
     <row r="2365">
       <c r="A2365" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2365" t="n">
-        <v>326</v>
+        <v>15</v>
       </c>
       <c r="C2365" t="n">
-        <v>19.2000007629395</v>
+        <v>18.9500007629395</v>
       </c>
       <c r="D2365" t="n">
         <v>18.9500007629395</v>
       </c>
       <c r="E2365" t="n">
-        <v>19.1499996185303</v>
+        <v>18.9500007629395</v>
       </c>
       <c r="F2365" t="n">
         <v>18.9500007629395</v>
@@ -54769,22 +54769,22 @@
     </row>
     <row r="2366">
       <c r="A2366" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2366" t="n">
-        <v>606</v>
+        <v>326</v>
       </c>
       <c r="C2366" t="n">
         <v>19.2000007629395</v>
       </c>
       <c r="D2366" t="n">
-        <v>19</v>
+        <v>18.9500007629395</v>
       </c>
       <c r="E2366" t="n">
         <v>19.1499996185303</v>
       </c>
       <c r="F2366" t="n">
-        <v>19</v>
+        <v>18.9500007629395</v>
       </c>
       <c r="G2366" t="s">
         <v>7</v>
@@ -54792,22 +54792,22 @@
     </row>
     <row r="2367">
       <c r="A2367" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2367" t="n">
-        <v>257</v>
+        <v>606</v>
       </c>
       <c r="C2367" t="n">
+        <v>19.2000007629395</v>
+      </c>
+      <c r="D2367" t="n">
         <v>19</v>
       </c>
-      <c r="D2367" t="n">
-        <v>18.6000003814697</v>
-      </c>
       <c r="E2367" t="n">
+        <v>19.1499996185303</v>
+      </c>
+      <c r="F2367" t="n">
         <v>19</v>
-      </c>
-      <c r="F2367" t="n">
-        <v>18.6000003814697</v>
       </c>
       <c r="G2367" t="s">
         <v>7</v>
@@ -54815,19 +54815,19 @@
     </row>
     <row r="2368">
       <c r="A2368" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2368" t="n">
-        <v>818</v>
+        <v>257</v>
       </c>
       <c r="C2368" t="n">
-        <v>18.7000007629395</v>
+        <v>19</v>
       </c>
       <c r="D2368" t="n">
         <v>18.6000003814697</v>
       </c>
       <c r="E2368" t="n">
-        <v>18.7000007629395</v>
+        <v>19</v>
       </c>
       <c r="F2368" t="n">
         <v>18.6000003814697</v>
@@ -54838,22 +54838,22 @@
     </row>
     <row r="2369">
       <c r="A2369" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2369" t="n">
-        <v>130</v>
+        <v>818</v>
       </c>
       <c r="C2369" t="n">
-        <v>18.7999992370605</v>
+        <v>18.7000007629395</v>
       </c>
       <c r="D2369" t="n">
         <v>18.6000003814697</v>
       </c>
       <c r="E2369" t="n">
-        <v>18.6499996185303</v>
+        <v>18.7000007629395</v>
       </c>
       <c r="F2369" t="n">
-        <v>18.7999992370605</v>
+        <v>18.6000003814697</v>
       </c>
       <c r="G2369" t="s">
         <v>7</v>
@@ -54861,13 +54861,13 @@
     </row>
     <row r="2370">
       <c r="A2370" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2370" t="n">
-        <v>909</v>
+        <v>130</v>
       </c>
       <c r="C2370" t="n">
-        <v>18.8999996185303</v>
+        <v>18.7999992370605</v>
       </c>
       <c r="D2370" t="n">
         <v>18.6000003814697</v>
@@ -54876,9 +54876,32 @@
         <v>18.6499996185303</v>
       </c>
       <c r="F2370" t="n">
+        <v>18.7999992370605</v>
+      </c>
+      <c r="G2370" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2371" t="n">
+        <v>382</v>
+      </c>
+      <c r="C2371" t="n">
         <v>18.6000003814697</v>
       </c>
-      <c r="G2370" t="s">
+      <c r="D2371" t="n">
+        <v>18.3500003814697</v>
+      </c>
+      <c r="E2371" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="F2371" t="n">
+        <v>18.3999996185303</v>
+      </c>
+      <c r="G2371" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/INDB.MI.xlsx
+++ b/data/INDB.MI.xlsx
@@ -55059,7 +55059,9 @@
       <c r="E2378" t="n">
         <v>18.2999992370605</v>
       </c>
-      <c r="F2378"/>
+      <c r="F2378" t="n">
+        <v>18.5</v>
+      </c>
       <c r="G2378" t="s">
         <v>7</v>
       </c>

--- a/data/INDB.MI.xlsx
+++ b/data/INDB.MI.xlsx
@@ -55174,8 +55174,31 @@
       <c r="E2383" t="n">
         <v>17.7000007629395</v>
       </c>
-      <c r="F2383"/>
+      <c r="F2383" t="n">
+        <v>17.7000007629395</v>
+      </c>
       <c r="G2383" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2384" t="n">
+        <v>564</v>
+      </c>
+      <c r="C2384" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="D2384" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="E2384" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="F2384"/>
+      <c r="G2384" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/INDB.MI.xlsx
+++ b/data/INDB.MI.xlsx
@@ -55197,7 +55197,9 @@
       <c r="E2384" t="n">
         <v>17.75</v>
       </c>
-      <c r="F2384"/>
+      <c r="F2384" t="n">
+        <v>17.9500007629395</v>
+      </c>
       <c r="G2384" t="s">
         <v>7</v>
       </c>

--- a/data/INDB.MI.xlsx
+++ b/data/INDB.MI.xlsx
@@ -55204,6 +55204,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2385">
+      <c r="A2385" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2385" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2385" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="D2385" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="E2385" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="F2385" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="G2385" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2386">
+      <c r="A2386" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2386" t="n">
+        <v>642</v>
+      </c>
+      <c r="C2386" t="n">
+        <v>18.2000007629395</v>
+      </c>
+      <c r="D2386" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="E2386" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2386"/>
+      <c r="G2386" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/INDB.MI.xlsx
+++ b/data/INDB.MI.xlsx
@@ -55243,8 +55243,31 @@
       <c r="E2386" t="n">
         <v>18</v>
       </c>
-      <c r="F2386"/>
+      <c r="F2386" t="n">
+        <v>17.9500007629395</v>
+      </c>
       <c r="G2386" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2387" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2387" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="D2387" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="E2387" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="F2387"/>
+      <c r="G2387" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/INDB.MI.xlsx
+++ b/data/INDB.MI.xlsx
@@ -55273,6 +55273,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2388">
+      <c r="A2388" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2388" t="n">
+        <v>150</v>
+      </c>
+      <c r="C2388" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="D2388" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="E2388" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="F2388" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="G2388" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/INDB.MI.xlsx
+++ b/data/INDB.MI.xlsx
@@ -514,7 +514,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G5" t="n">
-        <v>20.8712482452393</v>
+        <v>20.8712501525879</v>
       </c>
       <c r="H5" t="n">
         <v>24133</v>
@@ -572,7 +572,7 @@
         <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>21.027006149292</v>
+        <v>21.0270023345947</v>
       </c>
       <c r="H7" t="n">
         <v>11060</v>
@@ -630,7 +630,7 @@
         <v>26.75</v>
       </c>
       <c r="G9" t="n">
-        <v>20.8323135375977</v>
+        <v>20.832311630249</v>
       </c>
       <c r="H9" t="n">
         <v>4096</v>
@@ -659,7 +659,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>20.7154922485352</v>
+        <v>20.7154960632324</v>
       </c>
       <c r="H10" t="n">
         <v>5200</v>
@@ -688,7 +688,7 @@
         <v>26.9899997711182</v>
       </c>
       <c r="G11" t="n">
-        <v>21.0192165374756</v>
+        <v>21.0192184448242</v>
       </c>
       <c r="H11" t="n">
         <v>9996</v>
@@ -717,7 +717,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>20.5986766815186</v>
+        <v>20.5986804962158</v>
       </c>
       <c r="H12" t="n">
         <v>3506</v>
@@ -746,7 +746,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G13" t="n">
-        <v>19.8822040557861</v>
+        <v>19.8822021484375</v>
       </c>
       <c r="H13" t="n">
         <v>7801</v>
@@ -775,7 +775,7 @@
         <v>26.5</v>
       </c>
       <c r="G14" t="n">
-        <v>20.6376171112061</v>
+        <v>20.6376152038574</v>
       </c>
       <c r="H14" t="n">
         <v>8135</v>
@@ -833,7 +833,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>20.5986766815186</v>
+        <v>20.5986804962158</v>
       </c>
       <c r="H16" t="n">
         <v>4055</v>
@@ -862,7 +862,7 @@
         <v>26.5200004577637</v>
       </c>
       <c r="G17" t="n">
-        <v>20.653190612793</v>
+        <v>20.6531925201416</v>
       </c>
       <c r="H17" t="n">
         <v>821</v>
@@ -891,7 +891,7 @@
         <v>25.7299995422363</v>
       </c>
       <c r="G18" t="n">
-        <v>20.0379581451416</v>
+        <v>20.037956237793</v>
       </c>
       <c r="H18" t="n">
         <v>18922</v>
@@ -920,7 +920,7 @@
         <v>26.9899997711182</v>
       </c>
       <c r="G19" t="n">
-        <v>21.0192165374756</v>
+        <v>21.0192184448242</v>
       </c>
       <c r="H19" t="n">
         <v>4714</v>
@@ -949,7 +949,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G20" t="n">
-        <v>20.3728313446045</v>
+        <v>20.3728332519531</v>
       </c>
       <c r="H20" t="n">
         <v>2994</v>
@@ -978,7 +978,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G21" t="n">
-        <v>20.3261051177979</v>
+        <v>20.3261070251465</v>
       </c>
       <c r="H21" t="n">
         <v>284</v>
@@ -1036,7 +1036,7 @@
         <v>25.5300006866455</v>
       </c>
       <c r="G23" t="n">
-        <v>19.8822040557861</v>
+        <v>19.8822021484375</v>
       </c>
       <c r="H23" t="n">
         <v>1378</v>
@@ -1065,7 +1065,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>19.9756565093994</v>
+        <v>19.9756546020508</v>
       </c>
       <c r="H24" t="n">
         <v>2327</v>
@@ -1094,7 +1094,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G25" t="n">
-        <v>20.8712482452393</v>
+        <v>20.8712501525879</v>
       </c>
       <c r="H25" t="n">
         <v>3049</v>
@@ -1123,7 +1123,7 @@
         <v>26.2099990844727</v>
       </c>
       <c r="G26" t="n">
-        <v>20.4117698669434</v>
+        <v>20.411771774292</v>
       </c>
       <c r="H26" t="n">
         <v>4049</v>
@@ -1152,7 +1152,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G27" t="n">
-        <v>20.5986766815186</v>
+        <v>20.5986804962158</v>
       </c>
       <c r="H27" t="n">
         <v>1256</v>
@@ -1181,7 +1181,7 @@
         <v>27</v>
       </c>
       <c r="G28" t="n">
-        <v>21.027006149292</v>
+        <v>21.0270023345947</v>
       </c>
       <c r="H28" t="n">
         <v>11169</v>
@@ -1239,7 +1239,7 @@
         <v>26.9899997711182</v>
       </c>
       <c r="G30" t="n">
-        <v>21.0192165374756</v>
+        <v>21.0192184448242</v>
       </c>
       <c r="H30" t="n">
         <v>1736</v>
@@ -1268,7 +1268,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G31" t="n">
-        <v>20.9880695343018</v>
+        <v>20.9880657196045</v>
       </c>
       <c r="H31" t="n">
         <v>7827</v>
@@ -1297,7 +1297,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G32" t="n">
-        <v>21.0425815582275</v>
+        <v>21.0425834655762</v>
       </c>
       <c r="H32" t="n">
         <v>2241</v>
@@ -1326,7 +1326,7 @@
         <v>27.25</v>
       </c>
       <c r="G33" t="n">
-        <v>21.221700668335</v>
+        <v>21.2216987609863</v>
       </c>
       <c r="H33" t="n">
         <v>1340</v>
@@ -1413,7 +1413,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>20.3261051177979</v>
+        <v>20.3261070251465</v>
       </c>
       <c r="H36" t="n">
         <v>20450</v>
@@ -1471,7 +1471,7 @@
         <v>27.2299995422363</v>
       </c>
       <c r="G38" t="n">
-        <v>21.2061233520508</v>
+        <v>21.206127166748</v>
       </c>
       <c r="H38" t="n">
         <v>3113</v>
@@ -1500,7 +1500,7 @@
         <v>27</v>
       </c>
       <c r="G39" t="n">
-        <v>21.027006149292</v>
+        <v>21.0270023345947</v>
       </c>
       <c r="H39" t="n">
         <v>4212</v>
@@ -1587,7 +1587,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>20.9491271972656</v>
+        <v>20.949125289917</v>
       </c>
       <c r="H42" t="n">
         <v>934</v>
@@ -1645,7 +1645,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>20.9491271972656</v>
+        <v>20.949125289917</v>
       </c>
       <c r="H44" t="n">
         <v>2515</v>
@@ -1674,7 +1674,7 @@
         <v>27</v>
       </c>
       <c r="G45" t="n">
-        <v>21.027006149292</v>
+        <v>21.0270023345947</v>
       </c>
       <c r="H45" t="n">
         <v>1075</v>
@@ -1703,7 +1703,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>20.9491271972656</v>
+        <v>20.949125289917</v>
       </c>
       <c r="H46" t="n">
         <v>729</v>
@@ -1732,7 +1732,7 @@
         <v>27</v>
       </c>
       <c r="G47" t="n">
-        <v>21.027006149292</v>
+        <v>21.0270023345947</v>
       </c>
       <c r="H47" t="n">
         <v>4748</v>
@@ -1790,7 +1790,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G49" t="n">
-        <v>21.4631195068359</v>
+        <v>21.4631214141846</v>
       </c>
       <c r="H49" t="n">
         <v>3873</v>
@@ -1819,7 +1819,7 @@
         <v>27.3299999237061</v>
       </c>
       <c r="G50" t="n">
-        <v>21.2840023040771</v>
+        <v>21.2840042114258</v>
       </c>
       <c r="H50" t="n">
         <v>6710</v>
@@ -1848,7 +1848,7 @@
         <v>27.5</v>
       </c>
       <c r="G51" t="n">
-        <v>21.4163970947266</v>
+        <v>21.4163932800293</v>
       </c>
       <c r="H51" t="n">
         <v>3852</v>
@@ -1906,7 +1906,7 @@
         <v>27.7700004577637</v>
       </c>
       <c r="G53" t="n">
-        <v>21.6266670227051</v>
+        <v>21.6266651153564</v>
       </c>
       <c r="H53" t="n">
         <v>8449</v>
@@ -1935,7 +1935,7 @@
         <v>27.7700004577637</v>
       </c>
       <c r="G54" t="n">
-        <v>21.6266670227051</v>
+        <v>21.6266651153564</v>
       </c>
       <c r="H54" t="n">
         <v>2379</v>
@@ -1964,7 +1964,7 @@
         <v>27.2900009155273</v>
       </c>
       <c r="G55" t="n">
-        <v>21.2528533935547</v>
+        <v>21.2528495788574</v>
       </c>
       <c r="H55" t="n">
         <v>950</v>
@@ -1993,7 +1993,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>21.650032043457</v>
+        <v>21.6500282287598</v>
       </c>
       <c r="H56" t="n">
         <v>1858</v>
@@ -2022,7 +2022,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G57" t="n">
-        <v>21.572151184082</v>
+        <v>21.5721492767334</v>
       </c>
       <c r="H57" t="n">
         <v>1171</v>
@@ -2051,7 +2051,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G58" t="n">
-        <v>21.572151184082</v>
+        <v>21.5721492767334</v>
       </c>
       <c r="H58" t="n">
         <v>750</v>
@@ -2109,7 +2109,7 @@
         <v>27.3099994659424</v>
       </c>
       <c r="G60" t="n">
-        <v>21.2684268951416</v>
+        <v>21.268424987793</v>
       </c>
       <c r="H60" t="n">
         <v>758</v>
@@ -2254,7 +2254,7 @@
         <v>27.6900005340576</v>
       </c>
       <c r="G65" t="n">
-        <v>21.5643634796143</v>
+        <v>21.5643615722656</v>
       </c>
       <c r="H65" t="n">
         <v>328</v>
@@ -2457,7 +2457,7 @@
         <v>27.2600002288818</v>
       </c>
       <c r="G72" t="n">
-        <v>21.2294883728027</v>
+        <v>21.2294864654541</v>
       </c>
       <c r="H72" t="n">
         <v>882</v>
@@ -2486,7 +2486,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>21.1048851013184</v>
+        <v>21.1048831939697</v>
       </c>
       <c r="H73" t="n">
         <v>1100</v>
@@ -2515,7 +2515,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G74" t="n">
-        <v>21.2995777130127</v>
+        <v>21.2995758056641</v>
       </c>
       <c r="H74" t="n">
         <v>1126</v>
@@ -2573,7 +2573,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>21.650032043457</v>
+        <v>21.6500282287598</v>
       </c>
       <c r="H76" t="n">
         <v>6037</v>
@@ -2602,7 +2602,7 @@
         <v>27.5</v>
       </c>
       <c r="G77" t="n">
-        <v>21.4163970947266</v>
+        <v>21.4163932800293</v>
       </c>
       <c r="H77" t="n">
         <v>6849</v>
@@ -2660,7 +2660,7 @@
         <v>26.5</v>
       </c>
       <c r="G79" t="n">
-        <v>20.6376171112061</v>
+        <v>20.6376152038574</v>
       </c>
       <c r="H79" t="n">
         <v>9060</v>
@@ -2689,7 +2689,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G80" t="n">
-        <v>20.7154922485352</v>
+        <v>20.7154960632324</v>
       </c>
       <c r="H80" t="n">
         <v>100</v>
@@ -2718,7 +2718,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G81" t="n">
-        <v>20.5597400665283</v>
+        <v>20.5597381591797</v>
       </c>
       <c r="H81" t="n">
         <v>535</v>
@@ -2747,7 +2747,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G82" t="n">
-        <v>20.8712482452393</v>
+        <v>20.8712501525879</v>
       </c>
       <c r="H82" t="n">
         <v>1022</v>
@@ -2805,7 +2805,7 @@
         <v>26.5300006866455</v>
       </c>
       <c r="G84" t="n">
-        <v>20.6609783172607</v>
+        <v>20.6609802246094</v>
       </c>
       <c r="H84" t="n">
         <v>227</v>
@@ -2834,7 +2834,7 @@
         <v>26.75</v>
       </c>
       <c r="G85" t="n">
-        <v>20.8323135375977</v>
+        <v>20.832311630249</v>
       </c>
       <c r="H85" t="n">
         <v>1000</v>
@@ -2863,7 +2863,7 @@
         <v>26.7700004577637</v>
       </c>
       <c r="G86" t="n">
-        <v>20.8478889465332</v>
+        <v>20.8478870391846</v>
       </c>
       <c r="H86" t="n">
         <v>83</v>
@@ -2892,7 +2892,7 @@
         <v>26.7700004577637</v>
       </c>
       <c r="G87" t="n">
-        <v>20.8478889465332</v>
+        <v>20.8478870391846</v>
       </c>
       <c r="H87" t="n">
         <v>216</v>
@@ -2921,7 +2921,7 @@
         <v>26.9300003051758</v>
       </c>
       <c r="G88" t="n">
-        <v>20.9724903106689</v>
+        <v>20.9724922180176</v>
       </c>
       <c r="H88" t="n">
         <v>947</v>
@@ -3008,7 +3008,7 @@
         <v>26.75</v>
       </c>
       <c r="G91" t="n">
-        <v>20.8323135375977</v>
+        <v>20.832311630249</v>
       </c>
       <c r="H91" t="n">
         <v>2846</v>
@@ -3066,7 +3066,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G93" t="n">
-        <v>21.5565738677979</v>
+        <v>21.5565757751465</v>
       </c>
       <c r="H93" t="n">
         <v>4723</v>
@@ -3124,7 +3124,7 @@
         <v>27.5</v>
       </c>
       <c r="G95" t="n">
-        <v>21.4163970947266</v>
+        <v>21.4163932800293</v>
       </c>
       <c r="H95" t="n">
         <v>3002</v>
@@ -3182,7 +3182,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>21.572151184082</v>
+        <v>21.5721492767334</v>
       </c>
       <c r="H97" t="n">
         <v>19396</v>
@@ -3211,7 +3211,7 @@
         <v>28.2600002288818</v>
       </c>
       <c r="G98" t="n">
-        <v>22.0082683563232</v>
+        <v>22.0082664489746</v>
       </c>
       <c r="H98" t="n">
         <v>33083</v>
@@ -3240,7 +3240,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G99" t="n">
-        <v>22.8960742950439</v>
+        <v>22.8960723876953</v>
       </c>
       <c r="H99" t="n">
         <v>129721</v>
@@ -3298,7 +3298,7 @@
         <v>29.8799991607666</v>
       </c>
       <c r="G101" t="n">
-        <v>23.2698860168457</v>
+        <v>23.2698841094971</v>
       </c>
       <c r="H101" t="n">
         <v>57558</v>
@@ -3327,7 +3327,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G102" t="n">
-        <v>23.9863624572754</v>
+        <v>23.9863605499268</v>
       </c>
       <c r="H102" t="n">
         <v>32863</v>
@@ -3356,7 +3356,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>24.648323059082</v>
+        <v>24.6483211517334</v>
       </c>
       <c r="H103" t="n">
         <v>23345</v>
@@ -3385,7 +3385,7 @@
         <v>31.4699993133545</v>
       </c>
       <c r="G104" t="n">
-        <v>24.5081443786621</v>
+        <v>24.5081424713135</v>
       </c>
       <c r="H104" t="n">
         <v>21297</v>
@@ -3414,7 +3414,7 @@
         <v>31.7700004577637</v>
       </c>
       <c r="G105" t="n">
-        <v>24.7417774200439</v>
+        <v>24.7417755126953</v>
       </c>
       <c r="H105" t="n">
         <v>22649</v>
@@ -3443,7 +3443,7 @@
         <v>33</v>
       </c>
       <c r="G106" t="n">
-        <v>25.6996746063232</v>
+        <v>25.6996784210205</v>
       </c>
       <c r="H106" t="n">
         <v>82705</v>
@@ -3472,7 +3472,7 @@
         <v>34.2900009155273</v>
       </c>
       <c r="G107" t="n">
-        <v>26.7042961120605</v>
+        <v>26.7042980194092</v>
       </c>
       <c r="H107" t="n">
         <v>48448</v>
@@ -3501,7 +3501,7 @@
         <v>35</v>
       </c>
       <c r="G108" t="n">
-        <v>27.257230758667</v>
+        <v>27.2572269439697</v>
       </c>
       <c r="H108" t="n">
         <v>41060</v>
@@ -3559,7 +3559,7 @@
         <v>34</v>
       </c>
       <c r="G110" t="n">
-        <v>26.4784507751465</v>
+        <v>26.4784526824951</v>
       </c>
       <c r="H110" t="n">
         <v>33933</v>
@@ -3617,7 +3617,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G112" t="n">
-        <v>26.9457168579102</v>
+        <v>26.9457187652588</v>
       </c>
       <c r="H112" t="n">
         <v>3860</v>
@@ -3646,7 +3646,7 @@
         <v>33.5</v>
       </c>
       <c r="G113" t="n">
-        <v>26.0890598297119</v>
+        <v>26.0890636444092</v>
       </c>
       <c r="H113" t="n">
         <v>12586</v>
@@ -3675,7 +3675,7 @@
         <v>33.0800018310547</v>
       </c>
       <c r="G114" t="n">
-        <v>25.7619781494141</v>
+        <v>25.7619762420654</v>
       </c>
       <c r="H114" t="n">
         <v>7353</v>
@@ -3733,7 +3733,7 @@
         <v>33.4900016784668</v>
       </c>
       <c r="G116" t="n">
-        <v>26.0812759399414</v>
+        <v>26.08127784729</v>
       </c>
       <c r="H116" t="n">
         <v>2749</v>
@@ -3791,7 +3791,7 @@
         <v>34.7200012207031</v>
       </c>
       <c r="G118" t="n">
-        <v>27.0391731262207</v>
+        <v>27.0391693115234</v>
       </c>
       <c r="H118" t="n">
         <v>19816</v>
@@ -3820,7 +3820,7 @@
         <v>35.2400016784668</v>
       </c>
       <c r="G119" t="n">
-        <v>27.4441375732422</v>
+        <v>27.4441394805908</v>
       </c>
       <c r="H119" t="n">
         <v>10926</v>
@@ -3849,7 +3849,7 @@
         <v>35</v>
       </c>
       <c r="G120" t="n">
-        <v>27.257230758667</v>
+        <v>27.2572269439697</v>
       </c>
       <c r="H120" t="n">
         <v>4199</v>
@@ -3878,7 +3878,7 @@
         <v>34.6699981689453</v>
       </c>
       <c r="G121" t="n">
-        <v>27.0002288818359</v>
+        <v>27.0002326965332</v>
       </c>
       <c r="H121" t="n">
         <v>5695</v>
@@ -3907,7 +3907,7 @@
         <v>34.2599983215332</v>
       </c>
       <c r="G122" t="n">
-        <v>26.6809310913086</v>
+        <v>26.6809349060059</v>
       </c>
       <c r="H122" t="n">
         <v>12734</v>
@@ -3965,7 +3965,7 @@
         <v>34.2599983215332</v>
       </c>
       <c r="G124" t="n">
-        <v>26.6809310913086</v>
+        <v>26.6809349060059</v>
       </c>
       <c r="H124" t="n">
         <v>7319</v>
@@ -3994,7 +3994,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G125" t="n">
-        <v>26.3616313934326</v>
+        <v>26.3616352081299</v>
       </c>
       <c r="H125" t="n">
         <v>6601</v>
@@ -4023,7 +4023,7 @@
         <v>32.9900016784668</v>
       </c>
       <c r="G126" t="n">
-        <v>25.6918869018555</v>
+        <v>25.6918888092041</v>
       </c>
       <c r="H126" t="n">
         <v>11429</v>
@@ -4052,7 +4052,7 @@
         <v>32.5</v>
       </c>
       <c r="G127" t="n">
-        <v>25.3102836608887</v>
+        <v>25.3102874755859</v>
       </c>
       <c r="H127" t="n">
         <v>13436</v>
@@ -4081,7 +4081,7 @@
         <v>32.810001373291</v>
       </c>
       <c r="G128" t="n">
-        <v>25.5517063140869</v>
+        <v>25.5517082214355</v>
       </c>
       <c r="H128" t="n">
         <v>3332</v>
@@ -4110,7 +4110,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G129" t="n">
-        <v>25.2791328430176</v>
+        <v>25.2791347503662</v>
       </c>
       <c r="H129" t="n">
         <v>4525</v>
@@ -4139,7 +4139,7 @@
         <v>32.1399993896484</v>
       </c>
       <c r="G130" t="n">
-        <v>25.0299243927002</v>
+        <v>25.0299224853516</v>
       </c>
       <c r="H130" t="n">
         <v>6748</v>
@@ -4168,7 +4168,7 @@
         <v>32.6599998474121</v>
       </c>
       <c r="G131" t="n">
-        <v>25.434886932373</v>
+        <v>25.4348907470703</v>
       </c>
       <c r="H131" t="n">
         <v>344</v>
@@ -4197,7 +4197,7 @@
         <v>32.6699981689453</v>
       </c>
       <c r="G132" t="n">
-        <v>25.4426765441895</v>
+        <v>25.4426727294922</v>
       </c>
       <c r="H132" t="n">
         <v>2635</v>
@@ -4255,7 +4255,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>25.037712097168</v>
+        <v>25.0377140045166</v>
       </c>
       <c r="H134" t="n">
         <v>13031</v>
@@ -4284,7 +4284,7 @@
         <v>32.1399993896484</v>
       </c>
       <c r="G135" t="n">
-        <v>25.0299243927002</v>
+        <v>25.0299224853516</v>
       </c>
       <c r="H135" t="n">
         <v>978</v>
@@ -4313,7 +4313,7 @@
         <v>31.8700008392334</v>
       </c>
       <c r="G136" t="n">
-        <v>24.8196506500244</v>
+        <v>24.8196563720703</v>
       </c>
       <c r="H136" t="n">
         <v>995</v>
@@ -4371,7 +4371,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G138" t="n">
-        <v>25.1545295715332</v>
+        <v>25.1545257568359</v>
       </c>
       <c r="H138" t="n">
         <v>2986</v>
@@ -4400,7 +4400,7 @@
         <v>32.0400009155273</v>
       </c>
       <c r="G139" t="n">
-        <v>24.9520454406738</v>
+        <v>24.9520473480225</v>
       </c>
       <c r="H139" t="n">
         <v>3355</v>
@@ -4458,7 +4458,7 @@
         <v>32.1500015258789</v>
       </c>
       <c r="G141" t="n">
-        <v>25.037712097168</v>
+        <v>25.0377140045166</v>
       </c>
       <c r="H141" t="n">
         <v>1637</v>
@@ -4487,7 +4487,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G142" t="n">
-        <v>25.1545295715332</v>
+        <v>25.1545257568359</v>
       </c>
       <c r="H142" t="n">
         <v>5696</v>
@@ -4545,7 +4545,7 @@
         <v>32.0699996948242</v>
       </c>
       <c r="G144" t="n">
-        <v>24.9754085540771</v>
+        <v>24.9754104614258</v>
       </c>
       <c r="H144" t="n">
         <v>1467</v>
@@ -4603,7 +4603,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G146" t="n">
-        <v>25.1545295715332</v>
+        <v>25.1545257568359</v>
       </c>
       <c r="H146" t="n">
         <v>3501</v>
@@ -4777,7 +4777,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>26.0111865997314</v>
+        <v>26.0111885070801</v>
       </c>
       <c r="H152" t="n">
         <v>2548</v>
@@ -4806,7 +4806,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>26.0111865997314</v>
+        <v>26.0111885070801</v>
       </c>
       <c r="H153" t="n">
         <v>2339</v>
@@ -4864,7 +4864,7 @@
         <v>33.060001373291</v>
       </c>
       <c r="G155" t="n">
-        <v>25.7464027404785</v>
+        <v>25.7464008331299</v>
       </c>
       <c r="H155" t="n">
         <v>4129</v>
@@ -4922,7 +4922,7 @@
         <v>32.5</v>
       </c>
       <c r="G157" t="n">
-        <v>25.3102836608887</v>
+        <v>25.3102874755859</v>
       </c>
       <c r="H157" t="n">
         <v>3379</v>
@@ -4951,7 +4951,7 @@
         <v>33.2299995422363</v>
       </c>
       <c r="G158" t="n">
-        <v>25.8787937164307</v>
+        <v>25.878791809082</v>
       </c>
       <c r="H158" t="n">
         <v>120</v>
@@ -4980,7 +4980,7 @@
         <v>33.1800003051758</v>
       </c>
       <c r="G159" t="n">
-        <v>25.8398513793945</v>
+        <v>25.8398532867432</v>
       </c>
       <c r="H159" t="n">
         <v>1728</v>
@@ -5009,7 +5009,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G160" t="n">
-        <v>25.8554306030273</v>
+        <v>25.8554286956787</v>
       </c>
       <c r="H160" t="n">
         <v>1206</v>
@@ -5038,7 +5038,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G161" t="n">
-        <v>25.6217975616455</v>
+        <v>25.6217994689941</v>
       </c>
       <c r="H161" t="n">
         <v>984</v>
@@ -5067,7 +5067,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G162" t="n">
-        <v>26.322696685791</v>
+        <v>26.3226928710938</v>
       </c>
       <c r="H162" t="n">
         <v>3557</v>
@@ -5096,7 +5096,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>27.0235939025879</v>
+        <v>27.0236015319824</v>
       </c>
       <c r="H163" t="n">
         <v>6263</v>
@@ -5125,7 +5125,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G164" t="n">
-        <v>27.724494934082</v>
+        <v>27.7244968414307</v>
       </c>
       <c r="H164" t="n">
         <v>9877</v>
@@ -5154,7 +5154,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G165" t="n">
-        <v>27.8023738861084</v>
+        <v>27.8023719787598</v>
       </c>
       <c r="H165" t="n">
         <v>3475</v>
@@ -5183,7 +5183,7 @@
         <v>36</v>
       </c>
       <c r="G166" t="n">
-        <v>28.0360050201416</v>
+        <v>28.0360069274902</v>
       </c>
       <c r="H166" t="n">
         <v>9880</v>
@@ -5212,7 +5212,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G167" t="n">
-        <v>28.659029006958</v>
+        <v>28.6590309143066</v>
       </c>
       <c r="H167" t="n">
         <v>13339</v>
@@ -5299,7 +5299,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>28.3475189208984</v>
+        <v>28.3475208282471</v>
       </c>
       <c r="H170" t="n">
         <v>2310</v>
@@ -5386,7 +5386,7 @@
         <v>35</v>
       </c>
       <c r="G173" t="n">
-        <v>27.257230758667</v>
+        <v>27.2572269439697</v>
       </c>
       <c r="H173" t="n">
         <v>3125</v>
@@ -5415,7 +5415,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G174" t="n">
-        <v>27.4129848480225</v>
+        <v>27.4129867553711</v>
       </c>
       <c r="H174" t="n">
         <v>6992</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G178" t="n">
-        <v>28.0360050201416</v>
+        <v>28.0360069274902</v>
       </c>
       <c r="H178" t="n">
         <v>1619</v>
@@ -5589,7 +5589,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G180" t="n">
-        <v>27.0235939025879</v>
+        <v>27.0236015319824</v>
       </c>
       <c r="H180" t="n">
         <v>7931</v>
@@ -5647,7 +5647,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>26.7120819091797</v>
+        <v>26.7120838165283</v>
       </c>
       <c r="H182" t="n">
         <v>1589</v>
@@ -5705,7 +5705,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>26.6342067718506</v>
+        <v>26.6342086791992</v>
       </c>
       <c r="H184" t="n">
         <v>7675</v>
@@ -5821,7 +5821,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G188" t="n">
-        <v>24.76513671875</v>
+        <v>24.7651386260986</v>
       </c>
       <c r="H188" t="n">
         <v>4764</v>
@@ -5850,7 +5850,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>24.3757495880127</v>
+        <v>24.3757476806641</v>
       </c>
       <c r="H189" t="n">
         <v>3231</v>
@@ -5908,7 +5908,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G191" t="n">
-        <v>25.6217975616455</v>
+        <v>25.6217994689941</v>
       </c>
       <c r="H191" t="n">
         <v>1664</v>
@@ -5966,7 +5966,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G193" t="n">
-        <v>25.8554306030273</v>
+        <v>25.8554286956787</v>
       </c>
       <c r="H193" t="n">
         <v>1028</v>
@@ -6053,7 +6053,7 @@
         <v>34</v>
       </c>
       <c r="G196" t="n">
-        <v>26.4784507751465</v>
+        <v>26.4784526824951</v>
       </c>
       <c r="H196" t="n">
         <v>501</v>
@@ -6082,7 +6082,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G197" t="n">
-        <v>26.7899608612061</v>
+        <v>26.7899684906006</v>
       </c>
       <c r="H197" t="n">
         <v>6683</v>
@@ -6111,7 +6111,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G198" t="n">
-        <v>26.9457168579102</v>
+        <v>26.9457187652588</v>
       </c>
       <c r="H198" t="n">
         <v>4790</v>
@@ -6169,7 +6169,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G200" t="n">
-        <v>25.6217975616455</v>
+        <v>25.6217994689941</v>
       </c>
       <c r="H200" t="n">
         <v>2308</v>
@@ -6198,7 +6198,7 @@
         <v>33</v>
       </c>
       <c r="G201" t="n">
-        <v>25.6996746063232</v>
+        <v>25.6996784210205</v>
       </c>
       <c r="H201" t="n">
         <v>283</v>
@@ -6227,7 +6227,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>24.8430194854736</v>
+        <v>24.843017578125</v>
       </c>
       <c r="H202" t="n">
         <v>5057</v>
@@ -6256,7 +6256,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G203" t="n">
-        <v>24.76513671875</v>
+        <v>24.7651386260986</v>
       </c>
       <c r="H203" t="n">
         <v>2660</v>
@@ -6343,7 +6343,7 @@
         <v>32.5</v>
       </c>
       <c r="G206" t="n">
-        <v>25.3102836608887</v>
+        <v>25.3102874755859</v>
       </c>
       <c r="H206" t="n">
         <v>1220</v>
@@ -6372,7 +6372,7 @@
         <v>32.5</v>
       </c>
       <c r="G207" t="n">
-        <v>25.3102836608887</v>
+        <v>25.3102874755859</v>
       </c>
       <c r="H207" t="n">
         <v>2453</v>
@@ -6401,7 +6401,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G208" t="n">
-        <v>26.0111865997314</v>
+        <v>26.0111885070801</v>
       </c>
       <c r="H208" t="n">
         <v>281</v>
@@ -6546,7 +6546,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G213" t="n">
-        <v>26.0111865997314</v>
+        <v>26.0111885070801</v>
       </c>
       <c r="H213" t="n">
         <v>312</v>
@@ -6604,7 +6604,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>26.322696685791</v>
+        <v>26.3226928710938</v>
       </c>
       <c r="H215" t="n">
         <v>187</v>
@@ -6662,7 +6662,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G217" t="n">
-        <v>26.1669387817383</v>
+        <v>26.1669368743896</v>
       </c>
       <c r="H217" t="n">
         <v>299</v>
@@ -6691,7 +6691,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G218" t="n">
-        <v>25.6217975616455</v>
+        <v>25.6217994689941</v>
       </c>
       <c r="H218" t="n">
         <v>4384</v>
@@ -6720,7 +6720,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G219" t="n">
-        <v>25.4660396575928</v>
+        <v>25.4660415649414</v>
       </c>
       <c r="H219" t="n">
         <v>875</v>
@@ -6749,7 +6749,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>25.4660396575928</v>
+        <v>25.4660415649414</v>
       </c>
       <c r="H220" t="n">
         <v>1296</v>
@@ -6778,7 +6778,7 @@
         <v>32</v>
       </c>
       <c r="G221" t="n">
-        <v>24.9208946228027</v>
+        <v>24.9208965301514</v>
       </c>
       <c r="H221" t="n">
         <v>10203</v>
@@ -6836,7 +6836,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G223" t="n">
-        <v>26.7899608612061</v>
+        <v>26.7899684906006</v>
       </c>
       <c r="H223" t="n">
         <v>2581</v>
@@ -6865,7 +6865,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G224" t="n">
-        <v>26.0111865997314</v>
+        <v>26.0111885070801</v>
       </c>
       <c r="H224" t="n">
         <v>5330</v>
@@ -6952,7 +6952,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G227" t="n">
-        <v>25.8554306030273</v>
+        <v>25.8554286956787</v>
       </c>
       <c r="H227" t="n">
         <v>6391</v>
@@ -6981,7 +6981,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G228" t="n">
-        <v>25.8554306030273</v>
+        <v>25.8554286956787</v>
       </c>
       <c r="H228" t="n">
         <v>581</v>
@@ -7039,7 +7039,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G230" t="n">
-        <v>25.4660396575928</v>
+        <v>25.4660415649414</v>
       </c>
       <c r="H230" t="n">
         <v>520</v>
@@ -7213,7 +7213,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G236" t="n">
-        <v>26.7899608612061</v>
+        <v>26.7899684906006</v>
       </c>
       <c r="H236" t="n">
         <v>968</v>
@@ -7242,7 +7242,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>26.7120819091797</v>
+        <v>26.7120838165283</v>
       </c>
       <c r="H237" t="n">
         <v>3045</v>
@@ -7271,7 +7271,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G238" t="n">
-        <v>26.7120819091797</v>
+        <v>26.7120838165283</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>26.6342067718506</v>
+        <v>26.6342086791992</v>
       </c>
       <c r="H240" t="n">
         <v>353</v>
@@ -7387,7 +7387,7 @@
         <v>34</v>
       </c>
       <c r="G242" t="n">
-        <v>26.4784507751465</v>
+        <v>26.4784526824951</v>
       </c>
       <c r="H242" t="n">
         <v>1034</v>
@@ -7445,7 +7445,7 @@
         <v>34</v>
       </c>
       <c r="G244" t="n">
-        <v>26.4784507751465</v>
+        <v>26.4784526824951</v>
       </c>
       <c r="H244" t="n">
         <v>552</v>
@@ -7503,7 +7503,7 @@
         <v>34</v>
       </c>
       <c r="G246" t="n">
-        <v>26.4784507751465</v>
+        <v>26.4784526824951</v>
       </c>
       <c r="H246" t="n">
         <v>1008</v>
@@ -7532,7 +7532,7 @@
         <v>34</v>
       </c>
       <c r="G247" t="n">
-        <v>26.4784507751465</v>
+        <v>26.4784526824951</v>
       </c>
       <c r="H247" t="n">
         <v>1269</v>
@@ -7561,7 +7561,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G248" t="n">
-        <v>26.7899608612061</v>
+        <v>26.7899684906006</v>
       </c>
       <c r="H248" t="n">
         <v>2819</v>
@@ -7590,7 +7590,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G249" t="n">
-        <v>26.1669387817383</v>
+        <v>26.1669368743896</v>
       </c>
       <c r="H249" t="n">
         <v>304</v>
@@ -7648,7 +7648,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>27.0235939025879</v>
+        <v>27.0236015319824</v>
       </c>
       <c r="H251" t="n">
         <v>405</v>
@@ -7706,7 +7706,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G253" t="n">
-        <v>26.322696685791</v>
+        <v>26.3226928710938</v>
       </c>
       <c r="H253" t="n">
         <v>2196</v>
@@ -7764,7 +7764,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G255" t="n">
-        <v>26.1669387817383</v>
+        <v>26.1669368743896</v>
       </c>
       <c r="H255" t="n">
         <v>2989</v>
@@ -7793,7 +7793,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G256" t="n">
-        <v>26.3895053863525</v>
+        <v>26.3895034790039</v>
       </c>
       <c r="H256" t="n">
         <v>146</v>
@@ -7851,7 +7851,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>25.6741237640381</v>
+        <v>25.6741218566895</v>
       </c>
       <c r="H258" t="n">
         <v>1105</v>
@@ -7880,7 +7880,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G259" t="n">
-        <v>26.3895053863525</v>
+        <v>26.3895034790039</v>
       </c>
       <c r="H259" t="n">
         <v>3038</v>
@@ -7938,7 +7938,7 @@
         <v>33</v>
       </c>
       <c r="G261" t="n">
-        <v>26.2305316925049</v>
+        <v>26.2305297851562</v>
       </c>
       <c r="H261" t="n">
         <v>8471</v>
@@ -7967,7 +7967,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>25.1177196502686</v>
+        <v>25.1177215576172</v>
       </c>
       <c r="H262" t="n">
         <v>7793</v>
@@ -7996,7 +7996,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G263" t="n">
-        <v>25.35618019104</v>
+        <v>25.3561782836914</v>
       </c>
       <c r="H263" t="n">
         <v>985</v>
@@ -8025,7 +8025,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G264" t="n">
-        <v>25.5151519775391</v>
+        <v>25.5151500701904</v>
       </c>
       <c r="H264" t="n">
         <v>240</v>
@@ -8054,7 +8054,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>25.9920711517334</v>
+        <v>25.9920692443848</v>
       </c>
       <c r="H265" t="n">
         <v>2251</v>
@@ -8112,7 +8112,7 @@
         <v>33</v>
       </c>
       <c r="G267" t="n">
-        <v>26.2305316925049</v>
+        <v>26.2305297851562</v>
       </c>
       <c r="H267" t="n">
         <v>310</v>
@@ -8141,7 +8141,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G268" t="n">
-        <v>26.4689865112305</v>
+        <v>26.4689884185791</v>
       </c>
       <c r="H268" t="n">
         <v>3961</v>
@@ -8170,7 +8170,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>26.8664226531982</v>
+        <v>26.866418838501</v>
       </c>
       <c r="H269" t="n">
         <v>1325</v>
@@ -8199,7 +8199,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G270" t="n">
-        <v>26.3895053863525</v>
+        <v>26.3895034790039</v>
       </c>
       <c r="H270" t="n">
         <v>18</v>
@@ -8228,7 +8228,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G271" t="n">
-        <v>26.3895053863525</v>
+        <v>26.3895034790039</v>
       </c>
       <c r="H271" t="n">
         <v>1160</v>
@@ -8257,7 +8257,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G272" t="n">
-        <v>26.4689865112305</v>
+        <v>26.4689884185791</v>
       </c>
       <c r="H272" t="n">
         <v>20</v>
@@ -8286,7 +8286,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>26.7869358062744</v>
+        <v>26.7869338989258</v>
       </c>
       <c r="H273" t="n">
         <v>528</v>
@@ -8315,7 +8315,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G274" t="n">
-        <v>26.4689865112305</v>
+        <v>26.4689884185791</v>
       </c>
       <c r="H274" t="n">
         <v>22</v>
@@ -8344,7 +8344,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G275" t="n">
-        <v>26.4689865112305</v>
+        <v>26.4689884185791</v>
       </c>
       <c r="H275" t="n">
         <v>64</v>
@@ -8373,7 +8373,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G276" t="n">
-        <v>26.4689865112305</v>
+        <v>26.4689884185791</v>
       </c>
       <c r="H276" t="n">
         <v>424</v>
@@ -8402,7 +8402,7 @@
         <v>33.5</v>
       </c>
       <c r="G277" t="n">
-        <v>26.6279602050781</v>
+        <v>26.6279621124268</v>
       </c>
       <c r="H277" t="n">
         <v>101</v>
@@ -8431,7 +8431,7 @@
         <v>33.5</v>
       </c>
       <c r="G278" t="n">
-        <v>26.6279602050781</v>
+        <v>26.6279621124268</v>
       </c>
       <c r="H278" t="n">
         <v>11083</v>
@@ -8489,7 +8489,7 @@
         <v>34</v>
       </c>
       <c r="G280" t="n">
-        <v>27.0253925323486</v>
+        <v>27.0253944396973</v>
       </c>
       <c r="H280" t="n">
         <v>2112</v>
@@ -8518,7 +8518,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>26.8664226531982</v>
+        <v>26.866418838501</v>
       </c>
       <c r="H281" t="n">
         <v>54</v>
@@ -8547,7 +8547,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G282" t="n">
-        <v>26.8664226531982</v>
+        <v>26.866418838501</v>
       </c>
       <c r="H282" t="n">
         <v>5889</v>
@@ -8576,7 +8576,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>26.8664226531982</v>
+        <v>26.866418838501</v>
       </c>
       <c r="H283" t="n">
         <v>958</v>
@@ -8605,7 +8605,7 @@
         <v>33.5</v>
       </c>
       <c r="G284" t="n">
-        <v>26.6279602050781</v>
+        <v>26.6279621124268</v>
       </c>
       <c r="H284" t="n">
         <v>2415</v>
@@ -8634,7 +8634,7 @@
         <v>34</v>
       </c>
       <c r="G285" t="n">
-        <v>27.0253925323486</v>
+        <v>27.0253944396973</v>
       </c>
       <c r="H285" t="n">
         <v>85</v>
@@ -8721,7 +8721,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G288" t="n">
-        <v>26.7869358062744</v>
+        <v>26.7869338989258</v>
       </c>
       <c r="H288" t="n">
         <v>125</v>
@@ -8779,7 +8779,7 @@
         <v>33.5</v>
       </c>
       <c r="G290" t="n">
-        <v>26.6279602050781</v>
+        <v>26.6279621124268</v>
       </c>
       <c r="H290" t="n">
         <v>1096</v>
@@ -8808,7 +8808,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>26.8664226531982</v>
+        <v>26.866418838501</v>
       </c>
       <c r="H291" t="n">
         <v>4293</v>
@@ -8837,7 +8837,7 @@
         <v>33.5</v>
       </c>
       <c r="G292" t="n">
-        <v>26.6279602050781</v>
+        <v>26.6279621124268</v>
       </c>
       <c r="H292" t="n">
         <v>705</v>
@@ -8866,7 +8866,7 @@
         <v>33.5</v>
       </c>
       <c r="G293" t="n">
-        <v>26.6279602050781</v>
+        <v>26.6279621124268</v>
       </c>
       <c r="H293" t="n">
         <v>2042</v>
@@ -8895,7 +8895,7 @@
         <v>33.5</v>
       </c>
       <c r="G294" t="n">
-        <v>26.6279602050781</v>
+        <v>26.6279621124268</v>
       </c>
       <c r="H294" t="n">
         <v>11</v>
@@ -8924,7 +8924,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G295" t="n">
-        <v>26.3895053863525</v>
+        <v>26.3895034790039</v>
       </c>
       <c r="H295" t="n">
         <v>3589</v>
@@ -8953,7 +8953,7 @@
         <v>33</v>
       </c>
       <c r="G296" t="n">
-        <v>26.2305316925049</v>
+        <v>26.2305297851562</v>
       </c>
       <c r="H296" t="n">
         <v>10793</v>
@@ -8982,7 +8982,7 @@
         <v>33</v>
       </c>
       <c r="G297" t="n">
-        <v>26.2305316925049</v>
+        <v>26.2305297851562</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -9011,7 +9011,7 @@
         <v>34.5</v>
       </c>
       <c r="G298" t="n">
-        <v>27.4228267669678</v>
+        <v>27.4228248596191</v>
       </c>
       <c r="H298" t="n">
         <v>660</v>
@@ -9040,7 +9040,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>26.8664226531982</v>
+        <v>26.866418838501</v>
       </c>
       <c r="H299" t="n">
         <v>30</v>
@@ -9069,7 +9069,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G300" t="n">
-        <v>26.9459095001221</v>
+        <v>26.9459075927734</v>
       </c>
       <c r="H300" t="n">
         <v>494</v>
@@ -9098,7 +9098,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>26.8664226531982</v>
+        <v>26.866418838501</v>
       </c>
       <c r="H301" t="n">
         <v>149</v>
@@ -9127,7 +9127,7 @@
         <v>33.5</v>
       </c>
       <c r="G302" t="n">
-        <v>26.6279602050781</v>
+        <v>26.6279621124268</v>
       </c>
       <c r="H302" t="n">
         <v>135</v>
@@ -9156,7 +9156,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>26.7869358062744</v>
+        <v>26.7869338989258</v>
       </c>
       <c r="H303" t="n">
         <v>1429</v>
@@ -9185,7 +9185,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G304" t="n">
-        <v>27.1048774719238</v>
+        <v>27.1048793792725</v>
       </c>
       <c r="H304" t="n">
         <v>28</v>
@@ -9243,7 +9243,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G306" t="n">
-        <v>26.4689865112305</v>
+        <v>26.4689884185791</v>
       </c>
       <c r="H306" t="n">
         <v>1033</v>
@@ -9272,7 +9272,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G307" t="n">
-        <v>26.3895053863525</v>
+        <v>26.3895034790039</v>
       </c>
       <c r="H307" t="n">
         <v>91</v>
@@ -9301,7 +9301,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>26.8664226531982</v>
+        <v>26.866418838501</v>
       </c>
       <c r="H308" t="n">
         <v>56</v>
@@ -9359,7 +9359,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>26.5484790802002</v>
+        <v>26.5484752655029</v>
       </c>
       <c r="H310" t="n">
         <v>269</v>
@@ -9388,7 +9388,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G311" t="n">
-        <v>26.1510448455811</v>
+        <v>26.1510429382324</v>
       </c>
       <c r="H311" t="n">
         <v>173</v>
@@ -9417,7 +9417,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G312" t="n">
-        <v>26.1510448455811</v>
+        <v>26.1510429382324</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G315" t="n">
-        <v>26.0715579986572</v>
+        <v>26.0715560913086</v>
       </c>
       <c r="H315" t="n">
         <v>147</v>
@@ -9562,7 +9562,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G317" t="n">
-        <v>25.5151519775391</v>
+        <v>25.5151500701904</v>
       </c>
       <c r="H317" t="n">
         <v>1111</v>
@@ -9591,7 +9591,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G318" t="n">
-        <v>25.5151519775391</v>
+        <v>25.5151500701904</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9678,7 +9678,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G321" t="n">
-        <v>25.6741237640381</v>
+        <v>25.6741218566895</v>
       </c>
       <c r="H321" t="n">
         <v>370</v>
@@ -9736,7 +9736,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G323" t="n">
-        <v>25.7536125183105</v>
+        <v>25.7536144256592</v>
       </c>
       <c r="H323" t="n">
         <v>87</v>
@@ -9765,7 +9765,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G324" t="n">
-        <v>25.9920711517334</v>
+        <v>25.9920692443848</v>
       </c>
       <c r="H324" t="n">
         <v>420</v>
@@ -9794,7 +9794,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>26.7869358062744</v>
+        <v>26.7869338989258</v>
       </c>
       <c r="H325" t="n">
         <v>1774</v>
@@ -9823,7 +9823,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>27.661283493042</v>
+        <v>27.6612854003906</v>
       </c>
       <c r="H326" t="n">
         <v>1128</v>
@@ -9852,7 +9852,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G327" t="n">
-        <v>27.5817966461182</v>
+        <v>27.5818023681641</v>
       </c>
       <c r="H327" t="n">
         <v>379</v>
@@ -9881,7 +9881,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>27.5817966461182</v>
+        <v>27.5818023681641</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>26.3895053863525</v>
+        <v>26.3895034790039</v>
       </c>
       <c r="H329" t="n">
         <v>207</v>
@@ -9939,7 +9939,7 @@
         <v>33</v>
       </c>
       <c r="G330" t="n">
-        <v>26.2305316925049</v>
+        <v>26.2305297851562</v>
       </c>
       <c r="H330" t="n">
         <v>1158</v>
@@ -9968,7 +9968,7 @@
         <v>33</v>
       </c>
       <c r="G331" t="n">
-        <v>26.2305316925049</v>
+        <v>26.2305297851562</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -9997,7 +9997,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G332" t="n">
-        <v>25.7536125183105</v>
+        <v>25.7536144256592</v>
       </c>
       <c r="H332" t="n">
         <v>262</v>
@@ -10055,7 +10055,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G334" t="n">
-        <v>26.7869358062744</v>
+        <v>26.7869338989258</v>
       </c>
       <c r="H334" t="n">
         <v>462</v>
@@ -10084,7 +10084,7 @@
         <v>33</v>
       </c>
       <c r="G335" t="n">
-        <v>26.2305316925049</v>
+        <v>26.2305297851562</v>
       </c>
       <c r="H335" t="n">
         <v>4058</v>
@@ -10113,7 +10113,7 @@
         <v>33</v>
       </c>
       <c r="G336" t="n">
-        <v>26.2305316925049</v>
+        <v>26.2305297851562</v>
       </c>
       <c r="H336" t="n">
         <v>1118</v>
@@ -10142,7 +10142,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G337" t="n">
-        <v>26.4689865112305</v>
+        <v>26.4689884185791</v>
       </c>
       <c r="H337" t="n">
         <v>504</v>
@@ -10171,7 +10171,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G338" t="n">
-        <v>26.5484790802002</v>
+        <v>26.5484752655029</v>
       </c>
       <c r="H338" t="n">
         <v>1421</v>
@@ -10200,7 +10200,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G339" t="n">
-        <v>26.8664226531982</v>
+        <v>26.866418838501</v>
       </c>
       <c r="H339" t="n">
         <v>1080</v>
@@ -10229,7 +10229,7 @@
         <v>34</v>
       </c>
       <c r="G340" t="n">
-        <v>27.0253925323486</v>
+        <v>27.0253944396973</v>
       </c>
       <c r="H340" t="n">
         <v>782</v>
@@ -10258,7 +10258,7 @@
         <v>33.5</v>
       </c>
       <c r="G341" t="n">
-        <v>26.6279602050781</v>
+        <v>26.6279621124268</v>
       </c>
       <c r="H341" t="n">
         <v>2655</v>
@@ -10287,7 +10287,7 @@
         <v>34</v>
       </c>
       <c r="G342" t="n">
-        <v>27.0253925323486</v>
+        <v>27.0253944396973</v>
       </c>
       <c r="H342" t="n">
         <v>296</v>
@@ -10316,7 +10316,7 @@
         <v>34</v>
       </c>
       <c r="G343" t="n">
-        <v>27.0253925323486</v>
+        <v>27.0253944396973</v>
       </c>
       <c r="H343" t="n">
         <v>1116</v>
@@ -10345,7 +10345,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G344" t="n">
-        <v>26.9459095001221</v>
+        <v>26.9459075927734</v>
       </c>
       <c r="H344" t="n">
         <v>207</v>
@@ -10403,7 +10403,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G346" t="n">
-        <v>26.7869358062744</v>
+        <v>26.7869338989258</v>
       </c>
       <c r="H346" t="n">
         <v>1389</v>
@@ -10432,7 +10432,7 @@
         <v>34</v>
       </c>
       <c r="G347" t="n">
-        <v>27.0253925323486</v>
+        <v>27.0253944396973</v>
       </c>
       <c r="H347" t="n">
         <v>403</v>
@@ -10461,7 +10461,7 @@
         <v>34</v>
       </c>
       <c r="G348" t="n">
-        <v>27.0253925323486</v>
+        <v>27.0253944396973</v>
       </c>
       <c r="H348" t="n">
         <v>754</v>
@@ -10519,7 +10519,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>26.8664226531982</v>
+        <v>26.866418838501</v>
       </c>
       <c r="H350" t="n">
         <v>55</v>
@@ -10548,7 +10548,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G351" t="n">
-        <v>26.4689865112305</v>
+        <v>26.4689884185791</v>
       </c>
       <c r="H351" t="n">
         <v>1614</v>
@@ -10577,7 +10577,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>26.1510448455811</v>
+        <v>26.1510429382324</v>
       </c>
       <c r="H352" t="n">
         <v>199</v>
@@ -10606,7 +10606,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G353" t="n">
-        <v>26.3895053863525</v>
+        <v>26.3895034790039</v>
       </c>
       <c r="H353" t="n">
         <v>124</v>
@@ -10635,7 +10635,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G354" t="n">
-        <v>26.3895053863525</v>
+        <v>26.3895034790039</v>
       </c>
       <c r="H354" t="n">
         <v>345</v>
@@ -10693,7 +10693,7 @@
         <v>32.0999984741211</v>
       </c>
       <c r="G356" t="n">
-        <v>25.5151519775391</v>
+        <v>25.5151500701904</v>
       </c>
       <c r="H356" t="n">
         <v>12072</v>
@@ -10722,7 +10722,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>25.6741237640381</v>
+        <v>25.6741218566895</v>
       </c>
       <c r="H357" t="n">
         <v>167</v>
@@ -10751,7 +10751,7 @@
         <v>31.5</v>
       </c>
       <c r="G358" t="n">
-        <v>25.0382328033447</v>
+        <v>25.0382308959961</v>
       </c>
       <c r="H358" t="n">
         <v>3357</v>
@@ -10780,7 +10780,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G359" t="n">
-        <v>24.3228549957275</v>
+        <v>24.3228569030762</v>
       </c>
       <c r="H359" t="n">
         <v>1873</v>
@@ -10867,7 +10867,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G362" t="n">
-        <v>23.607479095459</v>
+        <v>23.6074771881104</v>
       </c>
       <c r="H362" t="n">
         <v>467</v>
@@ -10896,7 +10896,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>23.2100448608398</v>
+        <v>23.2100467681885</v>
       </c>
       <c r="H363" t="n">
         <v>2139</v>
@@ -10983,7 +10983,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G366" t="n">
-        <v>22.5741539001465</v>
+        <v>22.5741519927979</v>
       </c>
       <c r="H366" t="n">
         <v>769</v>
@@ -11041,7 +11041,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G368" t="n">
-        <v>22.5741539001465</v>
+        <v>22.5741519927979</v>
       </c>
       <c r="H368" t="n">
         <v>3454</v>
@@ -11099,7 +11099,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G370" t="n">
-        <v>22.494665145874</v>
+        <v>22.4946670532227</v>
       </c>
       <c r="H370" t="n">
         <v>1192</v>
@@ -11157,7 +11157,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>21.9382610321045</v>
+        <v>21.9382629394531</v>
       </c>
       <c r="H372" t="n">
         <v>4678</v>
@@ -11215,7 +11215,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G374" t="n">
-        <v>22.494665145874</v>
+        <v>22.4946670532227</v>
       </c>
       <c r="H374" t="n">
         <v>109</v>
@@ -11302,7 +11302,7 @@
         <v>26.5</v>
       </c>
       <c r="G377" t="n">
-        <v>21.0639114379883</v>
+        <v>21.0639095306396</v>
       </c>
       <c r="H377" t="n">
         <v>5193</v>
@@ -11360,7 +11360,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G379" t="n">
-        <v>21.6203136444092</v>
+        <v>21.6203174591064</v>
       </c>
       <c r="H379" t="n">
         <v>3312</v>
@@ -11389,7 +11389,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G380" t="n">
-        <v>21.7792873382568</v>
+        <v>21.7792892456055</v>
       </c>
       <c r="H380" t="n">
         <v>1996</v>
@@ -11534,7 +11534,7 @@
         <v>26.5</v>
       </c>
       <c r="G385" t="n">
-        <v>21.0639114379883</v>
+        <v>21.0639095306396</v>
       </c>
       <c r="H385" t="n">
         <v>226</v>
@@ -11563,7 +11563,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G386" t="n">
-        <v>20.3485317230225</v>
+        <v>20.3485336303711</v>
       </c>
       <c r="H386" t="n">
         <v>1178</v>
@@ -11737,7 +11737,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>20.3485317230225</v>
+        <v>20.3485336303711</v>
       </c>
       <c r="H392" t="n">
         <v>654</v>
@@ -11766,7 +11766,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>20.3485317230225</v>
+        <v>20.3485336303711</v>
       </c>
       <c r="H393" t="n">
         <v>583</v>
@@ -11795,7 +11795,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>20.4280185699463</v>
+        <v>20.4280204772949</v>
       </c>
       <c r="H394" t="n">
         <v>674</v>
@@ -11824,7 +11824,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G395" t="n">
-        <v>19.9511013031006</v>
+        <v>19.951099395752</v>
       </c>
       <c r="H395" t="n">
         <v>403</v>
@@ -11853,7 +11853,7 @@
         <v>25</v>
       </c>
       <c r="G396" t="n">
-        <v>19.8716125488281</v>
+        <v>19.8716144561768</v>
       </c>
       <c r="H396" t="n">
         <v>7135</v>
@@ -11882,7 +11882,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>19.7126388549805</v>
+        <v>19.7126407623291</v>
       </c>
       <c r="H397" t="n">
         <v>1315</v>
@@ -11940,7 +11940,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G399" t="n">
-        <v>18.9177761077881</v>
+        <v>18.9177742004395</v>
       </c>
       <c r="H399" t="n">
         <v>7009</v>
@@ -11998,7 +11998,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>19.3152084350586</v>
+        <v>19.31520652771</v>
       </c>
       <c r="H401" t="n">
         <v>4009</v>
@@ -12027,7 +12027,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>18.9972610473633</v>
+        <v>18.9972591400146</v>
       </c>
       <c r="H402" t="n">
         <v>1449</v>
@@ -12085,7 +12085,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>18.9972610473633</v>
+        <v>18.9972591400146</v>
       </c>
       <c r="H404" t="n">
         <v>1062</v>
@@ -12114,7 +12114,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>18.5203437805176</v>
+        <v>18.5203418731689</v>
       </c>
       <c r="H405" t="n">
         <v>764</v>
@@ -12143,7 +12143,7 @@
         <v>23</v>
       </c>
       <c r="G406" t="n">
-        <v>18.2818851470947</v>
+        <v>18.2818832397461</v>
       </c>
       <c r="H406" t="n">
         <v>1511</v>
@@ -12172,7 +12172,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G407" t="n">
-        <v>18.1229095458984</v>
+        <v>18.1229114532471</v>
       </c>
       <c r="H407" t="n">
         <v>1282</v>
@@ -12201,7 +12201,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G408" t="n">
-        <v>17.7254810333252</v>
+        <v>17.7254772186279</v>
       </c>
       <c r="H408" t="n">
         <v>861</v>
@@ -12230,7 +12230,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G409" t="n">
-        <v>17.5665092468262</v>
+        <v>17.5665054321289</v>
       </c>
       <c r="H409" t="n">
         <v>4448</v>
@@ -12259,7 +12259,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G410" t="n">
-        <v>17.4075355529785</v>
+        <v>17.4075317382812</v>
       </c>
       <c r="H410" t="n">
         <v>522</v>
@@ -12288,7 +12288,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G411" t="n">
-        <v>18.9972610473633</v>
+        <v>18.9972591400146</v>
       </c>
       <c r="H411" t="n">
         <v>9367</v>
@@ -12317,7 +12317,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G412" t="n">
-        <v>18.9972610473633</v>
+        <v>18.9972591400146</v>
       </c>
       <c r="H412" t="n">
         <v>278</v>
@@ -12404,7 +12404,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G415" t="n">
-        <v>18.3613719940186</v>
+        <v>18.3613681793213</v>
       </c>
       <c r="H415" t="n">
         <v>3296</v>
@@ -12433,7 +12433,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>18.0434284210205</v>
+        <v>18.0434246063232</v>
       </c>
       <c r="H416" t="n">
         <v>1957</v>
@@ -12491,7 +12491,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G418" t="n">
-        <v>17.2485618591309</v>
+        <v>17.2485599517822</v>
       </c>
       <c r="H418" t="n">
         <v>2600</v>
@@ -12520,7 +12520,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>17.2485618591309</v>
+        <v>17.2485599517822</v>
       </c>
       <c r="H419" t="n">
         <v>1727</v>
@@ -12549,7 +12549,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>16.2152347564697</v>
+        <v>16.2152366638184</v>
       </c>
       <c r="H420" t="n">
         <v>9265</v>
@@ -12578,7 +12578,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G421" t="n">
-        <v>15.7383155822754</v>
+        <v>15.738317489624</v>
       </c>
       <c r="H421" t="n">
         <v>3214</v>
@@ -12607,7 +12607,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>16.0562629699707</v>
+        <v>16.056266784668</v>
       </c>
       <c r="H422" t="n">
         <v>16513</v>
@@ -12636,7 +12636,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G423" t="n">
-        <v>16.6126689910889</v>
+        <v>16.6126670837402</v>
       </c>
       <c r="H423" t="n">
         <v>5251</v>
@@ -12665,7 +12665,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>16.374210357666</v>
+        <v>16.3742084503174</v>
       </c>
       <c r="H424" t="n">
         <v>1326</v>
@@ -12723,7 +12723,7 @@
         <v>20</v>
       </c>
       <c r="G426" t="n">
-        <v>15.897289276123</v>
+        <v>15.8972911834717</v>
       </c>
       <c r="H426" t="n">
         <v>3491</v>
@@ -12752,7 +12752,7 @@
         <v>20</v>
       </c>
       <c r="G427" t="n">
-        <v>15.897289276123</v>
+        <v>15.8972911834717</v>
       </c>
       <c r="H427" t="n">
         <v>14751</v>
@@ -12781,7 +12781,7 @@
         <v>20</v>
       </c>
       <c r="G428" t="n">
-        <v>15.897289276123</v>
+        <v>15.8972911834717</v>
       </c>
       <c r="H428" t="n">
         <v>2023</v>
@@ -12926,7 +12926,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G433" t="n">
-        <v>16.2152347564697</v>
+        <v>16.2152366638184</v>
       </c>
       <c r="H433" t="n">
         <v>11592</v>
@@ -12955,7 +12955,7 @@
         <v>20.5</v>
       </c>
       <c r="G434" t="n">
-        <v>16.2947235107422</v>
+        <v>16.2947216033936</v>
       </c>
       <c r="H434" t="n">
         <v>2791</v>
@@ -12984,7 +12984,7 @@
         <v>20.5</v>
       </c>
       <c r="G435" t="n">
-        <v>16.2947235107422</v>
+        <v>16.2947216033936</v>
       </c>
       <c r="H435" t="n">
         <v>25692</v>
@@ -13042,7 +13042,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G437" t="n">
-        <v>17.0101013183594</v>
+        <v>17.0100994110107</v>
       </c>
       <c r="H437" t="n">
         <v>3730</v>
@@ -13071,7 +13071,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>16.6126689910889</v>
+        <v>16.6126670837402</v>
       </c>
       <c r="H438" t="n">
         <v>15823</v>
@@ -13100,7 +13100,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G439" t="n">
-        <v>16.2152347564697</v>
+        <v>16.2152366638184</v>
       </c>
       <c r="H439" t="n">
         <v>4994</v>
@@ -13245,7 +13245,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G444" t="n">
-        <v>17.6459922790527</v>
+        <v>17.6459941864014</v>
       </c>
       <c r="H444" t="n">
         <v>6729</v>
@@ -13274,7 +13274,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G445" t="n">
-        <v>18.0434284210205</v>
+        <v>18.0434246063232</v>
       </c>
       <c r="H445" t="n">
         <v>3143</v>
@@ -13303,7 +13303,7 @@
         <v>23</v>
       </c>
       <c r="G446" t="n">
-        <v>18.2818851470947</v>
+        <v>18.2818832397461</v>
       </c>
       <c r="H446" t="n">
         <v>7021</v>
@@ -13332,7 +13332,7 @@
         <v>23</v>
       </c>
       <c r="G447" t="n">
-        <v>18.2818851470947</v>
+        <v>18.2818832397461</v>
       </c>
       <c r="H447" t="n">
         <v>855</v>
@@ -13361,7 +13361,7 @@
         <v>23</v>
       </c>
       <c r="G448" t="n">
-        <v>18.2818851470947</v>
+        <v>18.2818832397461</v>
       </c>
       <c r="H448" t="n">
         <v>1832</v>
@@ -13390,7 +13390,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>18.9177761077881</v>
+        <v>18.9177742004395</v>
       </c>
       <c r="H449" t="n">
         <v>7589</v>
@@ -13419,7 +13419,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G450" t="n">
-        <v>18.9177761077881</v>
+        <v>18.9177742004395</v>
       </c>
       <c r="H450" t="n">
         <v>4613</v>
@@ -13448,7 +13448,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G451" t="n">
-        <v>18.5203437805176</v>
+        <v>18.5203418731689</v>
       </c>
       <c r="H451" t="n">
         <v>4867</v>
@@ -13477,7 +13477,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G452" t="n">
-        <v>18.5203437805176</v>
+        <v>18.5203418731689</v>
       </c>
       <c r="H452" t="n">
         <v>3713</v>
@@ -13506,7 +13506,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G453" t="n">
-        <v>18.5203437805176</v>
+        <v>18.5203418731689</v>
       </c>
       <c r="H453" t="n">
         <v>5130</v>
@@ -13535,7 +13535,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G454" t="n">
-        <v>18.5203437805176</v>
+        <v>18.5203418731689</v>
       </c>
       <c r="H454" t="n">
         <v>753</v>
@@ -13622,7 +13622,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>18.9972610473633</v>
+        <v>18.9972591400146</v>
       </c>
       <c r="H457" t="n">
         <v>6301</v>
@@ -13680,7 +13680,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G459" t="n">
-        <v>18.4408588409424</v>
+        <v>18.4408569335938</v>
       </c>
       <c r="H459" t="n">
         <v>1927</v>
@@ -13709,7 +13709,7 @@
         <v>23</v>
       </c>
       <c r="G460" t="n">
-        <v>18.2818851470947</v>
+        <v>18.2818832397461</v>
       </c>
       <c r="H460" t="n">
         <v>1819</v>
@@ -13738,7 +13738,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>18.2024002075195</v>
+        <v>18.2023983001709</v>
       </c>
       <c r="H461" t="n">
         <v>743</v>
@@ -13767,7 +13767,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G462" t="n">
-        <v>18.1229095458984</v>
+        <v>18.1229114532471</v>
       </c>
       <c r="H462" t="n">
         <v>1349</v>
@@ -13796,7 +13796,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G463" t="n">
-        <v>18.1229095458984</v>
+        <v>18.1229114532471</v>
       </c>
       <c r="H463" t="n">
         <v>5390</v>
@@ -13825,7 +13825,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G464" t="n">
-        <v>17.7254810333252</v>
+        <v>17.7254772186279</v>
       </c>
       <c r="H464" t="n">
         <v>487</v>
@@ -13854,7 +13854,7 @@
         <v>22.5</v>
       </c>
       <c r="G465" t="n">
-        <v>17.8844547271729</v>
+        <v>17.8844509124756</v>
       </c>
       <c r="H465" t="n">
         <v>8120</v>
@@ -13883,7 +13883,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>18.0434284210205</v>
+        <v>18.0434246063232</v>
       </c>
       <c r="H466" t="n">
         <v>3574</v>
@@ -13912,7 +13912,7 @@
         <v>22.5</v>
       </c>
       <c r="G467" t="n">
-        <v>17.8844547271729</v>
+        <v>17.8844509124756</v>
       </c>
       <c r="H467" t="n">
         <v>274</v>
@@ -13941,7 +13941,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G468" t="n">
-        <v>17.7254810333252</v>
+        <v>17.7254772186279</v>
       </c>
       <c r="H468" t="n">
         <v>700</v>
@@ -13970,7 +13970,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G469" t="n">
-        <v>17.7254810333252</v>
+        <v>17.7254772186279</v>
       </c>
       <c r="H469" t="n">
         <v>1724</v>
@@ -13999,7 +13999,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G470" t="n">
-        <v>17.7254810333252</v>
+        <v>17.7254772186279</v>
       </c>
       <c r="H470" t="n">
         <v>766</v>
@@ -14057,7 +14057,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G472" t="n">
-        <v>17.7254810333252</v>
+        <v>17.7254772186279</v>
       </c>
       <c r="H472" t="n">
         <v>1969</v>
@@ -14086,7 +14086,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G473" t="n">
-        <v>17.6459922790527</v>
+        <v>17.6459941864014</v>
       </c>
       <c r="H473" t="n">
         <v>647</v>
@@ -14144,7 +14144,7 @@
         <v>22.5</v>
       </c>
       <c r="G475" t="n">
-        <v>17.8844547271729</v>
+        <v>17.8844509124756</v>
       </c>
       <c r="H475" t="n">
         <v>1005</v>
@@ -14173,7 +14173,7 @@
         <v>22.5</v>
       </c>
       <c r="G476" t="n">
-        <v>17.8844547271729</v>
+        <v>17.8844509124756</v>
       </c>
       <c r="H476" t="n">
         <v>2510</v>
@@ -14202,7 +14202,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>17.8049640655518</v>
+        <v>17.8049659729004</v>
       </c>
       <c r="H477" t="n">
         <v>1106</v>
@@ -14231,7 +14231,7 @@
         <v>22.5</v>
       </c>
       <c r="G478" t="n">
-        <v>17.8844547271729</v>
+        <v>17.8844509124756</v>
       </c>
       <c r="H478" t="n">
         <v>1276</v>
@@ -14260,7 +14260,7 @@
         <v>23</v>
       </c>
       <c r="G479" t="n">
-        <v>18.2818851470947</v>
+        <v>18.2818832397461</v>
       </c>
       <c r="H479" t="n">
         <v>2678</v>
@@ -14289,7 +14289,7 @@
         <v>23</v>
       </c>
       <c r="G480" t="n">
-        <v>18.2818851470947</v>
+        <v>18.2818832397461</v>
       </c>
       <c r="H480" t="n">
         <v>110</v>
@@ -14318,7 +14318,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G481" t="n">
-        <v>18.1229095458984</v>
+        <v>18.1229114532471</v>
       </c>
       <c r="H481" t="n">
         <v>1075</v>
@@ -14347,7 +14347,7 @@
         <v>23</v>
       </c>
       <c r="G482" t="n">
-        <v>18.2818851470947</v>
+        <v>18.2818832397461</v>
       </c>
       <c r="H482" t="n">
         <v>208</v>
@@ -14376,7 +14376,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G483" t="n">
-        <v>18.2024002075195</v>
+        <v>18.2023983001709</v>
       </c>
       <c r="H483" t="n">
         <v>4379</v>
@@ -14463,7 +14463,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>18.9177761077881</v>
+        <v>18.9177742004395</v>
       </c>
       <c r="H486" t="n">
         <v>1116</v>
@@ -14521,7 +14521,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G488" t="n">
-        <v>18.9972610473633</v>
+        <v>18.9972591400146</v>
       </c>
       <c r="H488" t="n">
         <v>9602</v>
@@ -14550,7 +14550,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G489" t="n">
-        <v>18.5203437805176</v>
+        <v>18.5203418731689</v>
       </c>
       <c r="H489" t="n">
         <v>4411</v>
@@ -14579,7 +14579,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G490" t="n">
-        <v>18.1229095458984</v>
+        <v>18.1229114532471</v>
       </c>
       <c r="H490" t="n">
         <v>1775</v>
@@ -14608,7 +14608,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G491" t="n">
-        <v>18.1229095458984</v>
+        <v>18.1229114532471</v>
       </c>
       <c r="H491" t="n">
         <v>2839</v>
@@ -14637,7 +14637,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>18.3613719940186</v>
+        <v>18.3613681793213</v>
       </c>
       <c r="H492" t="n">
         <v>1587</v>
@@ -14666,7 +14666,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G493" t="n">
-        <v>18.4408588409424</v>
+        <v>18.4408569335938</v>
       </c>
       <c r="H493" t="n">
         <v>726</v>
@@ -14695,7 +14695,7 @@
         <v>23</v>
       </c>
       <c r="G494" t="n">
-        <v>18.2818851470947</v>
+        <v>18.2818832397461</v>
       </c>
       <c r="H494" t="n">
         <v>708</v>
@@ -14724,7 +14724,7 @@
         <v>22.5</v>
       </c>
       <c r="G495" t="n">
-        <v>17.8844547271729</v>
+        <v>17.8844509124756</v>
       </c>
       <c r="H495" t="n">
         <v>1729</v>
@@ -14753,7 +14753,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G496" t="n">
-        <v>17.8049640655518</v>
+        <v>17.8049659729004</v>
       </c>
       <c r="H496" t="n">
         <v>1868</v>
@@ -14782,7 +14782,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>17.5665092468262</v>
+        <v>17.5665054321289</v>
       </c>
       <c r="H497" t="n">
         <v>1702</v>
@@ -14840,7 +14840,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G499" t="n">
-        <v>17.9639358520508</v>
+        <v>17.9639377593994</v>
       </c>
       <c r="H499" t="n">
         <v>8054</v>
@@ -14869,7 +14869,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G500" t="n">
-        <v>17.8049640655518</v>
+        <v>17.8049659729004</v>
       </c>
       <c r="H500" t="n">
         <v>21136</v>
@@ -14898,7 +14898,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G501" t="n">
-        <v>17.9639358520508</v>
+        <v>17.9639377593994</v>
       </c>
       <c r="H501" t="n">
         <v>5001</v>
@@ -14927,7 +14927,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G502" t="n">
-        <v>17.5665092468262</v>
+        <v>17.5665054321289</v>
       </c>
       <c r="H502" t="n">
         <v>2130</v>
@@ -14956,7 +14956,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>17.5665092468262</v>
+        <v>17.5665054321289</v>
       </c>
       <c r="H503" t="n">
         <v>7496</v>
@@ -15014,7 +15014,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>17.9639358520508</v>
+        <v>17.9639377593994</v>
       </c>
       <c r="H505" t="n">
         <v>3828</v>
@@ -15043,7 +15043,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>17.9639358520508</v>
+        <v>17.9639377593994</v>
       </c>
       <c r="H506" t="n">
         <v>1891</v>
@@ -15072,7 +15072,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>17.8049640655518</v>
+        <v>17.8049659729004</v>
       </c>
       <c r="H507" t="n">
         <v>1434</v>
@@ -15101,7 +15101,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G508" t="n">
-        <v>18.0434284210205</v>
+        <v>18.0434246063232</v>
       </c>
       <c r="H508" t="n">
         <v>886</v>
@@ -15130,7 +15130,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G509" t="n">
-        <v>17.8049640655518</v>
+        <v>17.8049659729004</v>
       </c>
       <c r="H509" t="n">
         <v>341</v>
@@ -15159,7 +15159,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G510" t="n">
-        <v>17.8049640655518</v>
+        <v>17.8049659729004</v>
       </c>
       <c r="H510" t="n">
         <v>794</v>
@@ -15188,7 +15188,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G511" t="n">
-        <v>18.2888412475586</v>
+        <v>18.28883934021</v>
       </c>
       <c r="H511" t="n">
         <v>2034</v>
@@ -15275,7 +15275,7 @@
         <v>22</v>
       </c>
       <c r="G514" t="n">
-        <v>18.0428028106689</v>
+        <v>18.0428009033203</v>
       </c>
       <c r="H514" t="n">
         <v>270</v>
@@ -15304,7 +15304,7 @@
         <v>22</v>
       </c>
       <c r="G515" t="n">
-        <v>18.0428028106689</v>
+        <v>18.0428009033203</v>
       </c>
       <c r="H515" t="n">
         <v>150</v>
@@ -15478,7 +15478,7 @@
         <v>21.5</v>
       </c>
       <c r="G521" t="n">
-        <v>17.6327419281006</v>
+        <v>17.632740020752</v>
       </c>
       <c r="H521" t="n">
         <v>570</v>
@@ -15507,7 +15507,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G522" t="n">
-        <v>16.9766387939453</v>
+        <v>16.9766368865967</v>
       </c>
       <c r="H522" t="n">
         <v>575</v>
@@ -15739,7 +15739,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G530" t="n">
-        <v>18.2888412475586</v>
+        <v>18.28883934021</v>
       </c>
       <c r="H530" t="n">
         <v>1100</v>
@@ -15768,7 +15768,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G531" t="n">
-        <v>18.2888412475586</v>
+        <v>18.28883934021</v>
       </c>
       <c r="H531" t="n">
         <v>322</v>
@@ -15797,7 +15797,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G532" t="n">
-        <v>18.2888412475586</v>
+        <v>18.28883934021</v>
       </c>
       <c r="H532" t="n">
         <v>5273</v>
@@ -15855,7 +15855,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G534" t="n">
-        <v>19.0269565582275</v>
+        <v>19.0269546508789</v>
       </c>
       <c r="H534" t="n">
         <v>12571</v>
@@ -15942,7 +15942,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G537" t="n">
-        <v>19.1909790039062</v>
+        <v>19.1909809112549</v>
       </c>
       <c r="H537" t="n">
         <v>1390</v>
@@ -15971,7 +15971,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G538" t="n">
-        <v>19.1909790039062</v>
+        <v>19.1909809112549</v>
       </c>
       <c r="H538" t="n">
         <v>6235</v>
@@ -16029,7 +16029,7 @@
         <v>23.5</v>
       </c>
       <c r="G540" t="n">
-        <v>19.2729911804199</v>
+        <v>19.2729930877686</v>
       </c>
       <c r="H540" t="n">
         <v>1038</v>
@@ -16058,7 +16058,7 @@
         <v>23.5</v>
       </c>
       <c r="G541" t="n">
-        <v>19.2729911804199</v>
+        <v>19.2729930877686</v>
       </c>
       <c r="H541" t="n">
         <v>731</v>
@@ -16087,7 +16087,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>19.1909790039062</v>
+        <v>19.1909809112549</v>
       </c>
       <c r="H542" t="n">
         <v>1338</v>
@@ -16116,7 +16116,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>19.0269565582275</v>
+        <v>19.0269546508789</v>
       </c>
       <c r="H543" t="n">
         <v>1643</v>
@@ -16145,7 +16145,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>19.1909790039062</v>
+        <v>19.1909809112549</v>
       </c>
       <c r="H544" t="n">
         <v>331</v>
@@ -16406,7 +16406,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G553" t="n">
-        <v>18.5348796844482</v>
+        <v>18.5348777770996</v>
       </c>
       <c r="H553" t="n">
         <v>1335</v>
@@ -16464,7 +16464,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G555" t="n">
-        <v>18.2888412475586</v>
+        <v>18.28883934021</v>
       </c>
       <c r="H555" t="n">
         <v>1025</v>
@@ -16551,7 +16551,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G558" t="n">
-        <v>18.2888412475586</v>
+        <v>18.28883934021</v>
       </c>
       <c r="H558" t="n">
         <v>1409</v>
@@ -16783,7 +16783,7 @@
         <v>22</v>
       </c>
       <c r="G566" t="n">
-        <v>18.0428028106689</v>
+        <v>18.0428009033203</v>
       </c>
       <c r="H566" t="n">
         <v>145</v>
@@ -16812,7 +16812,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>18.1248168945312</v>
+        <v>18.1248149871826</v>
       </c>
       <c r="H567" t="n">
         <v>645</v>
@@ -16841,7 +16841,7 @@
         <v>22</v>
       </c>
       <c r="G568" t="n">
-        <v>18.0428028106689</v>
+        <v>18.0428009033203</v>
       </c>
       <c r="H568" t="n">
         <v>401</v>
@@ -16870,7 +16870,7 @@
         <v>22</v>
       </c>
       <c r="G569" t="n">
-        <v>18.0428028106689</v>
+        <v>18.0428009033203</v>
       </c>
       <c r="H569" t="n">
         <v>523</v>
@@ -16899,7 +16899,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G570" t="n">
-        <v>17.7967662811279</v>
+        <v>17.7967643737793</v>
       </c>
       <c r="H570" t="n">
         <v>394</v>
@@ -16957,7 +16957,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G572" t="n">
-        <v>18.2888412475586</v>
+        <v>18.28883934021</v>
       </c>
       <c r="H572" t="n">
         <v>170</v>
@@ -16986,7 +16986,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G573" t="n">
-        <v>18.2888412475586</v>
+        <v>18.28883934021</v>
       </c>
       <c r="H573" t="n">
         <v>630</v>
@@ -17015,7 +17015,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G574" t="n">
-        <v>18.2888412475586</v>
+        <v>18.28883934021</v>
       </c>
       <c r="H574" t="n">
         <v>570</v>
@@ -17247,7 +17247,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G582" t="n">
-        <v>18.1248168945312</v>
+        <v>18.1248149871826</v>
       </c>
       <c r="H582" t="n">
         <v>297</v>
@@ -17334,7 +17334,7 @@
         <v>22</v>
       </c>
       <c r="G585" t="n">
-        <v>18.0428028106689</v>
+        <v>18.0428009033203</v>
       </c>
       <c r="H585" t="n">
         <v>270</v>
@@ -17363,7 +17363,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G586" t="n">
-        <v>18.5348796844482</v>
+        <v>18.5348777770996</v>
       </c>
       <c r="H586" t="n">
         <v>3649</v>
@@ -17595,7 +17595,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>18.2888412475586</v>
+        <v>18.28883934021</v>
       </c>
       <c r="H594" t="n">
         <v>944</v>
@@ -17624,7 +17624,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G595" t="n">
-        <v>18.5348796844482</v>
+        <v>18.5348777770996</v>
       </c>
       <c r="H595" t="n">
         <v>559</v>
@@ -17653,7 +17653,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G596" t="n">
-        <v>18.5348796844482</v>
+        <v>18.5348777770996</v>
       </c>
       <c r="H596" t="n">
         <v>847</v>
@@ -17827,7 +17827,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G602" t="n">
-        <v>16.32053565979</v>
+        <v>16.3205337524414</v>
       </c>
       <c r="H602" t="n">
         <v>17384</v>
@@ -17856,7 +17856,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>16.32053565979</v>
+        <v>16.3205337524414</v>
       </c>
       <c r="H603" t="n">
         <v>1523</v>
@@ -17885,7 +17885,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G604" t="n">
-        <v>16.5665721893311</v>
+        <v>16.5665760040283</v>
       </c>
       <c r="H604" t="n">
         <v>1273</v>
@@ -17914,7 +17914,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>16.5665721893311</v>
+        <v>16.5665760040283</v>
       </c>
       <c r="H605" t="n">
         <v>1933</v>
@@ -17943,7 +17943,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G606" t="n">
-        <v>16.5665721893311</v>
+        <v>16.5665760040283</v>
       </c>
       <c r="H606" t="n">
         <v>2565</v>
@@ -17972,7 +17972,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G607" t="n">
-        <v>16.5665721893311</v>
+        <v>16.5665760040283</v>
       </c>
       <c r="H607" t="n">
         <v>875</v>
@@ -18001,7 +18001,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>16.32053565979</v>
+        <v>16.3205337524414</v>
       </c>
       <c r="H608" t="n">
         <v>1301</v>
@@ -18146,7 +18146,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>16.1565093994141</v>
+        <v>16.1565113067627</v>
       </c>
       <c r="H613" t="n">
         <v>1355</v>
@@ -18175,7 +18175,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G614" t="n">
-        <v>16.2385196685791</v>
+        <v>16.2385215759277</v>
       </c>
       <c r="H614" t="n">
         <v>2123</v>
@@ -18204,7 +18204,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G615" t="n">
-        <v>16.32053565979</v>
+        <v>16.3205337524414</v>
       </c>
       <c r="H615" t="n">
         <v>986</v>
@@ -18233,7 +18233,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>16.5665721893311</v>
+        <v>16.5665760040283</v>
       </c>
       <c r="H616" t="n">
         <v>4471</v>
@@ -18291,7 +18291,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>16.2385196685791</v>
+        <v>16.2385215759277</v>
       </c>
       <c r="H618" t="n">
         <v>3322</v>
@@ -18320,7 +18320,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G619" t="n">
-        <v>16.1565093994141</v>
+        <v>16.1565113067627</v>
       </c>
       <c r="H619" t="n">
         <v>4583</v>
@@ -18378,7 +18378,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G621" t="n">
-        <v>16.0334873199463</v>
+        <v>16.0334892272949</v>
       </c>
       <c r="H621" t="n">
         <v>6890</v>
@@ -18407,7 +18407,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G622" t="n">
-        <v>16.1565093994141</v>
+        <v>16.1565113067627</v>
       </c>
       <c r="H622" t="n">
         <v>7694</v>
@@ -18465,7 +18465,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G624" t="n">
-        <v>16.32053565979</v>
+        <v>16.3205337524414</v>
       </c>
       <c r="H624" t="n">
         <v>1269</v>
@@ -18494,7 +18494,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G625" t="n">
-        <v>15.4594011306763</v>
+        <v>15.459400177002</v>
       </c>
       <c r="H625" t="n">
         <v>17116</v>
@@ -18523,7 +18523,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>15.4594011306763</v>
+        <v>15.459400177002</v>
       </c>
       <c r="H626" t="n">
         <v>4871</v>
@@ -18552,7 +18552,7 @@
         <v>19</v>
       </c>
       <c r="G627" t="n">
-        <v>15.5824193954468</v>
+        <v>15.5824203491211</v>
       </c>
       <c r="H627" t="n">
         <v>3868</v>
@@ -18581,7 +18581,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>15.5414113998413</v>
+        <v>15.5414142608643</v>
       </c>
       <c r="H628" t="n">
         <v>2723</v>
@@ -18610,7 +18610,7 @@
         <v>19</v>
       </c>
       <c r="G629" t="n">
-        <v>15.5824193954468</v>
+        <v>15.5824203491211</v>
       </c>
       <c r="H629" t="n">
         <v>2109</v>
@@ -18639,7 +18639,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G630" t="n">
-        <v>15.6234264373779</v>
+        <v>15.6234254837036</v>
       </c>
       <c r="H630" t="n">
         <v>4009</v>
@@ -18668,7 +18668,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>15.3363828659058</v>
+        <v>15.3363847732544</v>
       </c>
       <c r="H631" t="n">
         <v>2902</v>
@@ -18726,7 +18726,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>15.5004091262817</v>
+        <v>15.5004072189331</v>
       </c>
       <c r="H633" t="n">
         <v>3297</v>
@@ -18784,7 +18784,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G635" t="n">
-        <v>15.2543678283691</v>
+        <v>15.2543697357178</v>
       </c>
       <c r="H635" t="n">
         <v>3371</v>
@@ -18813,7 +18813,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>15.6234264373779</v>
+        <v>15.6234254837036</v>
       </c>
       <c r="H636" t="n">
         <v>6023</v>
@@ -18842,7 +18842,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G637" t="n">
-        <v>15.6234264373779</v>
+        <v>15.6234254837036</v>
       </c>
       <c r="H637" t="n">
         <v>1596</v>
@@ -18871,7 +18871,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>15.5004091262817</v>
+        <v>15.5004072189331</v>
       </c>
       <c r="H638" t="n">
         <v>3150</v>
@@ -18900,7 +18900,7 @@
         <v>19</v>
       </c>
       <c r="G639" t="n">
-        <v>15.5824193954468</v>
+        <v>15.5824203491211</v>
       </c>
       <c r="H639" t="n">
         <v>2084</v>
@@ -18929,7 +18929,7 @@
         <v>19</v>
       </c>
       <c r="G640" t="n">
-        <v>15.5824193954468</v>
+        <v>15.5824203491211</v>
       </c>
       <c r="H640" t="n">
         <v>3268</v>
@@ -18958,7 +18958,7 @@
         <v>19</v>
       </c>
       <c r="G641" t="n">
-        <v>15.5824193954468</v>
+        <v>15.5824203491211</v>
       </c>
       <c r="H641" t="n">
         <v>1572</v>
@@ -18987,7 +18987,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>15.6644344329834</v>
+        <v>15.6644334793091</v>
       </c>
       <c r="H642" t="n">
         <v>8472</v>
@@ -19016,7 +19016,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>15.6644344329834</v>
+        <v>15.6644334793091</v>
       </c>
       <c r="H643" t="n">
         <v>10694</v>
@@ -19045,7 +19045,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>15.6644344329834</v>
+        <v>15.6644334793091</v>
       </c>
       <c r="H644" t="n">
         <v>9680</v>
@@ -19306,7 +19306,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G653" t="n">
-        <v>16.9766387939453</v>
+        <v>16.9766368865967</v>
       </c>
       <c r="H653" t="n">
         <v>4193</v>
@@ -19422,7 +19422,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>17.7967662811279</v>
+        <v>17.7967643737793</v>
       </c>
       <c r="H657" t="n">
         <v>24549</v>
@@ -19509,7 +19509,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>17.4687118530273</v>
+        <v>17.4687099456787</v>
       </c>
       <c r="H660" t="n">
         <v>1613</v>
@@ -19567,7 +19567,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G662" t="n">
-        <v>17.4687118530273</v>
+        <v>17.4687099456787</v>
       </c>
       <c r="H662" t="n">
         <v>2438</v>
@@ -19596,7 +19596,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G663" t="n">
-        <v>17.7967662811279</v>
+        <v>17.7967643737793</v>
       </c>
       <c r="H663" t="n">
         <v>2933</v>
@@ -19625,7 +19625,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G664" t="n">
-        <v>17.7967662811279</v>
+        <v>17.7967643737793</v>
       </c>
       <c r="H664" t="n">
         <v>1371</v>
@@ -19683,7 +19683,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>17.4687118530273</v>
+        <v>17.4687099456787</v>
       </c>
       <c r="H666" t="n">
         <v>926</v>
@@ -19828,7 +19828,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G671" t="n">
-        <v>16.9766387939453</v>
+        <v>16.9766368865967</v>
       </c>
       <c r="H671" t="n">
         <v>6467</v>
@@ -19857,7 +19857,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G672" t="n">
-        <v>16.9766387939453</v>
+        <v>16.9766368865967</v>
       </c>
       <c r="H672" t="n">
         <v>520</v>
@@ -20147,7 +20147,7 @@
         <v>21.5</v>
       </c>
       <c r="G682" t="n">
-        <v>17.6327419281006</v>
+        <v>17.632740020752</v>
       </c>
       <c r="H682" t="n">
         <v>7721</v>
@@ -20205,7 +20205,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G684" t="n">
-        <v>17.7967662811279</v>
+        <v>17.7967643737793</v>
       </c>
       <c r="H684" t="n">
         <v>1890</v>
@@ -20234,7 +20234,7 @@
         <v>21.5</v>
       </c>
       <c r="G685" t="n">
-        <v>17.6327419281006</v>
+        <v>17.632740020752</v>
       </c>
       <c r="H685" t="n">
         <v>17346</v>
@@ -20408,7 +20408,7 @@
         <v>20.5</v>
       </c>
       <c r="G691" t="n">
-        <v>16.8126125335693</v>
+        <v>16.8126106262207</v>
       </c>
       <c r="H691" t="n">
         <v>1369</v>
@@ -20524,7 +20524,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G695" t="n">
-        <v>16.5665721893311</v>
+        <v>16.5665760040283</v>
       </c>
       <c r="H695" t="n">
         <v>1097</v>
@@ -20582,7 +20582,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>16.1565093994141</v>
+        <v>16.1565113067627</v>
       </c>
       <c r="H697" t="n">
         <v>1249</v>
@@ -20611,7 +20611,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>16.1565093994141</v>
+        <v>16.1565113067627</v>
       </c>
       <c r="H698" t="n">
         <v>793</v>
@@ -20727,7 +20727,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G702" t="n">
-        <v>15.0083312988281</v>
+        <v>15.0083332061768</v>
       </c>
       <c r="H702" t="n">
         <v>349</v>
@@ -20785,7 +20785,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G704" t="n">
-        <v>15.0083312988281</v>
+        <v>15.0083332061768</v>
       </c>
       <c r="H704" t="n">
         <v>2211</v>
@@ -20814,7 +20814,7 @@
         <v>17.5</v>
       </c>
       <c r="G705" t="n">
-        <v>14.3522291183472</v>
+        <v>14.3522281646729</v>
       </c>
       <c r="H705" t="n">
         <v>2984</v>
@@ -20843,7 +20843,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>14.721284866333</v>
+        <v>14.7212886810303</v>
       </c>
       <c r="H706" t="n">
         <v>2844</v>
@@ -20872,7 +20872,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G707" t="n">
-        <v>15.2543678283691</v>
+        <v>15.2543697357178</v>
       </c>
       <c r="H707" t="n">
         <v>1376</v>
@@ -20901,7 +20901,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G708" t="n">
-        <v>14.2292098999023</v>
+        <v>14.229211807251</v>
       </c>
       <c r="H708" t="n">
         <v>1701</v>
@@ -20959,7 +20959,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>12.6709661483765</v>
+        <v>12.6709671020508</v>
       </c>
       <c r="H710" t="n">
         <v>3678</v>
@@ -20988,7 +20988,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>11.6048011779785</v>
+        <v>11.6048030853271</v>
       </c>
       <c r="H711" t="n">
         <v>2777</v>
@@ -21017,7 +21017,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>11.8098344802856</v>
+        <v>11.8098335266113</v>
       </c>
       <c r="H712" t="n">
         <v>1837</v>
@@ -21162,7 +21162,7 @@
         <v>13.5</v>
       </c>
       <c r="G717" t="n">
-        <v>11.071720123291</v>
+        <v>11.0717191696167</v>
       </c>
       <c r="H717" t="n">
         <v>538</v>
@@ -21191,7 +21191,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G718" t="n">
-        <v>11.0307121276855</v>
+        <v>11.0307130813599</v>
       </c>
       <c r="H718" t="n">
         <v>574</v>
@@ -21220,7 +21220,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G719" t="n">
-        <v>10.2925977706909</v>
+        <v>10.2925987243652</v>
       </c>
       <c r="H719" t="n">
         <v>1023</v>
@@ -21249,7 +21249,7 @@
         <v>13</v>
       </c>
       <c r="G720" t="n">
-        <v>10.6616554260254</v>
+        <v>10.6616563796997</v>
       </c>
       <c r="H720" t="n">
         <v>4184</v>
@@ -21365,7 +21365,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G724" t="n">
-        <v>10.2925977706909</v>
+        <v>10.2925987243652</v>
       </c>
       <c r="H724" t="n">
         <v>3609</v>
@@ -21452,7 +21452,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G727" t="n">
-        <v>10.4156179428101</v>
+        <v>10.4156188964844</v>
       </c>
       <c r="H727" t="n">
         <v>1497</v>
@@ -21568,7 +21568,7 @@
         <v>12.75</v>
       </c>
       <c r="G731" t="n">
-        <v>10.4566230773926</v>
+        <v>10.4566240310669</v>
       </c>
       <c r="H731" t="n">
         <v>3856</v>
@@ -21626,7 +21626,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>9.59548950195312</v>
+        <v>9.59549045562744</v>
       </c>
       <c r="H733" t="n">
         <v>34244</v>
@@ -21742,7 +21742,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>10.7026615142822</v>
+        <v>10.7026634216309</v>
       </c>
       <c r="H737" t="n">
         <v>8882</v>
@@ -21800,7 +21800,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>11.7688283920288</v>
+        <v>11.7688293457031</v>
       </c>
       <c r="H739" t="n">
         <v>12484</v>
@@ -21829,7 +21829,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>11.7688283920288</v>
+        <v>11.7688293457031</v>
       </c>
       <c r="H740" t="n">
         <v>3570</v>
@@ -21858,7 +21858,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G741" t="n">
-        <v>11.7278213500977</v>
+        <v>11.7278232574463</v>
       </c>
       <c r="H741" t="n">
         <v>4602</v>
@@ -21887,7 +21887,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>11.6048011779785</v>
+        <v>11.6048030853271</v>
       </c>
       <c r="H742" t="n">
         <v>3261</v>
@@ -21916,7 +21916,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>11.6048011779785</v>
+        <v>11.6048030853271</v>
       </c>
       <c r="H743" t="n">
         <v>2653</v>
@@ -21945,7 +21945,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G744" t="n">
-        <v>11.7278213500977</v>
+        <v>11.7278232574463</v>
       </c>
       <c r="H744" t="n">
         <v>5199</v>
@@ -22003,7 +22003,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G746" t="n">
-        <v>11.8098344802856</v>
+        <v>11.8098335266113</v>
       </c>
       <c r="H746" t="n">
         <v>6096</v>
@@ -22032,7 +22032,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G747" t="n">
-        <v>11.8508415222168</v>
+        <v>11.8508396148682</v>
       </c>
       <c r="H747" t="n">
         <v>3116</v>
@@ -22061,7 +22061,7 @@
         <v>14</v>
       </c>
       <c r="G748" t="n">
-        <v>11.4817848205566</v>
+        <v>11.481782913208</v>
       </c>
       <c r="H748" t="n">
         <v>2932</v>
@@ -22090,7 +22090,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G749" t="n">
-        <v>11.645809173584</v>
+        <v>11.6458082199097</v>
       </c>
       <c r="H749" t="n">
         <v>474</v>
@@ -22119,7 +22119,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G750" t="n">
-        <v>11.3997716903687</v>
+        <v>11.3997707366943</v>
       </c>
       <c r="H750" t="n">
         <v>2207</v>
@@ -22148,7 +22148,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>11.3587636947632</v>
+        <v>11.3587646484375</v>
       </c>
       <c r="H751" t="n">
         <v>401</v>
@@ -22177,7 +22177,7 @@
         <v>13.5</v>
       </c>
       <c r="G752" t="n">
-        <v>11.071720123291</v>
+        <v>11.0717191696167</v>
       </c>
       <c r="H752" t="n">
         <v>1046</v>
@@ -22206,7 +22206,7 @@
         <v>12.75</v>
       </c>
       <c r="G753" t="n">
-        <v>10.4566230773926</v>
+        <v>10.4566240310669</v>
       </c>
       <c r="H753" t="n">
         <v>3056</v>
@@ -22293,7 +22293,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>10.3746109008789</v>
+        <v>10.3746128082275</v>
       </c>
       <c r="H756" t="n">
         <v>1446</v>
@@ -22351,7 +22351,7 @@
         <v>13</v>
       </c>
       <c r="G758" t="n">
-        <v>10.6616554260254</v>
+        <v>10.6616563796997</v>
       </c>
       <c r="H758" t="n">
         <v>3299</v>
@@ -22409,7 +22409,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G760" t="n">
-        <v>10.4156179428101</v>
+        <v>10.4156188964844</v>
       </c>
       <c r="H760" t="n">
         <v>2262</v>
@@ -22438,7 +22438,7 @@
         <v>13.5</v>
       </c>
       <c r="G761" t="n">
-        <v>11.071720123291</v>
+        <v>11.0717191696167</v>
       </c>
       <c r="H761" t="n">
         <v>4874</v>
@@ -22467,7 +22467,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G762" t="n">
-        <v>11.3997716903687</v>
+        <v>11.3997707366943</v>
       </c>
       <c r="H762" t="n">
         <v>1691</v>
@@ -22525,7 +22525,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G764" t="n">
-        <v>12.0148649215698</v>
+        <v>12.0148658752441</v>
       </c>
       <c r="H764" t="n">
         <v>1931</v>
@@ -22583,7 +22583,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G766" t="n">
-        <v>11.9328536987305</v>
+        <v>11.9328546524048</v>
       </c>
       <c r="H766" t="n">
         <v>1916</v>
@@ -22612,7 +22612,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>12.0148649215698</v>
+        <v>12.0148658752441</v>
       </c>
       <c r="H767" t="n">
         <v>3526</v>
@@ -22641,7 +22641,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G768" t="n">
-        <v>12.1378870010376</v>
+        <v>12.137885093689</v>
       </c>
       <c r="H768" t="n">
         <v>1254</v>
@@ -22699,7 +22699,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G770" t="n">
-        <v>12.0148649215698</v>
+        <v>12.0148658752441</v>
       </c>
       <c r="H770" t="n">
         <v>2134</v>
@@ -22757,7 +22757,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>12.4249286651611</v>
+        <v>12.4249296188354</v>
       </c>
       <c r="H772" t="n">
         <v>4778</v>
@@ -22815,7 +22815,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G774" t="n">
-        <v>14.3932323455811</v>
+        <v>14.393235206604</v>
       </c>
       <c r="H774" t="n">
         <v>15355</v>
@@ -22873,7 +22873,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G776" t="n">
-        <v>13.4500894546509</v>
+        <v>13.4500885009766</v>
       </c>
       <c r="H776" t="n">
         <v>4519</v>
@@ -22902,7 +22902,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>13.2860641479492</v>
+        <v>13.2860651016235</v>
       </c>
       <c r="H777" t="n">
         <v>2257</v>
@@ -22931,7 +22931,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G778" t="n">
-        <v>13.2860641479492</v>
+        <v>13.2860651016235</v>
       </c>
       <c r="H778" t="n">
         <v>1692</v>
@@ -22989,7 +22989,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>13.4910974502563</v>
+        <v>13.4910955429077</v>
       </c>
       <c r="H780" t="n">
         <v>495</v>
@@ -23047,7 +23047,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G782" t="n">
-        <v>12.9580125808716</v>
+        <v>12.9580135345459</v>
       </c>
       <c r="H782" t="n">
         <v>819</v>
@@ -23076,7 +23076,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G783" t="n">
-        <v>12.6709661483765</v>
+        <v>12.6709671020508</v>
       </c>
       <c r="H783" t="n">
         <v>379</v>
@@ -23308,7 +23308,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G791" t="n">
-        <v>13.0810308456421</v>
+        <v>13.0810317993164</v>
       </c>
       <c r="H791" t="n">
         <v>1933</v>
@@ -23395,7 +23395,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G794" t="n">
-        <v>13.2860641479492</v>
+        <v>13.2860651016235</v>
       </c>
       <c r="H794" t="n">
         <v>70</v>
@@ -23424,7 +23424,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>13.2450571060181</v>
+        <v>13.2450561523438</v>
       </c>
       <c r="H795" t="n">
         <v>968</v>
@@ -23482,7 +23482,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>13.0400238037109</v>
+        <v>13.0400247573853</v>
       </c>
       <c r="H797" t="n">
         <v>1010</v>
@@ -23511,7 +23511,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>12.7939882278442</v>
+        <v>12.7939872741699</v>
       </c>
       <c r="H798" t="n">
         <v>3330</v>
@@ -23569,7 +23569,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G800" t="n">
-        <v>12.7939882278442</v>
+        <v>12.7939872741699</v>
       </c>
       <c r="H800" t="n">
         <v>533</v>
@@ -23714,7 +23714,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G805" t="n">
-        <v>13.0810308456421</v>
+        <v>13.0810317993164</v>
       </c>
       <c r="H805" t="n">
         <v>88</v>
@@ -23743,7 +23743,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>13.0400238037109</v>
+        <v>13.0400247573853</v>
       </c>
       <c r="H806" t="n">
         <v>1344</v>
@@ -23830,7 +23830,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G809" t="n">
-        <v>12.7939882278442</v>
+        <v>12.7939872741699</v>
       </c>
       <c r="H809" t="n">
         <v>330</v>
@@ -23859,7 +23859,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G810" t="n">
-        <v>12.5889549255371</v>
+        <v>12.5889558792114</v>
       </c>
       <c r="H810" t="n">
         <v>4421</v>
@@ -23917,7 +23917,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>12.7529802322388</v>
+        <v>12.7529821395874</v>
       </c>
       <c r="H812" t="n">
         <v>350</v>
@@ -23946,7 +23946,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>12.6299610137939</v>
+        <v>12.6299600601196</v>
       </c>
       <c r="H813" t="n">
         <v>510</v>
@@ -23975,7 +23975,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G814" t="n">
-        <v>12.6299610137939</v>
+        <v>12.6299600601196</v>
       </c>
       <c r="H814" t="n">
         <v>0</v>
@@ -24033,7 +24033,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G816" t="n">
-        <v>12.5889549255371</v>
+        <v>12.5889558792114</v>
       </c>
       <c r="H816" t="n">
         <v>288</v>
@@ -24120,7 +24120,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G819" t="n">
-        <v>12.8349933624268</v>
+        <v>12.8349924087524</v>
       </c>
       <c r="H819" t="n">
         <v>460</v>
@@ -24149,7 +24149,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G820" t="n">
-        <v>12.8349933624268</v>
+        <v>12.8349924087524</v>
       </c>
       <c r="H820" t="n">
         <v>925</v>
@@ -24178,7 +24178,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>12.8349933624268</v>
+        <v>12.8349924087524</v>
       </c>
       <c r="H821" t="n">
         <v>0</v>
@@ -24207,7 +24207,7 @@
         <v>15.75</v>
       </c>
       <c r="G822" t="n">
-        <v>12.9170064926147</v>
+        <v>12.9170055389404</v>
       </c>
       <c r="H822" t="n">
         <v>30</v>
@@ -24265,7 +24265,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>12.8349933624268</v>
+        <v>12.8349924087524</v>
       </c>
       <c r="H824" t="n">
         <v>378</v>
@@ -24323,7 +24323,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G826" t="n">
-        <v>12.5889549255371</v>
+        <v>12.5889558792114</v>
       </c>
       <c r="H826" t="n">
         <v>7640</v>
@@ -24352,7 +24352,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>12.6299610137939</v>
+        <v>12.6299600601196</v>
       </c>
       <c r="H827" t="n">
         <v>15</v>
@@ -24381,7 +24381,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G828" t="n">
-        <v>12.5479488372803</v>
+        <v>12.5479497909546</v>
       </c>
       <c r="H828" t="n">
         <v>182</v>
@@ -24410,7 +24410,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>12.6709661483765</v>
+        <v>12.6709671020508</v>
       </c>
       <c r="H829" t="n">
         <v>2591</v>
@@ -24468,7 +24468,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>12.9580125808716</v>
+        <v>12.9580135345459</v>
       </c>
       <c r="H831" t="n">
         <v>423</v>
@@ -24497,7 +24497,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>12.8349933624268</v>
+        <v>12.8349924087524</v>
       </c>
       <c r="H832" t="n">
         <v>2211</v>
@@ -24526,7 +24526,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G833" t="n">
-        <v>12.9580125808716</v>
+        <v>12.9580135345459</v>
       </c>
       <c r="H833" t="n">
         <v>25</v>
@@ -24555,7 +24555,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G834" t="n">
-        <v>13.0810308456421</v>
+        <v>13.0810317993164</v>
       </c>
       <c r="H834" t="n">
         <v>916</v>
@@ -24584,7 +24584,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>13.0400238037109</v>
+        <v>13.0400247573853</v>
       </c>
       <c r="H835" t="n">
         <v>4585</v>
@@ -24613,7 +24613,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G836" t="n">
-        <v>13.2040519714355</v>
+        <v>13.2040510177612</v>
       </c>
       <c r="H836" t="n">
         <v>6194</v>
@@ -24758,7 +24758,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G841" t="n">
-        <v>13.4910974502563</v>
+        <v>13.4910955429077</v>
       </c>
       <c r="H841" t="n">
         <v>40</v>
@@ -24874,7 +24874,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>13.6961278915405</v>
+        <v>13.6961269378662</v>
       </c>
       <c r="H845" t="n">
         <v>706</v>
@@ -24903,7 +24903,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>13.5731086730957</v>
+        <v>13.5731077194214</v>
       </c>
       <c r="H846" t="n">
         <v>332</v>
@@ -24961,7 +24961,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G848" t="n">
-        <v>12.5889549255371</v>
+        <v>12.5889558792114</v>
       </c>
       <c r="H848" t="n">
         <v>2843</v>
@@ -24990,7 +24990,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G849" t="n">
-        <v>12.6709661483765</v>
+        <v>12.6709671020508</v>
       </c>
       <c r="H849" t="n">
         <v>1517</v>
@@ -25019,7 +25019,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G850" t="n">
-        <v>12.7939882278442</v>
+        <v>12.7939872741699</v>
       </c>
       <c r="H850" t="n">
         <v>2758</v>
@@ -25077,7 +25077,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>12.6299610137939</v>
+        <v>12.6299600601196</v>
       </c>
       <c r="H852" t="n">
         <v>7688</v>
@@ -25135,7 +25135,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G854" t="n">
-        <v>13.6961278915405</v>
+        <v>13.6961269378662</v>
       </c>
       <c r="H854" t="n">
         <v>4189</v>
@@ -25193,7 +25193,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G856" t="n">
-        <v>14.2292098999023</v>
+        <v>14.229211807251</v>
       </c>
       <c r="H856" t="n">
         <v>4704</v>
@@ -25222,7 +25222,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>14.4342412948608</v>
+        <v>14.4342422485352</v>
       </c>
       <c r="H857" t="n">
         <v>643</v>
@@ -25251,7 +25251,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>14.2702150344849</v>
+        <v>14.2702159881592</v>
       </c>
       <c r="H858" t="n">
         <v>1566</v>
@@ -25280,7 +25280,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G859" t="n">
-        <v>14.5162553787231</v>
+        <v>14.5162563323975</v>
       </c>
       <c r="H859" t="n">
         <v>708</v>
@@ -25367,7 +25367,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G862" t="n">
-        <v>14.5982666015625</v>
+        <v>14.5982685089111</v>
       </c>
       <c r="H862" t="n">
         <v>2852</v>
@@ -25396,7 +25396,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G863" t="n">
-        <v>14.4342412948608</v>
+        <v>14.4342422485352</v>
       </c>
       <c r="H863" t="n">
         <v>4831</v>
@@ -25454,7 +25454,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G865" t="n">
-        <v>14.5982666015625</v>
+        <v>14.5982685089111</v>
       </c>
       <c r="H865" t="n">
         <v>2262</v>
@@ -25541,7 +25541,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>14.1061906814575</v>
+        <v>14.1061916351318</v>
       </c>
       <c r="H868" t="n">
         <v>2660</v>
@@ -25570,7 +25570,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>14.2292098999023</v>
+        <v>14.229211807251</v>
       </c>
       <c r="H869" t="n">
         <v>1134</v>
@@ -25599,7 +25599,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>14.0651826858521</v>
+        <v>14.0651836395264</v>
       </c>
       <c r="H870" t="n">
         <v>1363</v>
@@ -25628,7 +25628,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G871" t="n">
-        <v>14.0651826858521</v>
+        <v>14.0651836395264</v>
       </c>
       <c r="H871" t="n">
         <v>1378</v>
@@ -25657,7 +25657,7 @@
         <v>17</v>
       </c>
       <c r="G872" t="n">
-        <v>13.9421644210815</v>
+        <v>13.9421653747559</v>
       </c>
       <c r="H872" t="n">
         <v>2985</v>
@@ -25686,7 +25686,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G873" t="n">
-        <v>13.7781400680542</v>
+        <v>13.7781391143799</v>
       </c>
       <c r="H873" t="n">
         <v>820</v>
@@ -25744,7 +25744,7 @@
         <v>16.75</v>
       </c>
       <c r="G875" t="n">
-        <v>13.7371320724487</v>
+        <v>13.7371339797974</v>
       </c>
       <c r="H875" t="n">
         <v>686</v>
@@ -25802,7 +25802,7 @@
         <v>17</v>
       </c>
       <c r="G877" t="n">
-        <v>13.9421644210815</v>
+        <v>13.9421653747559</v>
       </c>
       <c r="H877" t="n">
         <v>2600</v>
@@ -25831,7 +25831,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G878" t="n">
-        <v>13.9831705093384</v>
+        <v>13.9831714630127</v>
       </c>
       <c r="H878" t="n">
         <v>1511</v>
@@ -25860,7 +25860,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G879" t="n">
-        <v>13.9831705093384</v>
+        <v>13.9831714630127</v>
       </c>
       <c r="H879" t="n">
         <v>500</v>
@@ -25918,7 +25918,7 @@
         <v>17</v>
       </c>
       <c r="G881" t="n">
-        <v>13.9421644210815</v>
+        <v>13.9421653747559</v>
       </c>
       <c r="H881" t="n">
         <v>1780</v>
@@ -25947,7 +25947,7 @@
         <v>17</v>
       </c>
       <c r="G882" t="n">
-        <v>13.9421644210815</v>
+        <v>13.9421653747559</v>
       </c>
       <c r="H882" t="n">
         <v>1743</v>
@@ -25976,7 +25976,7 @@
         <v>17</v>
       </c>
       <c r="G883" t="n">
-        <v>13.9421644210815</v>
+        <v>13.9421653747559</v>
       </c>
       <c r="H883" t="n">
         <v>6738</v>
@@ -26005,7 +26005,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G884" t="n">
-        <v>14.4342412948608</v>
+        <v>14.4342422485352</v>
       </c>
       <c r="H884" t="n">
         <v>4887</v>
@@ -26034,7 +26034,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G885" t="n">
-        <v>14.5162553787231</v>
+        <v>14.5162563323975</v>
       </c>
       <c r="H885" t="n">
         <v>1090</v>
@@ -26063,7 +26063,7 @@
         <v>17.75</v>
       </c>
       <c r="G886" t="n">
-        <v>14.5572595596313</v>
+        <v>14.55726146698</v>
       </c>
       <c r="H886" t="n">
         <v>4345</v>
@@ -26092,7 +26092,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>14.5982666015625</v>
+        <v>14.5982685089111</v>
       </c>
       <c r="H887" t="n">
         <v>4610</v>
@@ -26150,7 +26150,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>14.9263181686401</v>
+        <v>14.9263200759888</v>
       </c>
       <c r="H889" t="n">
         <v>2167</v>
@@ -26179,7 +26179,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G890" t="n">
-        <v>15.3363828659058</v>
+        <v>15.3363847732544</v>
       </c>
       <c r="H890" t="n">
         <v>11840</v>
@@ -26208,7 +26208,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G891" t="n">
-        <v>15.6644344329834</v>
+        <v>15.6644334793091</v>
       </c>
       <c r="H891" t="n">
         <v>7465</v>
@@ -26295,7 +26295,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>16.484561920166</v>
+        <v>16.4845581054688</v>
       </c>
       <c r="H894" t="n">
         <v>3196</v>
@@ -26324,7 +26324,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G895" t="n">
-        <v>17.4687118530273</v>
+        <v>17.4687099456787</v>
       </c>
       <c r="H895" t="n">
         <v>8208</v>
@@ -26353,7 +26353,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>17.4687118530273</v>
+        <v>17.4687099456787</v>
       </c>
       <c r="H896" t="n">
         <v>7593</v>
@@ -26498,7 +26498,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G901" t="n">
-        <v>18.1248168945312</v>
+        <v>18.1248149871826</v>
       </c>
       <c r="H901" t="n">
         <v>6694</v>
@@ -26556,7 +26556,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G903" t="n">
-        <v>18.5348796844482</v>
+        <v>18.5348777770996</v>
       </c>
       <c r="H903" t="n">
         <v>4688</v>
@@ -26614,7 +26614,7 @@
         <v>21.5</v>
       </c>
       <c r="G905" t="n">
-        <v>17.6327419281006</v>
+        <v>17.632740020752</v>
       </c>
       <c r="H905" t="n">
         <v>2009</v>
@@ -26672,7 +26672,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G907" t="n">
-        <v>18.2888412475586</v>
+        <v>18.28883934021</v>
       </c>
       <c r="H907" t="n">
         <v>6235</v>
@@ -27020,7 +27020,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G919" t="n">
-        <v>18.5348796844482</v>
+        <v>18.5348777770996</v>
       </c>
       <c r="H919" t="n">
         <v>2901</v>
@@ -27136,7 +27136,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G923" t="n">
-        <v>18.9449443817139</v>
+        <v>18.9449405670166</v>
       </c>
       <c r="H923" t="n">
         <v>1918</v>
@@ -27165,7 +27165,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G924" t="n">
-        <v>18.9449443817139</v>
+        <v>18.9449405670166</v>
       </c>
       <c r="H924" t="n">
         <v>5571</v>
@@ -27194,7 +27194,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>18.9449443817139</v>
+        <v>18.9449405670166</v>
       </c>
       <c r="H925" t="n">
         <v>3393</v>
@@ -27223,7 +27223,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>18.9449443817139</v>
+        <v>18.9449405670166</v>
       </c>
       <c r="H926" t="n">
         <v>3955</v>
@@ -27252,7 +27252,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G927" t="n">
-        <v>19.0269565582275</v>
+        <v>19.0269546508789</v>
       </c>
       <c r="H927" t="n">
         <v>2862</v>
@@ -27281,7 +27281,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G928" t="n">
-        <v>19.1089687347412</v>
+        <v>19.1089668273926</v>
       </c>
       <c r="H928" t="n">
         <v>3523</v>
@@ -27310,7 +27310,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G929" t="n">
-        <v>19.1089687347412</v>
+        <v>19.1089668273926</v>
       </c>
       <c r="H929" t="n">
         <v>788</v>
@@ -27339,7 +27339,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G930" t="n">
-        <v>19.1909790039062</v>
+        <v>19.1909809112549</v>
       </c>
       <c r="H930" t="n">
         <v>1878</v>
@@ -27368,7 +27368,7 @@
         <v>23.5</v>
       </c>
       <c r="G931" t="n">
-        <v>19.2729911804199</v>
+        <v>19.2729930877686</v>
       </c>
       <c r="H931" t="n">
         <v>121</v>
@@ -27629,7 +27629,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G940" t="n">
-        <v>20.5851955413818</v>
+        <v>20.5851974487305</v>
       </c>
       <c r="H940" t="n">
         <v>740</v>
@@ -27861,7 +27861,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G948" t="n">
-        <v>20.5851955413818</v>
+        <v>20.5851974487305</v>
       </c>
       <c r="H948" t="n">
         <v>3616</v>
@@ -27919,7 +27919,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>21.4053230285645</v>
+        <v>21.4053268432617</v>
       </c>
       <c r="H950" t="n">
         <v>1757</v>
@@ -27977,7 +27977,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>20.5851955413818</v>
+        <v>20.5851974487305</v>
       </c>
       <c r="H952" t="n">
         <v>2774</v>
@@ -28064,7 +28064,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>20.8312358856201</v>
+        <v>20.8312377929688</v>
       </c>
       <c r="H955" t="n">
         <v>1664</v>
@@ -28209,7 +28209,7 @@
         <v>24.5</v>
       </c>
       <c r="G960" t="n">
-        <v>20.0931205749512</v>
+        <v>20.0931186676025</v>
       </c>
       <c r="H960" t="n">
         <v>395</v>
@@ -28238,7 +28238,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G961" t="n">
-        <v>20.5851955413818</v>
+        <v>20.5851974487305</v>
       </c>
       <c r="H961" t="n">
         <v>5322</v>
@@ -28267,7 +28267,7 @@
         <v>24.5</v>
       </c>
       <c r="G962" t="n">
-        <v>20.0931205749512</v>
+        <v>20.0931186676025</v>
       </c>
       <c r="H962" t="n">
         <v>476</v>
@@ -28296,7 +28296,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>20.7492218017578</v>
+        <v>20.7492256164551</v>
       </c>
       <c r="H963" t="n">
         <v>2984</v>
@@ -28325,7 +28325,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G964" t="n">
-        <v>20.5851955413818</v>
+        <v>20.5851974487305</v>
       </c>
       <c r="H964" t="n">
         <v>789</v>
@@ -28412,7 +28412,7 @@
         <v>24.5</v>
       </c>
       <c r="G967" t="n">
-        <v>20.0931205749512</v>
+        <v>20.0931186676025</v>
       </c>
       <c r="H967" t="n">
         <v>634</v>
@@ -28441,7 +28441,7 @@
         <v>24.5</v>
       </c>
       <c r="G968" t="n">
-        <v>20.0931205749512</v>
+        <v>20.0931186676025</v>
       </c>
       <c r="H968" t="n">
         <v>1198</v>
@@ -28673,7 +28673,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G976" t="n">
-        <v>20.5851955413818</v>
+        <v>20.5851974487305</v>
       </c>
       <c r="H976" t="n">
         <v>471</v>
@@ -28818,7 +28818,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G981" t="n">
-        <v>20.7492218017578</v>
+        <v>20.7492256164551</v>
       </c>
       <c r="H981" t="n">
         <v>239</v>
@@ -28934,7 +28934,7 @@
         <v>25.5</v>
       </c>
       <c r="G985" t="n">
-        <v>20.9132461547852</v>
+        <v>20.9132480621338</v>
       </c>
       <c r="H985" t="n">
         <v>2778</v>
@@ -28963,7 +28963,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G986" t="n">
-        <v>20.8312358856201</v>
+        <v>20.8312377929688</v>
       </c>
       <c r="H986" t="n">
         <v>829</v>
@@ -28992,7 +28992,7 @@
         <v>25.5</v>
       </c>
       <c r="G987" t="n">
-        <v>20.9132461547852</v>
+        <v>20.9132480621338</v>
       </c>
       <c r="H987" t="n">
         <v>4766</v>
@@ -29021,7 +29021,7 @@
         <v>25.5</v>
       </c>
       <c r="G988" t="n">
-        <v>20.9132461547852</v>
+        <v>20.9132480621338</v>
       </c>
       <c r="H988" t="n">
         <v>432</v>
@@ -29137,7 +29137,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G992" t="n">
-        <v>19.5190315246582</v>
+        <v>19.5190296173096</v>
       </c>
       <c r="H992" t="n">
         <v>9374</v>
@@ -29166,7 +29166,7 @@
         <v>23.5</v>
       </c>
       <c r="G993" t="n">
-        <v>19.2729911804199</v>
+        <v>19.2729930877686</v>
       </c>
       <c r="H993" t="n">
         <v>6581</v>
@@ -29253,7 +29253,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G996" t="n">
-        <v>19.6010437011719</v>
+        <v>19.6010417938232</v>
       </c>
       <c r="H996" t="n">
         <v>2860</v>
@@ -29282,7 +29282,7 @@
         <v>23.5</v>
       </c>
       <c r="G997" t="n">
-        <v>19.2729911804199</v>
+        <v>19.2729930877686</v>
       </c>
       <c r="H997" t="n">
         <v>5417</v>
@@ -29311,7 +29311,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G998" t="n">
-        <v>19.0269565582275</v>
+        <v>19.0269546508789</v>
       </c>
       <c r="H998" t="n">
         <v>6069</v>
@@ -29340,7 +29340,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G999" t="n">
-        <v>18.5348796844482</v>
+        <v>18.5348777770996</v>
       </c>
       <c r="H999" t="n">
         <v>6597</v>
@@ -29369,7 +29369,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>18.9449443817139</v>
+        <v>18.9449405670166</v>
       </c>
       <c r="H1000" t="n">
         <v>8055</v>
@@ -29398,7 +29398,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1001" t="n">
-        <v>19.1089687347412</v>
+        <v>19.1089668273926</v>
       </c>
       <c r="H1001" t="n">
         <v>1475</v>
@@ -29427,7 +29427,7 @@
         <v>23.5</v>
       </c>
       <c r="G1002" t="n">
-        <v>19.2729911804199</v>
+        <v>19.2729930877686</v>
       </c>
       <c r="H1002" t="n">
         <v>4699</v>
@@ -29456,7 +29456,7 @@
         <v>23.5</v>
       </c>
       <c r="G1003" t="n">
-        <v>19.2729911804199</v>
+        <v>19.2729930877686</v>
       </c>
       <c r="H1003" t="n">
         <v>1096</v>
@@ -29601,7 +29601,7 @@
         <v>25.5</v>
       </c>
       <c r="G1008" t="n">
-        <v>20.9132461547852</v>
+        <v>20.9132480621338</v>
       </c>
       <c r="H1008" t="n">
         <v>2349</v>
@@ -29630,7 +29630,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1009" t="n">
-        <v>20.5851955413818</v>
+        <v>20.5851974487305</v>
       </c>
       <c r="H1009" t="n">
         <v>1486</v>
@@ -29659,7 +29659,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1010" t="n">
-        <v>20.8312358856201</v>
+        <v>20.8312377929688</v>
       </c>
       <c r="H1010" t="n">
         <v>1592</v>
@@ -29717,7 +29717,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>20.7492218017578</v>
+        <v>20.7492256164551</v>
       </c>
       <c r="H1012" t="n">
         <v>2078</v>
@@ -29746,7 +29746,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1013" t="n">
-        <v>20.8312358856201</v>
+        <v>20.8312377929688</v>
       </c>
       <c r="H1013" t="n">
         <v>700</v>
@@ -29775,7 +29775,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>20.5851955413818</v>
+        <v>20.5851974487305</v>
       </c>
       <c r="H1014" t="n">
         <v>2983</v>
@@ -29862,7 +29862,7 @@
         <v>25.5</v>
       </c>
       <c r="G1017" t="n">
-        <v>20.9132461547852</v>
+        <v>20.9132480621338</v>
       </c>
       <c r="H1017" t="n">
         <v>1668</v>
@@ -29920,7 +29920,7 @@
         <v>25.5</v>
       </c>
       <c r="G1019" t="n">
-        <v>20.9132461547852</v>
+        <v>20.9132480621338</v>
       </c>
       <c r="H1019" t="n">
         <v>316</v>
@@ -30152,7 +30152,7 @@
         <v>25.5</v>
       </c>
       <c r="G1027" t="n">
-        <v>21.3451347351074</v>
+        <v>21.3451328277588</v>
       </c>
       <c r="H1027" t="n">
         <v>1679</v>
@@ -30181,7 +30181,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1028" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1028" t="n">
         <v>292</v>
@@ -30268,7 +30268,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1031" t="n">
-        <v>21.2614288330078</v>
+        <v>21.2614269256592</v>
       </c>
       <c r="H1031" t="n">
         <v>641</v>
@@ -30297,7 +30297,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1032" t="n">
-        <v>21.6799602508545</v>
+        <v>21.6799583435059</v>
       </c>
       <c r="H1032" t="n">
         <v>2625</v>
@@ -30413,7 +30413,7 @@
         <v>26</v>
       </c>
       <c r="G1036" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1036" t="n">
         <v>1000</v>
@@ -30500,7 +30500,7 @@
         <v>26</v>
       </c>
       <c r="G1039" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1039" t="n">
         <v>6025</v>
@@ -30558,7 +30558,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1041" t="n">
-        <v>22.2659072875977</v>
+        <v>22.265905380249</v>
       </c>
       <c r="H1041" t="n">
         <v>6178</v>
@@ -30587,7 +30587,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1042" t="n">
-        <v>22.2659072875977</v>
+        <v>22.265905380249</v>
       </c>
       <c r="H1042" t="n">
         <v>4281</v>
@@ -30616,7 +30616,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1043" t="n">
-        <v>22.2659072875977</v>
+        <v>22.265905380249</v>
       </c>
       <c r="H1043" t="n">
         <v>2120</v>
@@ -30645,7 +30645,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1044" t="n">
-        <v>22.3496131896973</v>
+        <v>22.3496112823486</v>
       </c>
       <c r="H1044" t="n">
         <v>2171</v>
@@ -30674,7 +30674,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1045" t="n">
-        <v>22.2659072875977</v>
+        <v>22.265905380249</v>
       </c>
       <c r="H1045" t="n">
         <v>2443</v>
@@ -30703,7 +30703,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1046" t="n">
-        <v>22.3496131896973</v>
+        <v>22.3496112823486</v>
       </c>
       <c r="H1046" t="n">
         <v>1356</v>
@@ -30732,7 +30732,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>22.0984916687012</v>
+        <v>22.0984897613525</v>
       </c>
       <c r="H1047" t="n">
         <v>1862</v>
@@ -30761,7 +30761,7 @@
         <v>26</v>
       </c>
       <c r="G1048" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1048" t="n">
         <v>2403</v>
@@ -30790,7 +30790,7 @@
         <v>26</v>
       </c>
       <c r="G1049" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1049" t="n">
         <v>162</v>
@@ -30848,7 +30848,7 @@
         <v>26</v>
       </c>
       <c r="G1051" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1051" t="n">
         <v>460</v>
@@ -30935,7 +30935,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1054" t="n">
-        <v>21.0940170288086</v>
+        <v>21.09401512146</v>
       </c>
       <c r="H1054" t="n">
         <v>1014</v>
@@ -30964,7 +30964,7 @@
         <v>24</v>
       </c>
       <c r="G1055" t="n">
-        <v>20.0895385742188</v>
+        <v>20.0895366668701</v>
       </c>
       <c r="H1055" t="n">
         <v>6882</v>
@@ -30993,7 +30993,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1056" t="n">
-        <v>20.256950378418</v>
+        <v>20.2569522857666</v>
       </c>
       <c r="H1056" t="n">
         <v>597</v>
@@ -31022,7 +31022,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1057" t="n">
-        <v>19.9221267700195</v>
+        <v>19.9221248626709</v>
       </c>
       <c r="H1057" t="n">
         <v>914</v>
@@ -31080,7 +31080,7 @@
         <v>24</v>
       </c>
       <c r="G1059" t="n">
-        <v>20.0895385742188</v>
+        <v>20.0895366668701</v>
       </c>
       <c r="H1059" t="n">
         <v>657</v>
@@ -31138,7 +31138,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1061" t="n">
-        <v>19.9221267700195</v>
+        <v>19.9221248626709</v>
       </c>
       <c r="H1061" t="n">
         <v>759</v>
@@ -31167,7 +31167,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1062" t="n">
-        <v>19.9221267700195</v>
+        <v>19.9221248626709</v>
       </c>
       <c r="H1062" t="n">
         <v>422</v>
@@ -31196,7 +31196,7 @@
         <v>24</v>
       </c>
       <c r="G1063" t="n">
-        <v>20.0895385742188</v>
+        <v>20.0895366668701</v>
       </c>
       <c r="H1063" t="n">
         <v>293</v>
@@ -31312,7 +31312,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1067" t="n">
-        <v>21.2614288330078</v>
+        <v>21.2614269256592</v>
       </c>
       <c r="H1067" t="n">
         <v>1938</v>
@@ -31399,7 +31399,7 @@
         <v>26</v>
       </c>
       <c r="G1070" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1070" t="n">
         <v>524</v>
@@ -31573,7 +31573,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1076" t="n">
-        <v>20.5917778015137</v>
+        <v>20.591775894165</v>
       </c>
       <c r="H1076" t="n">
         <v>5487</v>
@@ -31602,7 +31602,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1077" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1077" t="n">
         <v>3289</v>
@@ -31776,7 +31776,7 @@
         <v>25.5</v>
       </c>
       <c r="G1083" t="n">
-        <v>21.3451347351074</v>
+        <v>21.3451328277588</v>
       </c>
       <c r="H1083" t="n">
         <v>975</v>
@@ -31834,7 +31834,7 @@
         <v>25.5</v>
       </c>
       <c r="G1085" t="n">
-        <v>21.3451347351074</v>
+        <v>21.3451328277588</v>
       </c>
       <c r="H1085" t="n">
         <v>5249</v>
@@ -31863,7 +31863,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1086" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1086" t="n">
         <v>1486</v>
@@ -31892,7 +31892,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1087" t="n">
         <v>0</v>
@@ -31921,7 +31921,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1088" t="n">
-        <v>21.2614288330078</v>
+        <v>21.2614269256592</v>
       </c>
       <c r="H1088" t="n">
         <v>19553</v>
@@ -31979,7 +31979,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1090" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1090" t="n">
         <v>10682</v>
@@ -32008,7 +32008,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>21.6799602508545</v>
+        <v>21.6799583435059</v>
       </c>
       <c r="H1091" t="n">
         <v>641</v>
@@ -32037,7 +32037,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1092" t="n">
-        <v>21.6799602508545</v>
+        <v>21.6799583435059</v>
       </c>
       <c r="H1092" t="n">
         <v>239</v>
@@ -32066,7 +32066,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1093" t="n">
-        <v>21.6799602508545</v>
+        <v>21.6799583435059</v>
       </c>
       <c r="H1093" t="n">
         <v>120</v>
@@ -32095,7 +32095,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1094" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1094" t="n">
         <v>1559</v>
@@ -32124,7 +32124,7 @@
         <v>26</v>
       </c>
       <c r="G1095" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1095" t="n">
         <v>1654</v>
@@ -32153,7 +32153,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1096" t="n">
-        <v>21.6799602508545</v>
+        <v>21.6799583435059</v>
       </c>
       <c r="H1096" t="n">
         <v>346</v>
@@ -32182,7 +32182,7 @@
         <v>26</v>
       </c>
       <c r="G1097" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1097" t="n">
         <v>625</v>
@@ -32211,7 +32211,7 @@
         <v>25.5</v>
       </c>
       <c r="G1098" t="n">
-        <v>21.3451347351074</v>
+        <v>21.3451328277588</v>
       </c>
       <c r="H1098" t="n">
         <v>1242</v>
@@ -32240,7 +32240,7 @@
         <v>25.5</v>
       </c>
       <c r="G1099" t="n">
-        <v>21.3451347351074</v>
+        <v>21.3451328277588</v>
       </c>
       <c r="H1099" t="n">
         <v>0</v>
@@ -32269,7 +32269,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1100" t="n">
-        <v>21.6799602508545</v>
+        <v>21.6799583435059</v>
       </c>
       <c r="H1100" t="n">
         <v>3623</v>
@@ -32298,7 +32298,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1101" t="n">
-        <v>22.2659072875977</v>
+        <v>22.265905380249</v>
       </c>
       <c r="H1101" t="n">
         <v>37599</v>
@@ -32327,7 +32327,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1102" t="n">
-        <v>22.3496131896973</v>
+        <v>22.3496112823486</v>
       </c>
       <c r="H1102" t="n">
         <v>6172</v>
@@ -32356,7 +32356,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1103" t="n">
-        <v>22.7681446075439</v>
+        <v>22.7681427001953</v>
       </c>
       <c r="H1103" t="n">
         <v>4985</v>
@@ -32443,7 +32443,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1106" t="n">
-        <v>22.2659072875977</v>
+        <v>22.265905380249</v>
       </c>
       <c r="H1106" t="n">
         <v>3926</v>
@@ -32530,7 +32530,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1109" t="n">
-        <v>22.0984916687012</v>
+        <v>22.0984897613525</v>
       </c>
       <c r="H1109" t="n">
         <v>1523</v>
@@ -32617,7 +32617,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1112" t="n">
-        <v>22.0984916687012</v>
+        <v>22.0984897613525</v>
       </c>
       <c r="H1112" t="n">
         <v>4368</v>
@@ -32675,7 +32675,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1114" t="n">
-        <v>22.0147857666016</v>
+        <v>22.0147838592529</v>
       </c>
       <c r="H1114" t="n">
         <v>1144</v>
@@ -32704,7 +32704,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1115" t="n">
-        <v>22.2659072875977</v>
+        <v>22.265905380249</v>
       </c>
       <c r="H1115" t="n">
         <v>1146</v>
@@ -32733,7 +32733,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1116" t="n">
-        <v>22.2659072875977</v>
+        <v>22.265905380249</v>
       </c>
       <c r="H1116" t="n">
         <v>750</v>
@@ -32762,7 +32762,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1117" t="n">
-        <v>22.2659072875977</v>
+        <v>22.265905380249</v>
       </c>
       <c r="H1117" t="n">
         <v>292</v>
@@ -32849,7 +32849,7 @@
         <v>27</v>
       </c>
       <c r="G1120" t="n">
-        <v>22.6007289886475</v>
+        <v>22.6007308959961</v>
       </c>
       <c r="H1120" t="n">
         <v>4240</v>
@@ -32907,7 +32907,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1122" t="n">
-        <v>22.4333171844482</v>
+        <v>22.4333152770996</v>
       </c>
       <c r="H1122" t="n">
         <v>211</v>
@@ -32936,7 +32936,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1123" t="n">
-        <v>22.0984916687012</v>
+        <v>22.0984897613525</v>
       </c>
       <c r="H1123" t="n">
         <v>175</v>
@@ -32965,7 +32965,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1124" t="n">
-        <v>22.2659072875977</v>
+        <v>22.265905380249</v>
       </c>
       <c r="H1124" t="n">
         <v>852</v>
@@ -32994,7 +32994,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1125" t="n">
-        <v>22.2659072875977</v>
+        <v>22.265905380249</v>
       </c>
       <c r="H1125" t="n">
         <v>0</v>
@@ -33023,7 +33023,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1126" t="n">
-        <v>22.3496131896973</v>
+        <v>22.3496112823486</v>
       </c>
       <c r="H1126" t="n">
         <v>1040</v>
@@ -33052,7 +33052,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>22.4333171844482</v>
+        <v>22.4333152770996</v>
       </c>
       <c r="H1127" t="n">
         <v>670</v>
@@ -33139,7 +33139,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1130" t="n">
-        <v>22.0147857666016</v>
+        <v>22.0147838592529</v>
       </c>
       <c r="H1130" t="n">
         <v>1214</v>
@@ -33168,7 +33168,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>22.4333171844482</v>
+        <v>22.4333152770996</v>
       </c>
       <c r="H1131" t="n">
         <v>1670</v>
@@ -33255,7 +33255,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1134" t="n">
-        <v>23.186674118042</v>
+        <v>23.1866760253906</v>
       </c>
       <c r="H1134" t="n">
         <v>1544</v>
@@ -33487,7 +33487,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1142" t="n">
-        <v>22.4333171844482</v>
+        <v>22.4333152770996</v>
       </c>
       <c r="H1142" t="n">
         <v>513</v>
@@ -33574,7 +33574,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1145" t="n">
-        <v>22.7681446075439</v>
+        <v>22.7681427001953</v>
       </c>
       <c r="H1145" t="n">
         <v>1171</v>
@@ -33603,7 +33603,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>22.4333171844482</v>
+        <v>22.4333152770996</v>
       </c>
       <c r="H1146" t="n">
         <v>1275</v>
@@ -33632,7 +33632,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1147" t="n">
-        <v>22.3496131896973</v>
+        <v>22.3496112823486</v>
       </c>
       <c r="H1147" t="n">
         <v>1882</v>
@@ -33661,7 +33661,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1148" t="n">
-        <v>22.0147857666016</v>
+        <v>22.0147838592529</v>
       </c>
       <c r="H1148" t="n">
         <v>2013</v>
@@ -33690,7 +33690,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>22.3496131896973</v>
+        <v>22.3496112823486</v>
       </c>
       <c r="H1149" t="n">
         <v>1168</v>
@@ -33748,7 +33748,7 @@
         <v>26</v>
       </c>
       <c r="G1151" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1151" t="n">
         <v>2199</v>
@@ -33777,7 +33777,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>22.0984916687012</v>
+        <v>22.0984897613525</v>
       </c>
       <c r="H1152" t="n">
         <v>901</v>
@@ -33864,7 +33864,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1155" t="n">
-        <v>22.0984916687012</v>
+        <v>22.0984897613525</v>
       </c>
       <c r="H1155" t="n">
         <v>1742</v>
@@ -33922,7 +33922,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1157" t="n">
-        <v>22.0147857666016</v>
+        <v>22.0147838592529</v>
       </c>
       <c r="H1157" t="n">
         <v>447</v>
@@ -33951,7 +33951,7 @@
         <v>26</v>
       </c>
       <c r="G1158" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1158" t="n">
         <v>2779</v>
@@ -34125,7 +34125,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1164" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1164" t="n">
         <v>3498</v>
@@ -34154,7 +34154,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1165" t="n">
-        <v>21.0940170288086</v>
+        <v>21.09401512146</v>
       </c>
       <c r="H1165" t="n">
         <v>2756</v>
@@ -34183,7 +34183,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1166" t="n">
-        <v>21.0940170288086</v>
+        <v>21.09401512146</v>
       </c>
       <c r="H1166" t="n">
         <v>872</v>
@@ -34241,7 +34241,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1168" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1168" t="n">
         <v>4570</v>
@@ -34299,7 +34299,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>21.2614288330078</v>
+        <v>21.2614269256592</v>
       </c>
       <c r="H1170" t="n">
         <v>992</v>
@@ -34386,7 +34386,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1173" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1173" t="n">
         <v>1038</v>
@@ -34415,7 +34415,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.4333171844482</v>
+        <v>22.4333152770996</v>
       </c>
       <c r="H1174" t="n">
         <v>6007</v>
@@ -34444,7 +34444,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1175" t="n">
-        <v>22.2659072875977</v>
+        <v>22.265905380249</v>
       </c>
       <c r="H1175" t="n">
         <v>253</v>
@@ -34473,7 +34473,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>22.3496131896973</v>
+        <v>22.3496112823486</v>
       </c>
       <c r="H1176" t="n">
         <v>1444</v>
@@ -34502,7 +34502,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>22.0147857666016</v>
+        <v>22.0147838592529</v>
       </c>
       <c r="H1177" t="n">
         <v>1090</v>
@@ -34531,7 +34531,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1178" t="n">
-        <v>22.0147857666016</v>
+        <v>22.0147838592529</v>
       </c>
       <c r="H1178" t="n">
         <v>0</v>
@@ -34560,7 +34560,7 @@
         <v>26</v>
       </c>
       <c r="G1179" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1179" t="n">
         <v>991</v>
@@ -34647,7 +34647,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1182" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1182" t="n">
         <v>1737</v>
@@ -34734,7 +34734,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1185" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1185" t="n">
         <v>403</v>
@@ -34763,7 +34763,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1186" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1186" t="n">
         <v>459</v>
@@ -34879,7 +34879,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1190" t="n">
-        <v>20.5917778015137</v>
+        <v>20.591775894165</v>
       </c>
       <c r="H1190" t="n">
         <v>1003</v>
@@ -34908,7 +34908,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1191" t="n">
-        <v>20.8428974151611</v>
+        <v>20.8428955078125</v>
       </c>
       <c r="H1191" t="n">
         <v>284</v>
@@ -34937,7 +34937,7 @@
         <v>25</v>
       </c>
       <c r="G1192" t="n">
-        <v>20.9266033172607</v>
+        <v>20.9265995025635</v>
       </c>
       <c r="H1192" t="n">
         <v>789</v>
@@ -34966,7 +34966,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1193" t="n">
-        <v>21.0940170288086</v>
+        <v>21.09401512146</v>
       </c>
       <c r="H1193" t="n">
         <v>226</v>
@@ -34995,7 +34995,7 @@
         <v>25</v>
       </c>
       <c r="G1194" t="n">
-        <v>20.9266033172607</v>
+        <v>20.9265995025635</v>
       </c>
       <c r="H1194" t="n">
         <v>422</v>
@@ -35053,7 +35053,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1196" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1196" t="n">
         <v>1860</v>
@@ -35082,7 +35082,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1197" t="n">
-        <v>22.0147857666016</v>
+        <v>22.0147838592529</v>
       </c>
       <c r="H1197" t="n">
         <v>267</v>
@@ -35111,7 +35111,7 @@
         <v>26</v>
       </c>
       <c r="G1198" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1198" t="n">
         <v>1721</v>
@@ -35140,7 +35140,7 @@
         <v>25.5</v>
       </c>
       <c r="G1199" t="n">
-        <v>21.3451347351074</v>
+        <v>21.3451328277588</v>
       </c>
       <c r="H1199" t="n">
         <v>889</v>
@@ -35227,7 +35227,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1202" t="n">
-        <v>20.8428974151611</v>
+        <v>20.8428955078125</v>
       </c>
       <c r="H1202" t="n">
         <v>998</v>
@@ -35256,7 +35256,7 @@
         <v>25</v>
       </c>
       <c r="G1203" t="n">
-        <v>20.9266033172607</v>
+        <v>20.9265995025635</v>
       </c>
       <c r="H1203" t="n">
         <v>2856</v>
@@ -35285,7 +35285,7 @@
         <v>25</v>
       </c>
       <c r="G1204" t="n">
-        <v>20.9266033172607</v>
+        <v>20.9265995025635</v>
       </c>
       <c r="H1204" t="n">
         <v>0</v>
@@ -35372,7 +35372,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>20.4243640899658</v>
+        <v>20.4243621826172</v>
       </c>
       <c r="H1207" t="n">
         <v>119</v>
@@ -35401,7 +35401,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1208" t="n">
-        <v>20.5917778015137</v>
+        <v>20.591775894165</v>
       </c>
       <c r="H1208" t="n">
         <v>395</v>
@@ -35459,7 +35459,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1210" t="n">
-        <v>20.4243640899658</v>
+        <v>20.4243621826172</v>
       </c>
       <c r="H1210" t="n">
         <v>1635</v>
@@ -35488,7 +35488,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1211" t="n">
-        <v>20.3406562805176</v>
+        <v>20.3406543731689</v>
       </c>
       <c r="H1211" t="n">
         <v>134</v>
@@ -35517,7 +35517,7 @@
         <v>24</v>
       </c>
       <c r="G1212" t="n">
-        <v>20.0895385742188</v>
+        <v>20.0895366668701</v>
       </c>
       <c r="H1212" t="n">
         <v>1734</v>
@@ -35604,7 +35604,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1215" t="n">
-        <v>19.5035934448242</v>
+        <v>19.5035915374756</v>
       </c>
       <c r="H1215" t="n">
         <v>1541</v>
@@ -35633,7 +35633,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1216" t="n">
-        <v>19.5872974395752</v>
+        <v>19.5873012542725</v>
       </c>
       <c r="H1216" t="n">
         <v>2114</v>
@@ -35662,7 +35662,7 @@
         <v>24</v>
       </c>
       <c r="G1217" t="n">
-        <v>20.0895385742188</v>
+        <v>20.0895366668701</v>
       </c>
       <c r="H1217" t="n">
         <v>5601</v>
@@ -35691,7 +35691,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1218" t="n">
-        <v>20.3406562805176</v>
+        <v>20.3406543731689</v>
       </c>
       <c r="H1218" t="n">
         <v>1092</v>
@@ -35720,7 +35720,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>19.5872974395752</v>
+        <v>19.5873012542725</v>
       </c>
       <c r="H1219" t="n">
         <v>1361</v>
@@ -35749,7 +35749,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1220" t="n">
-        <v>18.499116897583</v>
+        <v>18.4991188049316</v>
       </c>
       <c r="H1220" t="n">
         <v>1096</v>
@@ -35923,7 +35923,7 @@
         <v>21</v>
       </c>
       <c r="G1226" t="n">
-        <v>17.5783443450928</v>
+        <v>17.5783462524414</v>
       </c>
       <c r="H1226" t="n">
         <v>3146</v>
@@ -36010,7 +36010,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1229" t="n">
-        <v>18.0805835723877</v>
+        <v>18.0805854797363</v>
       </c>
       <c r="H1229" t="n">
         <v>461</v>
@@ -36039,7 +36039,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>18.0805835723877</v>
+        <v>18.0805854797363</v>
       </c>
       <c r="H1230" t="n">
         <v>322</v>
@@ -36068,7 +36068,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1231" t="n">
-        <v>17.8294658660889</v>
+        <v>17.8294639587402</v>
       </c>
       <c r="H1231" t="n">
         <v>1342</v>
@@ -36097,7 +36097,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1232" t="n">
-        <v>18.1642894744873</v>
+        <v>18.1642913818359</v>
       </c>
       <c r="H1232" t="n">
         <v>1517</v>
@@ -36126,7 +36126,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>18.0805835723877</v>
+        <v>18.0805854797363</v>
       </c>
       <c r="H1233" t="n">
         <v>303</v>
@@ -36213,7 +36213,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1236" t="n">
-        <v>19.5872974395752</v>
+        <v>19.5873012542725</v>
       </c>
       <c r="H1236" t="n">
         <v>1877</v>
@@ -36242,7 +36242,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1237" t="n">
-        <v>19.9221267700195</v>
+        <v>19.9221248626709</v>
       </c>
       <c r="H1237" t="n">
         <v>41</v>
@@ -36300,7 +36300,7 @@
         <v>24</v>
       </c>
       <c r="G1239" t="n">
-        <v>20.0895385742188</v>
+        <v>20.0895366668701</v>
       </c>
       <c r="H1239" t="n">
         <v>444</v>
@@ -36329,7 +36329,7 @@
         <v>24</v>
       </c>
       <c r="G1240" t="n">
-        <v>20.0895385742188</v>
+        <v>20.0895366668701</v>
       </c>
       <c r="H1240" t="n">
         <v>527</v>
@@ -36358,7 +36358,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1241" t="n">
-        <v>20.3406562805176</v>
+        <v>20.3406543731689</v>
       </c>
       <c r="H1241" t="n">
         <v>314</v>
@@ -36387,7 +36387,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1242" t="n">
-        <v>19.5872974395752</v>
+        <v>19.5873012542725</v>
       </c>
       <c r="H1242" t="n">
         <v>2087</v>
@@ -36416,7 +36416,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1243" t="n">
-        <v>19.5872974395752</v>
+        <v>19.5873012542725</v>
       </c>
       <c r="H1243" t="n">
         <v>118</v>
@@ -36445,7 +36445,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>19.5872974395752</v>
+        <v>19.5873012542725</v>
       </c>
       <c r="H1244" t="n">
         <v>0</v>
@@ -36474,7 +36474,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>19.5872974395752</v>
+        <v>19.5873012542725</v>
       </c>
       <c r="H1245" t="n">
         <v>759</v>
@@ -36532,7 +36532,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1247" t="n">
-        <v>19.0013561248779</v>
+        <v>19.0013542175293</v>
       </c>
       <c r="H1247" t="n">
         <v>310</v>
@@ -36590,7 +36590,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1249" t="n">
-        <v>19.0013561248779</v>
+        <v>19.0013542175293</v>
       </c>
       <c r="H1249" t="n">
         <v>173</v>
@@ -36619,7 +36619,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1250" t="n">
-        <v>19.5035934448242</v>
+        <v>19.5035915374756</v>
       </c>
       <c r="H1250" t="n">
         <v>760</v>
@@ -36648,7 +36648,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1251" t="n">
-        <v>19.9221267700195</v>
+        <v>19.9221248626709</v>
       </c>
       <c r="H1251" t="n">
         <v>3258</v>
@@ -36677,7 +36677,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1252" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1252" t="n">
         <v>7119</v>
@@ -36764,7 +36764,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1255" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1255" t="n">
         <v>3460</v>
@@ -36793,7 +36793,7 @@
         <v>26</v>
       </c>
       <c r="G1256" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1256" t="n">
         <v>908</v>
@@ -36851,7 +36851,7 @@
         <v>26</v>
       </c>
       <c r="G1258" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1258" t="n">
         <v>391</v>
@@ -36880,7 +36880,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1259" t="n">
-        <v>21.6799602508545</v>
+        <v>21.6799583435059</v>
       </c>
       <c r="H1259" t="n">
         <v>111</v>
@@ -36909,7 +36909,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1260" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1260" t="n">
         <v>45939</v>
@@ -36938,7 +36938,7 @@
         <v>25</v>
       </c>
       <c r="G1261" t="n">
-        <v>20.9266033172607</v>
+        <v>20.9265995025635</v>
       </c>
       <c r="H1261" t="n">
         <v>160</v>
@@ -36967,7 +36967,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1262" t="n">
-        <v>21.6799602508545</v>
+        <v>21.6799583435059</v>
       </c>
       <c r="H1262" t="n">
         <v>2635</v>
@@ -37025,7 +37025,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1264" t="n">
-        <v>21.5962543487549</v>
+        <v>21.5962505340576</v>
       </c>
       <c r="H1264" t="n">
         <v>62</v>
@@ -37054,7 +37054,7 @@
         <v>26</v>
       </c>
       <c r="G1265" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1265" t="n">
         <v>644</v>
@@ -37083,7 +37083,7 @@
         <v>25.5</v>
       </c>
       <c r="G1266" t="n">
-        <v>21.3451347351074</v>
+        <v>21.3451328277588</v>
       </c>
       <c r="H1266" t="n">
         <v>70</v>
@@ -37112,7 +37112,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>21.2614288330078</v>
+        <v>21.2614269256592</v>
       </c>
       <c r="H1267" t="n">
         <v>804</v>
@@ -37141,7 +37141,7 @@
         <v>25</v>
       </c>
       <c r="G1268" t="n">
-        <v>20.9266033172607</v>
+        <v>20.9265995025635</v>
       </c>
       <c r="H1268" t="n">
         <v>3623</v>
@@ -37170,7 +37170,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1269" t="n">
-        <v>20.4243640899658</v>
+        <v>20.4243621826172</v>
       </c>
       <c r="H1269" t="n">
         <v>2610</v>
@@ -37199,7 +37199,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1270" t="n">
-        <v>20.7591896057129</v>
+        <v>20.7591876983643</v>
       </c>
       <c r="H1270" t="n">
         <v>75177</v>
@@ -37228,7 +37228,7 @@
         <v>25</v>
       </c>
       <c r="G1271" t="n">
-        <v>20.9266033172607</v>
+        <v>20.9265995025635</v>
       </c>
       <c r="H1271" t="n">
         <v>365</v>
@@ -37257,7 +37257,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>21.2614288330078</v>
+        <v>21.2614269256592</v>
       </c>
       <c r="H1272" t="n">
         <v>291</v>
@@ -37286,7 +37286,7 @@
         <v>25.5</v>
       </c>
       <c r="G1273" t="n">
-        <v>21.3451347351074</v>
+        <v>21.3451328277588</v>
       </c>
       <c r="H1273" t="n">
         <v>64</v>
@@ -37402,7 +37402,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1277" t="n">
-        <v>21.6799602508545</v>
+        <v>21.6799583435059</v>
       </c>
       <c r="H1277" t="n">
         <v>1438</v>
@@ -37431,7 +37431,7 @@
         <v>26</v>
       </c>
       <c r="G1278" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1278" t="n">
         <v>2578</v>
@@ -37489,7 +37489,7 @@
         <v>26</v>
       </c>
       <c r="G1280" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1280" t="n">
         <v>224</v>
@@ -37518,7 +37518,7 @@
         <v>25.5</v>
       </c>
       <c r="G1281" t="n">
-        <v>21.3451347351074</v>
+        <v>21.3451328277588</v>
       </c>
       <c r="H1281" t="n">
         <v>733</v>
@@ -37547,7 +37547,7 @@
         <v>26</v>
       </c>
       <c r="G1282" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1282" t="n">
         <v>7025</v>
@@ -37576,7 +37576,7 @@
         <v>26</v>
       </c>
       <c r="G1283" t="n">
-        <v>22.6342124938965</v>
+        <v>22.6342144012451</v>
       </c>
       <c r="H1283" t="n">
         <v>3175</v>
@@ -37605,7 +37605,7 @@
         <v>25.5</v>
       </c>
       <c r="G1284" t="n">
-        <v>22.1989421844482</v>
+        <v>22.198938369751</v>
       </c>
       <c r="H1284" t="n">
         <v>1702</v>
@@ -37634,7 +37634,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1285" t="n">
-        <v>21.8507194519043</v>
+        <v>21.8507213592529</v>
       </c>
       <c r="H1285" t="n">
         <v>574</v>
@@ -37663,7 +37663,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>21.4154491424561</v>
+        <v>21.4154472351074</v>
       </c>
       <c r="H1286" t="n">
         <v>2031</v>
@@ -37692,7 +37692,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1287" t="n">
-        <v>20.6319580078125</v>
+        <v>20.6319561004639</v>
       </c>
       <c r="H1287" t="n">
         <v>81</v>
@@ -37721,7 +37721,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1288" t="n">
         <v>356</v>
@@ -37895,7 +37895,7 @@
         <v>24</v>
       </c>
       <c r="G1294" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1294" t="n">
         <v>167</v>
@@ -37924,7 +37924,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1295" t="n">
-        <v>20.6319580078125</v>
+        <v>20.6319561004639</v>
       </c>
       <c r="H1295" t="n">
         <v>254</v>
@@ -37953,7 +37953,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1296" t="n">
-        <v>20.6319580078125</v>
+        <v>20.6319561004639</v>
       </c>
       <c r="H1296" t="n">
         <v>0</v>
@@ -38098,7 +38098,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1301" t="n">
-        <v>20.6319580078125</v>
+        <v>20.6319561004639</v>
       </c>
       <c r="H1301" t="n">
         <v>100</v>
@@ -38127,7 +38127,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1302" t="n">
-        <v>20.6319580078125</v>
+        <v>20.6319561004639</v>
       </c>
       <c r="H1302" t="n">
         <v>66</v>
@@ -38156,7 +38156,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1303" t="n">
-        <v>20.6319580078125</v>
+        <v>20.6319561004639</v>
       </c>
       <c r="H1303" t="n">
         <v>0</v>
@@ -38243,7 +38243,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1306" t="n">
-        <v>20.2837390899658</v>
+        <v>20.2837371826172</v>
       </c>
       <c r="H1306" t="n">
         <v>455</v>
@@ -38272,7 +38272,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.2837390899658</v>
+        <v>20.2837371826172</v>
       </c>
       <c r="H1307" t="n">
         <v>53</v>
@@ -38301,7 +38301,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1308" t="n">
         <v>458</v>
@@ -38330,7 +38330,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1309" t="n">
-        <v>19.9355182647705</v>
+        <v>19.9355201721191</v>
       </c>
       <c r="H1309" t="n">
         <v>263</v>
@@ -38359,7 +38359,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1310" t="n">
         <v>1124</v>
@@ -38707,7 +38707,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1322" t="n">
-        <v>20.6319580078125</v>
+        <v>20.6319561004639</v>
       </c>
       <c r="H1322" t="n">
         <v>1292</v>
@@ -38736,7 +38736,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1323" t="n">
-        <v>20.6319580078125</v>
+        <v>20.6319561004639</v>
       </c>
       <c r="H1323" t="n">
         <v>0</v>
@@ -38765,7 +38765,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1324" t="n">
-        <v>20.6319580078125</v>
+        <v>20.6319561004639</v>
       </c>
       <c r="H1324" t="n">
         <v>0</v>
@@ -38823,7 +38823,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>21.1542835235596</v>
+        <v>21.1542816162109</v>
       </c>
       <c r="H1326" t="n">
         <v>220</v>
@@ -38881,7 +38881,7 @@
         <v>24</v>
       </c>
       <c r="G1328" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1328" t="n">
         <v>83</v>
@@ -38910,7 +38910,7 @@
         <v>24</v>
       </c>
       <c r="G1329" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1329" t="n">
         <v>411</v>
@@ -38939,7 +38939,7 @@
         <v>24</v>
       </c>
       <c r="G1330" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1330" t="n">
         <v>1005</v>
@@ -38968,7 +38968,7 @@
         <v>24</v>
       </c>
       <c r="G1331" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1331" t="n">
         <v>1380</v>
@@ -38997,7 +38997,7 @@
         <v>24</v>
       </c>
       <c r="G1332" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1332" t="n">
         <v>0</v>
@@ -39026,7 +39026,7 @@
         <v>24</v>
       </c>
       <c r="G1333" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1333" t="n">
         <v>368</v>
@@ -39055,7 +39055,7 @@
         <v>24</v>
       </c>
       <c r="G1334" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1334" t="n">
         <v>0</v>
@@ -39084,7 +39084,7 @@
         <v>24</v>
       </c>
       <c r="G1335" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1335" t="n">
         <v>10</v>
@@ -39258,7 +39258,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1341" t="n">
-        <v>20.6319580078125</v>
+        <v>20.6319561004639</v>
       </c>
       <c r="H1341" t="n">
         <v>370</v>
@@ -39345,7 +39345,7 @@
         <v>24</v>
       </c>
       <c r="G1344" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1344" t="n">
         <v>492</v>
@@ -39374,7 +39374,7 @@
         <v>24</v>
       </c>
       <c r="G1345" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1345" t="n">
         <v>502</v>
@@ -39432,7 +39432,7 @@
         <v>24</v>
       </c>
       <c r="G1347" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1347" t="n">
         <v>179</v>
@@ -39693,7 +39693,7 @@
         <v>24</v>
       </c>
       <c r="G1356" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1356" t="n">
         <v>1240</v>
@@ -39722,7 +39722,7 @@
         <v>24</v>
       </c>
       <c r="G1357" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1357" t="n">
         <v>3</v>
@@ -39751,7 +39751,7 @@
         <v>24</v>
       </c>
       <c r="G1358" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1358" t="n">
         <v>407</v>
@@ -39780,7 +39780,7 @@
         <v>24</v>
       </c>
       <c r="G1359" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1359" t="n">
         <v>352</v>
@@ -39809,7 +39809,7 @@
         <v>24</v>
       </c>
       <c r="G1360" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1360" t="n">
         <v>0</v>
@@ -39838,7 +39838,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1361" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1361" t="n">
         <v>1502</v>
@@ -39867,7 +39867,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1362" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1362" t="n">
         <v>0</v>
@@ -39896,7 +39896,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1363" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1363" t="n">
         <v>0</v>
@@ -39925,7 +39925,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1364" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1364" t="n">
         <v>200</v>
@@ -39954,7 +39954,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1365" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1365" t="n">
         <v>0</v>
@@ -40012,7 +40012,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1367" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1367" t="n">
         <v>785</v>
@@ -40070,7 +40070,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1369" t="n">
-        <v>20.6319580078125</v>
+        <v>20.6319561004639</v>
       </c>
       <c r="H1369" t="n">
         <v>910</v>
@@ -40099,7 +40099,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1370" t="n">
-        <v>20.2837390899658</v>
+        <v>20.2837371826172</v>
       </c>
       <c r="H1370" t="n">
         <v>518</v>
@@ -40128,7 +40128,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1371" t="n">
-        <v>20.2837390899658</v>
+        <v>20.2837371826172</v>
       </c>
       <c r="H1371" t="n">
         <v>0</v>
@@ -40215,7 +40215,7 @@
         <v>22.5</v>
       </c>
       <c r="G1374" t="n">
-        <v>19.5872993469238</v>
+        <v>19.5873012542725</v>
       </c>
       <c r="H1374" t="n">
         <v>796</v>
@@ -40244,7 +40244,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1375" t="n">
-        <v>18.0203170776367</v>
+        <v>18.0203151702881</v>
       </c>
       <c r="H1375" t="n">
         <v>1005</v>
@@ -40302,7 +40302,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1377" t="n">
-        <v>17.6720962524414</v>
+        <v>17.67209815979</v>
       </c>
       <c r="H1377" t="n">
         <v>4089</v>
@@ -40331,7 +40331,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1378" t="n">
-        <v>17.5850467681885</v>
+        <v>17.5850448608398</v>
       </c>
       <c r="H1378" t="n">
         <v>1568</v>
@@ -40360,7 +40360,7 @@
         <v>20</v>
       </c>
       <c r="G1379" t="n">
-        <v>17.4109344482422</v>
+        <v>17.4109325408936</v>
       </c>
       <c r="H1379" t="n">
         <v>1038</v>
@@ -40389,7 +40389,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>17.6720962524414</v>
+        <v>17.67209815979</v>
       </c>
       <c r="H1380" t="n">
         <v>252</v>
@@ -40418,7 +40418,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1381" t="n">
-        <v>17.6720962524414</v>
+        <v>17.67209815979</v>
       </c>
       <c r="H1381" t="n">
         <v>0</v>
@@ -40447,7 +40447,7 @@
         <v>20</v>
       </c>
       <c r="G1382" t="n">
-        <v>17.4109344482422</v>
+        <v>17.4109325408936</v>
       </c>
       <c r="H1382" t="n">
         <v>1370</v>
@@ -40476,7 +40476,7 @@
         <v>20</v>
       </c>
       <c r="G1383" t="n">
-        <v>17.4109344482422</v>
+        <v>17.4109325408936</v>
       </c>
       <c r="H1383" t="n">
         <v>2649</v>
@@ -40505,7 +40505,7 @@
         <v>20</v>
       </c>
       <c r="G1384" t="n">
-        <v>17.4109344482422</v>
+        <v>17.4109325408936</v>
       </c>
       <c r="H1384" t="n">
         <v>636</v>
@@ -40534,7 +40534,7 @@
         <v>20</v>
       </c>
       <c r="G1385" t="n">
-        <v>17.4109344482422</v>
+        <v>17.4109325408936</v>
       </c>
       <c r="H1385" t="n">
         <v>1510</v>
@@ -40563,7 +40563,7 @@
         <v>20</v>
       </c>
       <c r="G1386" t="n">
-        <v>17.4109344482422</v>
+        <v>17.4109325408936</v>
       </c>
       <c r="H1386" t="n">
         <v>460</v>
@@ -40592,7 +40592,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1387" t="n">
-        <v>17.5850467681885</v>
+        <v>17.5850448608398</v>
       </c>
       <c r="H1387" t="n">
         <v>1377</v>
@@ -40621,7 +40621,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1388" t="n">
-        <v>17.5850467681885</v>
+        <v>17.5850448608398</v>
       </c>
       <c r="H1388" t="n">
         <v>100</v>
@@ -40650,7 +40650,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1389" t="n">
-        <v>17.5850467681885</v>
+        <v>17.5850448608398</v>
       </c>
       <c r="H1389" t="n">
         <v>0</v>
@@ -40708,7 +40708,7 @@
         <v>19.75</v>
       </c>
       <c r="G1391" t="n">
-        <v>17.1932945251465</v>
+        <v>17.1932964324951</v>
       </c>
       <c r="H1391" t="n">
         <v>1628</v>
@@ -40737,7 +40737,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1392" t="n">
-        <v>16.9321327209473</v>
+        <v>16.9321346282959</v>
       </c>
       <c r="H1392" t="n">
         <v>3454</v>
@@ -40766,7 +40766,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1393" t="n">
-        <v>16.9321327209473</v>
+        <v>16.9321346282959</v>
       </c>
       <c r="H1393" t="n">
         <v>9757</v>
@@ -40795,7 +40795,7 @@
         <v>19.5499992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>17.0191841125488</v>
+        <v>17.0191860198975</v>
       </c>
       <c r="H1394" t="n">
         <v>3818</v>
@@ -40882,7 +40882,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>19.4131889343262</v>
+        <v>19.4131908416748</v>
       </c>
       <c r="H1397" t="n">
         <v>5217</v>
@@ -40969,7 +40969,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1400" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1400" t="n">
         <v>5707</v>
@@ -40998,7 +40998,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1401" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1401" t="n">
         <v>0</v>
@@ -41027,7 +41027,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1402" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1402" t="n">
         <v>0</v>
@@ -41056,7 +41056,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1403" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1403" t="n">
         <v>320</v>
@@ -41085,7 +41085,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1404" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1404" t="n">
         <v>348</v>
@@ -41114,7 +41114,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1405" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1405" t="n">
         <v>0</v>
@@ -41143,7 +41143,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1406" t="n">
-        <v>20.370792388916</v>
+        <v>20.3707942962646</v>
       </c>
       <c r="H1406" t="n">
         <v>0</v>
@@ -41172,7 +41172,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1407" t="n">
-        <v>19.8484630584717</v>
+        <v>19.8484649658203</v>
       </c>
       <c r="H1407" t="n">
         <v>354</v>
@@ -41201,7 +41201,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1408" t="n">
-        <v>19.9355182647705</v>
+        <v>19.9355201721191</v>
       </c>
       <c r="H1408" t="n">
         <v>144</v>
@@ -41230,7 +41230,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1409" t="n">
-        <v>19.9355182647705</v>
+        <v>19.9355201721191</v>
       </c>
       <c r="H1409" t="n">
         <v>87</v>
@@ -41259,7 +41259,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1410" t="n">
-        <v>19.674352645874</v>
+        <v>19.6743545532227</v>
       </c>
       <c r="H1410" t="n">
         <v>3151</v>
@@ -41288,7 +41288,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1411" t="n">
-        <v>19.674352645874</v>
+        <v>19.6743545532227</v>
       </c>
       <c r="H1411" t="n">
         <v>358</v>
@@ -41317,7 +41317,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1412" t="n">
-        <v>19.326135635376</v>
+        <v>19.3261394500732</v>
       </c>
       <c r="H1412" t="n">
         <v>1566</v>
@@ -41404,7 +41404,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1415" t="n">
-        <v>19.9355182647705</v>
+        <v>19.9355201721191</v>
       </c>
       <c r="H1415" t="n">
         <v>226</v>
@@ -41433,7 +41433,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>19.9355182647705</v>
+        <v>19.9355201721191</v>
       </c>
       <c r="H1416" t="n">
         <v>250</v>
@@ -41549,7 +41549,7 @@
         <v>23</v>
       </c>
       <c r="G1420" t="n">
-        <v>20.022575378418</v>
+        <v>20.0225734710693</v>
       </c>
       <c r="H1420" t="n">
         <v>143</v>
@@ -41578,7 +41578,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1421" t="n">
-        <v>20.2837390899658</v>
+        <v>20.2837371826172</v>
       </c>
       <c r="H1421" t="n">
         <v>83</v>
@@ -41607,7 +41607,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>20.2837390899658</v>
+        <v>20.2837371826172</v>
       </c>
       <c r="H1422" t="n">
         <v>52</v>
@@ -41636,7 +41636,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1423" t="n">
-        <v>20.2837390899658</v>
+        <v>20.2837371826172</v>
       </c>
       <c r="H1423" t="n">
         <v>0</v>
@@ -41694,7 +41694,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1425" t="n">
-        <v>20.2837390899658</v>
+        <v>20.2837371826172</v>
       </c>
       <c r="H1425" t="n">
         <v>135</v>
@@ -41723,7 +41723,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1426" t="n">
-        <v>20.2837390899658</v>
+        <v>20.2837371826172</v>
       </c>
       <c r="H1426" t="n">
         <v>1201</v>
@@ -41781,7 +41781,7 @@
         <v>24</v>
       </c>
       <c r="G1428" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1428" t="n">
         <v>5249</v>
@@ -41839,7 +41839,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1430" t="n">
-        <v>21.8507194519043</v>
+        <v>21.8507213592529</v>
       </c>
       <c r="H1430" t="n">
         <v>6822</v>
@@ -41868,7 +41868,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1431" t="n">
-        <v>22.4601039886475</v>
+        <v>22.4601020812988</v>
       </c>
       <c r="H1431" t="n">
         <v>1324</v>
@@ -41897,7 +41897,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1432" t="n">
-        <v>22.4601039886475</v>
+        <v>22.4601020812988</v>
       </c>
       <c r="H1432" t="n">
         <v>18</v>
@@ -41926,7 +41926,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1433" t="n">
-        <v>22.0248317718506</v>
+        <v>22.024829864502</v>
       </c>
       <c r="H1433" t="n">
         <v>1556</v>
@@ -41955,7 +41955,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>21.8507194519043</v>
+        <v>21.8507213592529</v>
       </c>
       <c r="H1434" t="n">
         <v>1414</v>
@@ -42042,7 +42042,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>21.4154491424561</v>
+        <v>21.4154472351074</v>
       </c>
       <c r="H1437" t="n">
         <v>633</v>
@@ -42158,7 +42158,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1441" t="n">
-        <v>22.0248317718506</v>
+        <v>22.024829864502</v>
       </c>
       <c r="H1441" t="n">
         <v>501</v>
@@ -42274,7 +42274,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>21.1542835235596</v>
+        <v>21.1542816162109</v>
       </c>
       <c r="H1445" t="n">
         <v>114</v>
@@ -42303,7 +42303,7 @@
         <v>24.5</v>
       </c>
       <c r="G1446" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1446" t="n">
         <v>743</v>
@@ -42332,7 +42332,7 @@
         <v>24.5</v>
       </c>
       <c r="G1447" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1447" t="n">
         <v>0</v>
@@ -42477,7 +42477,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1452" t="n">
-        <v>20.9801731109619</v>
+        <v>20.9801750183105</v>
       </c>
       <c r="H1452" t="n">
         <v>120</v>
@@ -42564,7 +42564,7 @@
         <v>24</v>
       </c>
       <c r="G1455" t="n">
-        <v>20.8931217193604</v>
+        <v>20.8931198120117</v>
       </c>
       <c r="H1455" t="n">
         <v>4309</v>
@@ -42622,7 +42622,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>21.1542835235596</v>
+        <v>21.1542816162109</v>
       </c>
       <c r="H1457" t="n">
         <v>176</v>
@@ -42651,7 +42651,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>21.1542835235596</v>
+        <v>21.1542816162109</v>
       </c>
       <c r="H1458" t="n">
         <v>1226</v>
@@ -42738,7 +42738,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1461" t="n">
-        <v>21.1542835235596</v>
+        <v>21.1542816162109</v>
       </c>
       <c r="H1461" t="n">
         <v>559</v>
@@ -42767,7 +42767,7 @@
         <v>24.5</v>
       </c>
       <c r="G1462" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1462" t="n">
         <v>235</v>
@@ -42796,7 +42796,7 @@
         <v>24.5</v>
       </c>
       <c r="G1463" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1463" t="n">
         <v>215</v>
@@ -42883,7 +42883,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>21.4154491424561</v>
+        <v>21.4154472351074</v>
       </c>
       <c r="H1466" t="n">
         <v>842</v>
@@ -42941,7 +42941,7 @@
         <v>24.5</v>
       </c>
       <c r="G1468" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1468" t="n">
         <v>100</v>
@@ -42970,7 +42970,7 @@
         <v>24.5</v>
       </c>
       <c r="G1469" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1469" t="n">
         <v>0</v>
@@ -43376,7 +43376,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1483" t="n">
-        <v>21.4154491424561</v>
+        <v>21.4154472351074</v>
       </c>
       <c r="H1483" t="n">
         <v>1200</v>
@@ -43463,7 +43463,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1486" t="n">
-        <v>21.4154491424561</v>
+        <v>21.4154472351074</v>
       </c>
       <c r="H1486" t="n">
         <v>55</v>
@@ -43579,7 +43579,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1490" t="n">
-        <v>21.4154491424561</v>
+        <v>21.4154472351074</v>
       </c>
       <c r="H1490" t="n">
         <v>578</v>
@@ -43608,7 +43608,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1491" t="n">
-        <v>21.4154491424561</v>
+        <v>21.4154472351074</v>
       </c>
       <c r="H1491" t="n">
         <v>0</v>
@@ -43695,7 +43695,7 @@
         <v>24.5</v>
       </c>
       <c r="G1494" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1494" t="n">
         <v>62</v>
@@ -43724,7 +43724,7 @@
         <v>24.5</v>
       </c>
       <c r="G1495" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1495" t="n">
         <v>900</v>
@@ -43869,7 +43869,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1500" t="n">
-        <v>21.4154491424561</v>
+        <v>21.4154472351074</v>
       </c>
       <c r="H1500" t="n">
         <v>380</v>
@@ -43898,7 +43898,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>21.4154491424561</v>
+        <v>21.4154472351074</v>
       </c>
       <c r="H1501" t="n">
         <v>0</v>
@@ -43956,7 +43956,7 @@
         <v>24.5</v>
       </c>
       <c r="G1503" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1503" t="n">
         <v>971</v>
@@ -43985,7 +43985,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1504" t="n">
-        <v>21.4154491424561</v>
+        <v>21.4154472351074</v>
       </c>
       <c r="H1504" t="n">
         <v>1070</v>
@@ -44014,7 +44014,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1505" t="n">
-        <v>21.4154491424561</v>
+        <v>21.4154472351074</v>
       </c>
       <c r="H1505" t="n">
         <v>374</v>
@@ -44043,7 +44043,7 @@
         <v>24.5</v>
       </c>
       <c r="G1506" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1506" t="n">
         <v>485</v>
@@ -44072,7 +44072,7 @@
         <v>24.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1507" t="n">
         <v>0</v>
@@ -44101,7 +44101,7 @@
         <v>24.5</v>
       </c>
       <c r="G1508" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1508" t="n">
         <v>40</v>
@@ -44159,7 +44159,7 @@
         <v>24.5</v>
       </c>
       <c r="G1510" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1510" t="n">
         <v>260</v>
@@ -44188,7 +44188,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1511" t="n">
-        <v>21.1542835235596</v>
+        <v>21.1542816162109</v>
       </c>
       <c r="H1511" t="n">
         <v>320</v>
@@ -44217,7 +44217,7 @@
         <v>24.5</v>
       </c>
       <c r="G1512" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1512" t="n">
         <v>1186</v>
@@ -44246,7 +44246,7 @@
         <v>24.5</v>
       </c>
       <c r="G1513" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1513" t="n">
         <v>325</v>
@@ -44275,7 +44275,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1514" t="n">
-        <v>20.9801731109619</v>
+        <v>20.9801750183105</v>
       </c>
       <c r="H1514" t="n">
         <v>264</v>
@@ -44362,7 +44362,7 @@
         <v>24.5</v>
       </c>
       <c r="G1517" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1517" t="n">
         <v>1767</v>
@@ -44536,7 +44536,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1523" t="n">
-        <v>20.9801731109619</v>
+        <v>20.9801750183105</v>
       </c>
       <c r="H1523" t="n">
         <v>220</v>
@@ -44565,7 +44565,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G1524" t="n">
-        <v>20.9801731109619</v>
+        <v>20.9801750183105</v>
       </c>
       <c r="H1524" t="n">
         <v>0</v>
@@ -44681,7 +44681,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>21.4154491424561</v>
+        <v>21.4154472351074</v>
       </c>
       <c r="H1528" t="n">
         <v>1426</v>
@@ -44710,7 +44710,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1529" t="n">
-        <v>21.8507194519043</v>
+        <v>21.8507213592529</v>
       </c>
       <c r="H1529" t="n">
         <v>334</v>
@@ -44826,7 +44826,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1533" t="n">
-        <v>21.9377765655518</v>
+        <v>21.9377746582031</v>
       </c>
       <c r="H1533" t="n">
         <v>160</v>
@@ -44855,7 +44855,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1534" t="n">
-        <v>21.9377765655518</v>
+        <v>21.9377746582031</v>
       </c>
       <c r="H1534" t="n">
         <v>80</v>
@@ -44884,7 +44884,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1535" t="n">
-        <v>21.9377765655518</v>
+        <v>21.9377746582031</v>
       </c>
       <c r="H1535" t="n">
         <v>3220</v>
@@ -44942,7 +44942,7 @@
         <v>24.5</v>
       </c>
       <c r="G1537" t="n">
-        <v>21.3283939361572</v>
+        <v>21.3283920288086</v>
       </c>
       <c r="H1537" t="n">
         <v>705</v>
@@ -69818,7 +69818,7 @@
         <v>17.5</v>
       </c>
       <c r="E2395" t="n">
-        <v>17.5</v>
+        <v>17.3500003814697</v>
       </c>
       <c r="F2395" t="n">
         <v>17.3500003814697</v>
@@ -69830,6 +69830,35 @@
         <v>22</v>
       </c>
       <c r="I2395" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2396">
+      <c r="A2396" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2396" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2396" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D2396" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E2396" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F2396" t="n">
+        <v>17.3500003814697</v>
+      </c>
+      <c r="G2396" t="n">
+        <v>17.3500003814697</v>
+      </c>
+      <c r="H2396" t="n">
+        <v>69</v>
+      </c>
+      <c r="I2396" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/INDB.MI.xlsx
+++ b/data/INDB.MI.xlsx
@@ -427,7 +427,7 @@
         <v>25.9799995422363</v>
       </c>
       <c r="G2" t="n">
-        <v>20.2326507568359</v>
+        <v>20.2326526641846</v>
       </c>
       <c r="H2" t="n">
         <v>174561</v>
@@ -456,7 +456,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>19.7030811309814</v>
+        <v>19.7030830383301</v>
       </c>
       <c r="H3" t="n">
         <v>34393</v>
@@ -572,7 +572,7 @@
         <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>21.0270023345947</v>
+        <v>21.027006149292</v>
       </c>
       <c r="H7" t="n">
         <v>11060</v>
@@ -601,7 +601,7 @@
         <v>26.6700000762939</v>
       </c>
       <c r="G8" t="n">
-        <v>20.7700099945068</v>
+        <v>20.7700080871582</v>
       </c>
       <c r="H8" t="n">
         <v>4734</v>
@@ -630,7 +630,7 @@
         <v>26.75</v>
       </c>
       <c r="G9" t="n">
-        <v>20.832311630249</v>
+        <v>20.8323097229004</v>
       </c>
       <c r="H9" t="n">
         <v>4096</v>
@@ -659,7 +659,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G10" t="n">
-        <v>20.7154960632324</v>
+        <v>20.7154979705811</v>
       </c>
       <c r="H10" t="n">
         <v>5200</v>
@@ -688,7 +688,7 @@
         <v>26.9899997711182</v>
       </c>
       <c r="G11" t="n">
-        <v>21.0192184448242</v>
+        <v>21.0192165374756</v>
       </c>
       <c r="H11" t="n">
         <v>9996</v>
@@ -717,7 +717,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G12" t="n">
-        <v>20.5986804962158</v>
+        <v>20.5986747741699</v>
       </c>
       <c r="H12" t="n">
         <v>3506</v>
@@ -833,7 +833,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>20.5986804962158</v>
+        <v>20.5986747741699</v>
       </c>
       <c r="H16" t="n">
         <v>4055</v>
@@ -920,7 +920,7 @@
         <v>26.9899997711182</v>
       </c>
       <c r="G19" t="n">
-        <v>21.0192184448242</v>
+        <v>21.0192165374756</v>
       </c>
       <c r="H19" t="n">
         <v>4714</v>
@@ -1007,7 +1007,7 @@
         <v>25.9200000762939</v>
       </c>
       <c r="G22" t="n">
-        <v>20.1859245300293</v>
+        <v>20.1859264373779</v>
       </c>
       <c r="H22" t="n">
         <v>656</v>
@@ -1065,7 +1065,7 @@
         <v>25.6499996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>19.9756546020508</v>
+        <v>19.9756526947021</v>
       </c>
       <c r="H24" t="n">
         <v>2327</v>
@@ -1123,7 +1123,7 @@
         <v>26.2099990844727</v>
       </c>
       <c r="G26" t="n">
-        <v>20.411771774292</v>
+        <v>20.4117698669434</v>
       </c>
       <c r="H26" t="n">
         <v>4049</v>
@@ -1152,7 +1152,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G27" t="n">
-        <v>20.5986804962158</v>
+        <v>20.5986747741699</v>
       </c>
       <c r="H27" t="n">
         <v>1256</v>
@@ -1181,7 +1181,7 @@
         <v>27</v>
       </c>
       <c r="G28" t="n">
-        <v>21.0270023345947</v>
+        <v>21.027006149292</v>
       </c>
       <c r="H28" t="n">
         <v>11169</v>
@@ -1239,7 +1239,7 @@
         <v>26.9899997711182</v>
       </c>
       <c r="G30" t="n">
-        <v>21.0192184448242</v>
+        <v>21.0192165374756</v>
       </c>
       <c r="H30" t="n">
         <v>1736</v>
@@ -1268,7 +1268,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G31" t="n">
-        <v>20.9880657196045</v>
+        <v>20.9880676269531</v>
       </c>
       <c r="H31" t="n">
         <v>7827</v>
@@ -1297,7 +1297,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G32" t="n">
-        <v>21.0425834655762</v>
+        <v>21.0425796508789</v>
       </c>
       <c r="H32" t="n">
         <v>2241</v>
@@ -1326,7 +1326,7 @@
         <v>27.25</v>
       </c>
       <c r="G33" t="n">
-        <v>21.2216987609863</v>
+        <v>21.221700668335</v>
       </c>
       <c r="H33" t="n">
         <v>1340</v>
@@ -1355,7 +1355,7 @@
         <v>26.6100006103516</v>
       </c>
       <c r="G34" t="n">
-        <v>20.7232818603516</v>
+        <v>20.7232799530029</v>
       </c>
       <c r="H34" t="n">
         <v>699</v>
@@ -1471,7 +1471,7 @@
         <v>27.2299995422363</v>
       </c>
       <c r="G38" t="n">
-        <v>21.206127166748</v>
+        <v>21.2061252593994</v>
       </c>
       <c r="H38" t="n">
         <v>3113</v>
@@ -1500,7 +1500,7 @@
         <v>27</v>
       </c>
       <c r="G39" t="n">
-        <v>21.0270023345947</v>
+        <v>21.027006149292</v>
       </c>
       <c r="H39" t="n">
         <v>4212</v>
@@ -1529,7 +1529,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G40" t="n">
-        <v>20.7933731079102</v>
+        <v>20.7933712005615</v>
       </c>
       <c r="H40" t="n">
         <v>1438</v>
@@ -1558,7 +1558,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>21.1827602386475</v>
+        <v>21.1827621459961</v>
       </c>
       <c r="H41" t="n">
         <v>6873</v>
@@ -1587,7 +1587,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G42" t="n">
-        <v>20.949125289917</v>
+        <v>20.9491271972656</v>
       </c>
       <c r="H42" t="n">
         <v>934</v>
@@ -1616,7 +1616,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G43" t="n">
-        <v>21.1827602386475</v>
+        <v>21.1827621459961</v>
       </c>
       <c r="H43" t="n">
         <v>2552</v>
@@ -1645,7 +1645,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>20.949125289917</v>
+        <v>20.9491271972656</v>
       </c>
       <c r="H44" t="n">
         <v>2515</v>
@@ -1674,7 +1674,7 @@
         <v>27</v>
       </c>
       <c r="G45" t="n">
-        <v>21.0270023345947</v>
+        <v>21.027006149292</v>
       </c>
       <c r="H45" t="n">
         <v>1075</v>
@@ -1703,7 +1703,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G46" t="n">
-        <v>20.949125289917</v>
+        <v>20.9491271972656</v>
       </c>
       <c r="H46" t="n">
         <v>729</v>
@@ -1732,7 +1732,7 @@
         <v>27</v>
       </c>
       <c r="G47" t="n">
-        <v>21.0270023345947</v>
+        <v>21.027006149292</v>
       </c>
       <c r="H47" t="n">
         <v>4748</v>
@@ -1761,7 +1761,7 @@
         <v>27.3899993896484</v>
       </c>
       <c r="G48" t="n">
-        <v>21.3307266235352</v>
+        <v>21.3307304382324</v>
       </c>
       <c r="H48" t="n">
         <v>56</v>
@@ -1819,7 +1819,7 @@
         <v>27.3299999237061</v>
       </c>
       <c r="G50" t="n">
-        <v>21.2840042114258</v>
+        <v>21.2840023040771</v>
       </c>
       <c r="H50" t="n">
         <v>6710</v>
@@ -1848,7 +1848,7 @@
         <v>27.5</v>
       </c>
       <c r="G51" t="n">
-        <v>21.4163932800293</v>
+        <v>21.4163951873779</v>
       </c>
       <c r="H51" t="n">
         <v>3852</v>
@@ -1877,7 +1877,7 @@
         <v>27.4899997711182</v>
       </c>
       <c r="G52" t="n">
-        <v>21.4086074829102</v>
+        <v>21.4086093902588</v>
       </c>
       <c r="H52" t="n">
         <v>3626</v>
@@ -1964,7 +1964,7 @@
         <v>27.2900009155273</v>
       </c>
       <c r="G55" t="n">
-        <v>21.2528495788574</v>
+        <v>21.2528514862061</v>
       </c>
       <c r="H55" t="n">
         <v>950</v>
@@ -1993,7 +1993,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G56" t="n">
-        <v>21.6500282287598</v>
+        <v>21.6500263214111</v>
       </c>
       <c r="H56" t="n">
         <v>1858</v>
@@ -2022,7 +2022,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G57" t="n">
-        <v>21.5721492767334</v>
+        <v>21.572151184082</v>
       </c>
       <c r="H57" t="n">
         <v>1171</v>
@@ -2051,7 +2051,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G58" t="n">
-        <v>21.5721492767334</v>
+        <v>21.572151184082</v>
       </c>
       <c r="H58" t="n">
         <v>750</v>
@@ -2109,7 +2109,7 @@
         <v>27.3099994659424</v>
       </c>
       <c r="G60" t="n">
-        <v>21.268424987793</v>
+        <v>21.2684268951416</v>
       </c>
       <c r="H60" t="n">
         <v>758</v>
@@ -2138,7 +2138,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>21.5332107543945</v>
+        <v>21.5332126617432</v>
       </c>
       <c r="H61" t="n">
         <v>80</v>
@@ -2167,7 +2167,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G62" t="n">
-        <v>21.4942722320557</v>
+        <v>21.4942741394043</v>
       </c>
       <c r="H62" t="n">
         <v>2613</v>
@@ -2196,7 +2196,7 @@
         <v>27.7600002288818</v>
       </c>
       <c r="G63" t="n">
-        <v>21.6188774108887</v>
+        <v>21.61887550354</v>
       </c>
       <c r="H63" t="n">
         <v>1081</v>
@@ -2225,7 +2225,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G64" t="n">
-        <v>21.3385162353516</v>
+        <v>21.3385181427002</v>
       </c>
       <c r="H64" t="n">
         <v>1272</v>
@@ -2254,7 +2254,7 @@
         <v>27.6900005340576</v>
       </c>
       <c r="G65" t="n">
-        <v>21.5643615722656</v>
+        <v>21.5643634796143</v>
       </c>
       <c r="H65" t="n">
         <v>328</v>
@@ -2341,7 +2341,7 @@
         <v>27.4400005340576</v>
       </c>
       <c r="G68" t="n">
-        <v>21.3696670532227</v>
+        <v>21.3696689605713</v>
       </c>
       <c r="H68" t="n">
         <v>2977</v>
@@ -2370,7 +2370,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>21.3385162353516</v>
+        <v>21.3385181427002</v>
       </c>
       <c r="H69" t="n">
         <v>4896</v>
@@ -2457,7 +2457,7 @@
         <v>27.2600002288818</v>
       </c>
       <c r="G72" t="n">
-        <v>21.2294864654541</v>
+        <v>21.2294883728027</v>
       </c>
       <c r="H72" t="n">
         <v>882</v>
@@ -2486,7 +2486,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>21.1048831939697</v>
+        <v>21.1048812866211</v>
       </c>
       <c r="H73" t="n">
         <v>1100</v>
@@ -2515,7 +2515,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G74" t="n">
-        <v>21.2995758056641</v>
+        <v>21.2995796203613</v>
       </c>
       <c r="H74" t="n">
         <v>1126</v>
@@ -2573,7 +2573,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>21.6500282287598</v>
+        <v>21.6500263214111</v>
       </c>
       <c r="H76" t="n">
         <v>6037</v>
@@ -2602,7 +2602,7 @@
         <v>27.5</v>
       </c>
       <c r="G77" t="n">
-        <v>21.4163932800293</v>
+        <v>21.4163951873779</v>
       </c>
       <c r="H77" t="n">
         <v>6849</v>
@@ -2631,7 +2631,7 @@
         <v>27.0300006866455</v>
       </c>
       <c r="G78" t="n">
-        <v>21.0503711700439</v>
+        <v>21.0503673553467</v>
       </c>
       <c r="H78" t="n">
         <v>952</v>
@@ -2689,7 +2689,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G80" t="n">
-        <v>20.7154960632324</v>
+        <v>20.7154979705811</v>
       </c>
       <c r="H80" t="n">
         <v>100</v>
@@ -2718,7 +2718,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G81" t="n">
-        <v>20.5597381591797</v>
+        <v>20.5597400665283</v>
       </c>
       <c r="H81" t="n">
         <v>535</v>
@@ -2805,7 +2805,7 @@
         <v>26.5300006866455</v>
       </c>
       <c r="G84" t="n">
-        <v>20.6609802246094</v>
+        <v>20.6609783172607</v>
       </c>
       <c r="H84" t="n">
         <v>227</v>
@@ -2834,7 +2834,7 @@
         <v>26.75</v>
       </c>
       <c r="G85" t="n">
-        <v>20.832311630249</v>
+        <v>20.8323097229004</v>
       </c>
       <c r="H85" t="n">
         <v>1000</v>
@@ -2863,7 +2863,7 @@
         <v>26.7700004577637</v>
       </c>
       <c r="G86" t="n">
-        <v>20.8478870391846</v>
+        <v>20.8478851318359</v>
       </c>
       <c r="H86" t="n">
         <v>83</v>
@@ -2892,7 +2892,7 @@
         <v>26.7700004577637</v>
       </c>
       <c r="G87" t="n">
-        <v>20.8478870391846</v>
+        <v>20.8478851318359</v>
       </c>
       <c r="H87" t="n">
         <v>216</v>
@@ -3008,7 +3008,7 @@
         <v>26.75</v>
       </c>
       <c r="G91" t="n">
-        <v>20.832311630249</v>
+        <v>20.8323097229004</v>
       </c>
       <c r="H91" t="n">
         <v>2846</v>
@@ -3037,7 +3037,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G92" t="n">
-        <v>21.1827602386475</v>
+        <v>21.1827621459961</v>
       </c>
       <c r="H92" t="n">
         <v>5839</v>
@@ -3095,7 +3095,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>21.1827602386475</v>
+        <v>21.1827621459961</v>
       </c>
       <c r="H94" t="n">
         <v>2807</v>
@@ -3124,7 +3124,7 @@
         <v>27.5</v>
       </c>
       <c r="G95" t="n">
-        <v>21.4163932800293</v>
+        <v>21.4163951873779</v>
       </c>
       <c r="H95" t="n">
         <v>3002</v>
@@ -3182,7 +3182,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>21.5721492767334</v>
+        <v>21.572151184082</v>
       </c>
       <c r="H97" t="n">
         <v>19396</v>
@@ -3240,7 +3240,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G99" t="n">
-        <v>22.8960723876953</v>
+        <v>22.8960742950439</v>
       </c>
       <c r="H99" t="n">
         <v>129721</v>
@@ -3269,7 +3269,7 @@
         <v>29.5</v>
       </c>
       <c r="G100" t="n">
-        <v>22.9739513397217</v>
+        <v>22.9739475250244</v>
       </c>
       <c r="H100" t="n">
         <v>29152</v>
@@ -3298,7 +3298,7 @@
         <v>29.8799991607666</v>
       </c>
       <c r="G101" t="n">
-        <v>23.2698841094971</v>
+        <v>23.2698879241943</v>
       </c>
       <c r="H101" t="n">
         <v>57558</v>
@@ -3356,7 +3356,7 @@
         <v>31.6499996185303</v>
       </c>
       <c r="G103" t="n">
-        <v>24.6483211517334</v>
+        <v>24.648323059082</v>
       </c>
       <c r="H103" t="n">
         <v>23345</v>
@@ -3385,7 +3385,7 @@
         <v>31.4699993133545</v>
       </c>
       <c r="G104" t="n">
-        <v>24.5081424713135</v>
+        <v>24.5081443786621</v>
       </c>
       <c r="H104" t="n">
         <v>21297</v>
@@ -3414,7 +3414,7 @@
         <v>31.7700004577637</v>
       </c>
       <c r="G105" t="n">
-        <v>24.7417755126953</v>
+        <v>24.7417793273926</v>
       </c>
       <c r="H105" t="n">
         <v>22649</v>
@@ -3443,7 +3443,7 @@
         <v>33</v>
       </c>
       <c r="G106" t="n">
-        <v>25.6996784210205</v>
+        <v>25.6996726989746</v>
       </c>
       <c r="H106" t="n">
         <v>82705</v>
@@ -3530,7 +3530,7 @@
         <v>34.8800010681152</v>
       </c>
       <c r="G109" t="n">
-        <v>27.1637725830078</v>
+        <v>27.1637763977051</v>
       </c>
       <c r="H109" t="n">
         <v>12506</v>
@@ -3559,7 +3559,7 @@
         <v>34</v>
       </c>
       <c r="G110" t="n">
-        <v>26.4784526824951</v>
+        <v>26.4784545898438</v>
       </c>
       <c r="H110" t="n">
         <v>33933</v>
@@ -3588,7 +3588,7 @@
         <v>34.1399993896484</v>
       </c>
       <c r="G111" t="n">
-        <v>26.5874805450439</v>
+        <v>26.5874824523926</v>
       </c>
       <c r="H111" t="n">
         <v>11574</v>
@@ -3617,7 +3617,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G112" t="n">
-        <v>26.9457187652588</v>
+        <v>26.9457168579102</v>
       </c>
       <c r="H112" t="n">
         <v>3860</v>
@@ -3646,7 +3646,7 @@
         <v>33.5</v>
       </c>
       <c r="G113" t="n">
-        <v>26.0890636444092</v>
+        <v>26.0890617370605</v>
       </c>
       <c r="H113" t="n">
         <v>12586</v>
@@ -3675,7 +3675,7 @@
         <v>33.0800018310547</v>
       </c>
       <c r="G114" t="n">
-        <v>25.7619762420654</v>
+        <v>25.7619781494141</v>
       </c>
       <c r="H114" t="n">
         <v>7353</v>
@@ -3704,7 +3704,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>26.2448196411133</v>
+        <v>26.2448177337646</v>
       </c>
       <c r="H115" t="n">
         <v>1478</v>
@@ -3733,7 +3733,7 @@
         <v>33.4900016784668</v>
       </c>
       <c r="G116" t="n">
-        <v>26.08127784729</v>
+        <v>26.0812759399414</v>
       </c>
       <c r="H116" t="n">
         <v>2749</v>
@@ -3791,7 +3791,7 @@
         <v>34.7200012207031</v>
       </c>
       <c r="G118" t="n">
-        <v>27.0391693115234</v>
+        <v>27.0391731262207</v>
       </c>
       <c r="H118" t="n">
         <v>19816</v>
@@ -3907,7 +3907,7 @@
         <v>34.2599983215332</v>
       </c>
       <c r="G122" t="n">
-        <v>26.6809349060059</v>
+        <v>26.6809329986572</v>
       </c>
       <c r="H122" t="n">
         <v>12734</v>
@@ -3936,7 +3936,7 @@
         <v>34.0299987792969</v>
       </c>
       <c r="G123" t="n">
-        <v>26.5018138885498</v>
+        <v>26.5018157958984</v>
       </c>
       <c r="H123" t="n">
         <v>779</v>
@@ -3965,7 +3965,7 @@
         <v>34.2599983215332</v>
       </c>
       <c r="G124" t="n">
-        <v>26.6809349060059</v>
+        <v>26.6809329986572</v>
       </c>
       <c r="H124" t="n">
         <v>7319</v>
@@ -4052,7 +4052,7 @@
         <v>32.5</v>
       </c>
       <c r="G127" t="n">
-        <v>25.3102874755859</v>
+        <v>25.3102855682373</v>
       </c>
       <c r="H127" t="n">
         <v>13436</v>
@@ -4081,7 +4081,7 @@
         <v>32.810001373291</v>
       </c>
       <c r="G128" t="n">
-        <v>25.5517082214355</v>
+        <v>25.5517063140869</v>
       </c>
       <c r="H128" t="n">
         <v>3332</v>
@@ -4226,7 +4226,7 @@
         <v>33.1100006103516</v>
       </c>
       <c r="G133" t="n">
-        <v>25.7853393554688</v>
+        <v>25.7853412628174</v>
       </c>
       <c r="H133" t="n">
         <v>11311</v>
@@ -4342,7 +4342,7 @@
         <v>32.4900016784668</v>
       </c>
       <c r="G137" t="n">
-        <v>25.3024978637695</v>
+        <v>25.3024997711182</v>
       </c>
       <c r="H137" t="n">
         <v>782</v>
@@ -4400,7 +4400,7 @@
         <v>32.0400009155273</v>
       </c>
       <c r="G139" t="n">
-        <v>24.9520473480225</v>
+        <v>24.9520454406738</v>
       </c>
       <c r="H139" t="n">
         <v>3355</v>
@@ -4545,7 +4545,7 @@
         <v>32.0699996948242</v>
       </c>
       <c r="G144" t="n">
-        <v>24.9754104614258</v>
+        <v>24.9754085540771</v>
       </c>
       <c r="H144" t="n">
         <v>1467</v>
@@ -4777,7 +4777,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>26.0111885070801</v>
+        <v>26.0111846923828</v>
       </c>
       <c r="H152" t="n">
         <v>2548</v>
@@ -4806,7 +4806,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G153" t="n">
-        <v>26.0111885070801</v>
+        <v>26.0111846923828</v>
       </c>
       <c r="H153" t="n">
         <v>2339</v>
@@ -4893,7 +4893,7 @@
         <v>32.7599983215332</v>
       </c>
       <c r="G156" t="n">
-        <v>25.5127658843994</v>
+        <v>25.512767791748</v>
       </c>
       <c r="H156" t="n">
         <v>1290</v>
@@ -4922,7 +4922,7 @@
         <v>32.5</v>
       </c>
       <c r="G157" t="n">
-        <v>25.3102874755859</v>
+        <v>25.3102855682373</v>
       </c>
       <c r="H157" t="n">
         <v>3379</v>
@@ -4980,7 +4980,7 @@
         <v>33.1800003051758</v>
       </c>
       <c r="G159" t="n">
-        <v>25.8398532867432</v>
+        <v>25.8398551940918</v>
       </c>
       <c r="H159" t="n">
         <v>1728</v>
@@ -5067,7 +5067,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G162" t="n">
-        <v>26.3226928710938</v>
+        <v>26.3226947784424</v>
       </c>
       <c r="H162" t="n">
         <v>3557</v>
@@ -5096,7 +5096,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G163" t="n">
-        <v>27.0236015319824</v>
+        <v>27.0235977172852</v>
       </c>
       <c r="H163" t="n">
         <v>6263</v>
@@ -5125,7 +5125,7 @@
         <v>35.5999984741211</v>
       </c>
       <c r="G164" t="n">
-        <v>27.7244968414307</v>
+        <v>27.724494934082</v>
       </c>
       <c r="H164" t="n">
         <v>9877</v>
@@ -5154,7 +5154,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G165" t="n">
-        <v>27.8023719787598</v>
+        <v>27.8023738861084</v>
       </c>
       <c r="H165" t="n">
         <v>3475</v>
@@ -5183,7 +5183,7 @@
         <v>36</v>
       </c>
       <c r="G166" t="n">
-        <v>28.0360069274902</v>
+        <v>28.0360050201416</v>
       </c>
       <c r="H166" t="n">
         <v>9880</v>
@@ -5212,7 +5212,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G167" t="n">
-        <v>28.6590309143066</v>
+        <v>28.659029006958</v>
       </c>
       <c r="H167" t="n">
         <v>13339</v>
@@ -5241,7 +5241,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G168" t="n">
-        <v>28.5811519622803</v>
+        <v>28.5811557769775</v>
       </c>
       <c r="H168" t="n">
         <v>5116</v>
@@ -5270,7 +5270,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G169" t="n">
-        <v>28.5811519622803</v>
+        <v>28.5811557769775</v>
       </c>
       <c r="H169" t="n">
         <v>1884</v>
@@ -5299,7 +5299,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G170" t="n">
-        <v>28.3475208282471</v>
+        <v>28.3475189208984</v>
       </c>
       <c r="H170" t="n">
         <v>2310</v>
@@ -5328,7 +5328,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G171" t="n">
-        <v>27.8802490234375</v>
+        <v>27.8802547454834</v>
       </c>
       <c r="H171" t="n">
         <v>4115</v>
@@ -5415,7 +5415,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G174" t="n">
-        <v>27.4129867553711</v>
+        <v>27.4129848480225</v>
       </c>
       <c r="H174" t="n">
         <v>6992</v>
@@ -5444,7 +5444,7 @@
         <v>35.5</v>
       </c>
       <c r="G175" t="n">
-        <v>27.6466178894043</v>
+        <v>27.6466159820557</v>
       </c>
       <c r="H175" t="n">
         <v>3329</v>
@@ -5473,7 +5473,7 @@
         <v>35.5</v>
       </c>
       <c r="G176" t="n">
-        <v>27.6466178894043</v>
+        <v>27.6466159820557</v>
       </c>
       <c r="H176" t="n">
         <v>1450</v>
@@ -5502,7 +5502,7 @@
         <v>35.5</v>
       </c>
       <c r="G177" t="n">
-        <v>27.6466178894043</v>
+        <v>27.6466159820557</v>
       </c>
       <c r="H177" t="n">
         <v>705</v>
@@ -5531,7 +5531,7 @@
         <v>36</v>
       </c>
       <c r="G178" t="n">
-        <v>28.0360069274902</v>
+        <v>28.0360050201416</v>
       </c>
       <c r="H178" t="n">
         <v>1619</v>
@@ -5560,7 +5560,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G179" t="n">
-        <v>27.5687446594238</v>
+        <v>27.5687427520752</v>
       </c>
       <c r="H179" t="n">
         <v>2162</v>
@@ -5589,7 +5589,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G180" t="n">
-        <v>27.0236015319824</v>
+        <v>27.0235977172852</v>
       </c>
       <c r="H180" t="n">
         <v>7931</v>
@@ -5618,7 +5618,7 @@
         <v>34.5</v>
       </c>
       <c r="G181" t="n">
-        <v>26.8678398132324</v>
+        <v>26.8678359985352</v>
       </c>
       <c r="H181" t="n">
         <v>3053</v>
@@ -5647,7 +5647,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>26.7120838165283</v>
+        <v>26.7120819091797</v>
       </c>
       <c r="H182" t="n">
         <v>1589</v>
@@ -5676,7 +5676,7 @@
         <v>34.5</v>
       </c>
       <c r="G183" t="n">
-        <v>26.8678398132324</v>
+        <v>26.8678359985352</v>
       </c>
       <c r="H183" t="n">
         <v>5764</v>
@@ -5705,7 +5705,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>26.6342086791992</v>
+        <v>26.6342105865479</v>
       </c>
       <c r="H184" t="n">
         <v>7675</v>
@@ -5734,7 +5734,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G185" t="n">
-        <v>26.5563278198242</v>
+        <v>26.5563259124756</v>
       </c>
       <c r="H185" t="n">
         <v>16058</v>
@@ -5763,7 +5763,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G186" t="n">
-        <v>26.5563278198242</v>
+        <v>26.5563259124756</v>
       </c>
       <c r="H186" t="n">
         <v>1160</v>
@@ -5821,7 +5821,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G188" t="n">
-        <v>24.7651386260986</v>
+        <v>24.7651405334473</v>
       </c>
       <c r="H188" t="n">
         <v>4764</v>
@@ -5850,7 +5850,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G189" t="n">
-        <v>24.3757476806641</v>
+        <v>24.3757514953613</v>
       </c>
       <c r="H189" t="n">
         <v>3231</v>
@@ -5995,7 +5995,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G194" t="n">
-        <v>26.2448196411133</v>
+        <v>26.2448177337646</v>
       </c>
       <c r="H194" t="n">
         <v>8189</v>
@@ -6024,7 +6024,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G195" t="n">
-        <v>26.5563278198242</v>
+        <v>26.5563259124756</v>
       </c>
       <c r="H195" t="n">
         <v>5665</v>
@@ -6053,7 +6053,7 @@
         <v>34</v>
       </c>
       <c r="G196" t="n">
-        <v>26.4784526824951</v>
+        <v>26.4784545898438</v>
       </c>
       <c r="H196" t="n">
         <v>501</v>
@@ -6082,7 +6082,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G197" t="n">
-        <v>26.7899684906006</v>
+        <v>26.789966583252</v>
       </c>
       <c r="H197" t="n">
         <v>6683</v>
@@ -6111,7 +6111,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G198" t="n">
-        <v>26.9457187652588</v>
+        <v>26.9457168579102</v>
       </c>
       <c r="H198" t="n">
         <v>4790</v>
@@ -6140,7 +6140,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G199" t="n">
-        <v>26.2448196411133</v>
+        <v>26.2448177337646</v>
       </c>
       <c r="H199" t="n">
         <v>2681</v>
@@ -6198,7 +6198,7 @@
         <v>33</v>
       </c>
       <c r="G201" t="n">
-        <v>25.6996784210205</v>
+        <v>25.6996726989746</v>
       </c>
       <c r="H201" t="n">
         <v>283</v>
@@ -6227,7 +6227,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G202" t="n">
-        <v>24.843017578125</v>
+        <v>24.8430156707764</v>
       </c>
       <c r="H202" t="n">
         <v>5057</v>
@@ -6256,7 +6256,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G203" t="n">
-        <v>24.7651386260986</v>
+        <v>24.7651405334473</v>
       </c>
       <c r="H203" t="n">
         <v>2660</v>
@@ -6285,7 +6285,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G204" t="n">
-        <v>24.4536285400391</v>
+        <v>24.4536304473877</v>
       </c>
       <c r="H204" t="n">
         <v>1166</v>
@@ -6343,7 +6343,7 @@
         <v>32.5</v>
       </c>
       <c r="G206" t="n">
-        <v>25.3102874755859</v>
+        <v>25.3102855682373</v>
       </c>
       <c r="H206" t="n">
         <v>1220</v>
@@ -6372,7 +6372,7 @@
         <v>32.5</v>
       </c>
       <c r="G207" t="n">
-        <v>25.3102874755859</v>
+        <v>25.3102855682373</v>
       </c>
       <c r="H207" t="n">
         <v>2453</v>
@@ -6401,7 +6401,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G208" t="n">
-        <v>26.0111885070801</v>
+        <v>26.0111846923828</v>
       </c>
       <c r="H208" t="n">
         <v>281</v>
@@ -6430,7 +6430,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G209" t="n">
-        <v>26.400577545166</v>
+        <v>26.4005756378174</v>
       </c>
       <c r="H209" t="n">
         <v>4789</v>
@@ -6459,7 +6459,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G210" t="n">
-        <v>26.400577545166</v>
+        <v>26.4005756378174</v>
       </c>
       <c r="H210" t="n">
         <v>2397</v>
@@ -6546,7 +6546,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G213" t="n">
-        <v>26.0111885070801</v>
+        <v>26.0111846923828</v>
       </c>
       <c r="H213" t="n">
         <v>312</v>
@@ -6604,7 +6604,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G215" t="n">
-        <v>26.3226928710938</v>
+        <v>26.3226947784424</v>
       </c>
       <c r="H215" t="n">
         <v>187</v>
@@ -6633,7 +6633,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G216" t="n">
-        <v>26.400577545166</v>
+        <v>26.4005756378174</v>
       </c>
       <c r="H216" t="n">
         <v>5497</v>
@@ -6662,7 +6662,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G217" t="n">
-        <v>26.1669368743896</v>
+        <v>26.1669406890869</v>
       </c>
       <c r="H217" t="n">
         <v>299</v>
@@ -6720,7 +6720,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G219" t="n">
-        <v>25.4660415649414</v>
+        <v>25.4660396575928</v>
       </c>
       <c r="H219" t="n">
         <v>875</v>
@@ -6749,7 +6749,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>25.4660415649414</v>
+        <v>25.4660396575928</v>
       </c>
       <c r="H220" t="n">
         <v>1296</v>
@@ -6778,7 +6778,7 @@
         <v>32</v>
       </c>
       <c r="G221" t="n">
-        <v>24.9208965301514</v>
+        <v>24.9208946228027</v>
       </c>
       <c r="H221" t="n">
         <v>10203</v>
@@ -6807,7 +6807,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G222" t="n">
-        <v>24.4536285400391</v>
+        <v>24.4536304473877</v>
       </c>
       <c r="H222" t="n">
         <v>1876</v>
@@ -6836,7 +6836,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G223" t="n">
-        <v>26.7899684906006</v>
+        <v>26.789966583252</v>
       </c>
       <c r="H223" t="n">
         <v>2581</v>
@@ -6865,7 +6865,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G224" t="n">
-        <v>26.0111885070801</v>
+        <v>26.0111846923828</v>
       </c>
       <c r="H224" t="n">
         <v>5330</v>
@@ -6894,7 +6894,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G225" t="n">
-        <v>26.5563278198242</v>
+        <v>26.5563259124756</v>
       </c>
       <c r="H225" t="n">
         <v>8082</v>
@@ -7010,7 +7010,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G229" t="n">
-        <v>25.2324104309082</v>
+        <v>25.2324085235596</v>
       </c>
       <c r="H229" t="n">
         <v>613</v>
@@ -7039,7 +7039,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G230" t="n">
-        <v>25.4660415649414</v>
+        <v>25.4660396575928</v>
       </c>
       <c r="H230" t="n">
         <v>520</v>
@@ -7068,7 +7068,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G231" t="n">
-        <v>25.7775497436523</v>
+        <v>25.777551651001</v>
       </c>
       <c r="H231" t="n">
         <v>709</v>
@@ -7097,7 +7097,7 @@
         <v>34.5</v>
       </c>
       <c r="G232" t="n">
-        <v>26.8678398132324</v>
+        <v>26.8678359985352</v>
       </c>
       <c r="H232" t="n">
         <v>21858</v>
@@ -7126,7 +7126,7 @@
         <v>35.5</v>
       </c>
       <c r="G233" t="n">
-        <v>27.6466178894043</v>
+        <v>27.6466159820557</v>
       </c>
       <c r="H233" t="n">
         <v>9651</v>
@@ -7155,7 +7155,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G234" t="n">
-        <v>27.5687446594238</v>
+        <v>27.5687427520752</v>
       </c>
       <c r="H234" t="n">
         <v>4214</v>
@@ -7184,7 +7184,7 @@
         <v>35.5</v>
       </c>
       <c r="G235" t="n">
-        <v>27.6466178894043</v>
+        <v>27.6466159820557</v>
       </c>
       <c r="H235" t="n">
         <v>3108</v>
@@ -7213,7 +7213,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G236" t="n">
-        <v>26.7899684906006</v>
+        <v>26.789966583252</v>
       </c>
       <c r="H236" t="n">
         <v>968</v>
@@ -7242,7 +7242,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>26.7120838165283</v>
+        <v>26.7120819091797</v>
       </c>
       <c r="H237" t="n">
         <v>3045</v>
@@ -7271,7 +7271,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G238" t="n">
-        <v>26.7120838165283</v>
+        <v>26.7120819091797</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>27.1014709472656</v>
+        <v>27.1014728546143</v>
       </c>
       <c r="H239" t="n">
         <v>10</v>
@@ -7329,7 +7329,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G240" t="n">
-        <v>26.6342086791992</v>
+        <v>26.6342105865479</v>
       </c>
       <c r="H240" t="n">
         <v>353</v>
@@ -7358,7 +7358,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G241" t="n">
-        <v>26.400577545166</v>
+        <v>26.4005756378174</v>
       </c>
       <c r="H241" t="n">
         <v>2580</v>
@@ -7387,7 +7387,7 @@
         <v>34</v>
       </c>
       <c r="G242" t="n">
-        <v>26.4784526824951</v>
+        <v>26.4784545898438</v>
       </c>
       <c r="H242" t="n">
         <v>1034</v>
@@ -7416,7 +7416,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G243" t="n">
-        <v>26.5563278198242</v>
+        <v>26.5563259124756</v>
       </c>
       <c r="H243" t="n">
         <v>9</v>
@@ -7445,7 +7445,7 @@
         <v>34</v>
       </c>
       <c r="G244" t="n">
-        <v>26.4784526824951</v>
+        <v>26.4784545898438</v>
       </c>
       <c r="H244" t="n">
         <v>552</v>
@@ -7474,7 +7474,7 @@
         <v>34.5</v>
       </c>
       <c r="G245" t="n">
-        <v>26.8678398132324</v>
+        <v>26.8678359985352</v>
       </c>
       <c r="H245" t="n">
         <v>469</v>
@@ -7503,7 +7503,7 @@
         <v>34</v>
       </c>
       <c r="G246" t="n">
-        <v>26.4784526824951</v>
+        <v>26.4784545898438</v>
       </c>
       <c r="H246" t="n">
         <v>1008</v>
@@ -7532,7 +7532,7 @@
         <v>34</v>
       </c>
       <c r="G247" t="n">
-        <v>26.4784526824951</v>
+        <v>26.4784545898438</v>
       </c>
       <c r="H247" t="n">
         <v>1269</v>
@@ -7561,7 +7561,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G248" t="n">
-        <v>26.7899684906006</v>
+        <v>26.789966583252</v>
       </c>
       <c r="H248" t="n">
         <v>2819</v>
@@ -7590,7 +7590,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G249" t="n">
-        <v>26.1669368743896</v>
+        <v>26.1669406890869</v>
       </c>
       <c r="H249" t="n">
         <v>304</v>
@@ -7619,7 +7619,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G250" t="n">
-        <v>26.5563278198242</v>
+        <v>26.5563259124756</v>
       </c>
       <c r="H250" t="n">
         <v>406</v>
@@ -7648,7 +7648,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>27.0236015319824</v>
+        <v>27.0235977172852</v>
       </c>
       <c r="H251" t="n">
         <v>405</v>
@@ -7677,7 +7677,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G252" t="n">
-        <v>26.2448196411133</v>
+        <v>26.2448177337646</v>
       </c>
       <c r="H252" t="n">
         <v>292</v>
@@ -7706,7 +7706,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G253" t="n">
-        <v>26.3226928710938</v>
+        <v>26.3226947784424</v>
       </c>
       <c r="H253" t="n">
         <v>2196</v>
@@ -7735,7 +7735,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>26.2448196411133</v>
+        <v>26.2448177337646</v>
       </c>
       <c r="H254" t="n">
         <v>908</v>
@@ -7764,7 +7764,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G255" t="n">
-        <v>26.1669368743896</v>
+        <v>26.1669406890869</v>
       </c>
       <c r="H255" t="n">
         <v>2989</v>
@@ -7822,7 +7822,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G257" t="n">
-        <v>26.3100147247314</v>
+        <v>26.3100166320801</v>
       </c>
       <c r="H257" t="n">
         <v>420</v>
@@ -7909,7 +7909,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G260" t="n">
-        <v>26.3100147247314</v>
+        <v>26.3100166320801</v>
       </c>
       <c r="H260" t="n">
         <v>833</v>
@@ -7967,7 +7967,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>25.1177215576172</v>
+        <v>25.1177196502686</v>
       </c>
       <c r="H262" t="n">
         <v>7793</v>
@@ -8083,7 +8083,7 @@
         <v>32.5</v>
       </c>
       <c r="G266" t="n">
-        <v>25.8330955505371</v>
+        <v>25.8330974578857</v>
       </c>
       <c r="H266" t="n">
         <v>197</v>
@@ -8170,7 +8170,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>26.866418838501</v>
+        <v>26.8664207458496</v>
       </c>
       <c r="H269" t="n">
         <v>1325</v>
@@ -8460,7 +8460,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>27.1843681335449</v>
+        <v>27.1843700408936</v>
       </c>
       <c r="H279" t="n">
         <v>933</v>
@@ -8489,7 +8489,7 @@
         <v>34</v>
       </c>
       <c r="G280" t="n">
-        <v>27.0253944396973</v>
+        <v>27.0253982543945</v>
       </c>
       <c r="H280" t="n">
         <v>2112</v>
@@ -8518,7 +8518,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>26.866418838501</v>
+        <v>26.8664207458496</v>
       </c>
       <c r="H281" t="n">
         <v>54</v>
@@ -8547,7 +8547,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G282" t="n">
-        <v>26.866418838501</v>
+        <v>26.8664207458496</v>
       </c>
       <c r="H282" t="n">
         <v>5889</v>
@@ -8576,7 +8576,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G283" t="n">
-        <v>26.866418838501</v>
+        <v>26.8664207458496</v>
       </c>
       <c r="H283" t="n">
         <v>958</v>
@@ -8634,7 +8634,7 @@
         <v>34</v>
       </c>
       <c r="G285" t="n">
-        <v>27.0253944396973</v>
+        <v>27.0253982543945</v>
       </c>
       <c r="H285" t="n">
         <v>85</v>
@@ -8663,7 +8663,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G286" t="n">
-        <v>26.707447052002</v>
+        <v>26.7074489593506</v>
       </c>
       <c r="H286" t="n">
         <v>170</v>
@@ -8692,7 +8692,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G287" t="n">
-        <v>26.707447052002</v>
+        <v>26.7074489593506</v>
       </c>
       <c r="H287" t="n">
         <v>1022</v>
@@ -8750,7 +8750,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G289" t="n">
-        <v>26.707447052002</v>
+        <v>26.7074489593506</v>
       </c>
       <c r="H289" t="n">
         <v>1031</v>
@@ -8808,7 +8808,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>26.866418838501</v>
+        <v>26.8664207458496</v>
       </c>
       <c r="H291" t="n">
         <v>4293</v>
@@ -9011,7 +9011,7 @@
         <v>34.5</v>
       </c>
       <c r="G298" t="n">
-        <v>27.4228248596191</v>
+        <v>27.4228210449219</v>
       </c>
       <c r="H298" t="n">
         <v>660</v>
@@ -9040,7 +9040,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>26.866418838501</v>
+        <v>26.8664207458496</v>
       </c>
       <c r="H299" t="n">
         <v>30</v>
@@ -9069,7 +9069,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G300" t="n">
-        <v>26.9459075927734</v>
+        <v>26.9459095001221</v>
       </c>
       <c r="H300" t="n">
         <v>494</v>
@@ -9098,7 +9098,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G301" t="n">
-        <v>26.866418838501</v>
+        <v>26.8664207458496</v>
       </c>
       <c r="H301" t="n">
         <v>149</v>
@@ -9185,7 +9185,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G304" t="n">
-        <v>27.1048793792725</v>
+        <v>27.1048774719238</v>
       </c>
       <c r="H304" t="n">
         <v>28</v>
@@ -9214,7 +9214,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G305" t="n">
-        <v>26.707447052002</v>
+        <v>26.7074489593506</v>
       </c>
       <c r="H305" t="n">
         <v>131</v>
@@ -9301,7 +9301,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>26.866418838501</v>
+        <v>26.8664207458496</v>
       </c>
       <c r="H308" t="n">
         <v>56</v>
@@ -9330,7 +9330,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G309" t="n">
-        <v>26.3100147247314</v>
+        <v>26.3100166320801</v>
       </c>
       <c r="H309" t="n">
         <v>337</v>
@@ -9388,7 +9388,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G311" t="n">
-        <v>26.1510429382324</v>
+        <v>26.1510448455811</v>
       </c>
       <c r="H311" t="n">
         <v>173</v>
@@ -9417,7 +9417,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G312" t="n">
-        <v>26.1510429382324</v>
+        <v>26.1510448455811</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G313" t="n">
-        <v>26.3100147247314</v>
+        <v>26.3100166320801</v>
       </c>
       <c r="H313" t="n">
         <v>115</v>
@@ -9475,7 +9475,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G314" t="n">
-        <v>26.3100147247314</v>
+        <v>26.3100166320801</v>
       </c>
       <c r="H314" t="n">
         <v>444</v>
@@ -9707,7 +9707,7 @@
         <v>32.5</v>
       </c>
       <c r="G322" t="n">
-        <v>25.8330955505371</v>
+        <v>25.8330974578857</v>
       </c>
       <c r="H322" t="n">
         <v>105</v>
@@ -9852,7 +9852,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G327" t="n">
-        <v>27.5818023681641</v>
+        <v>27.5818004608154</v>
       </c>
       <c r="H327" t="n">
         <v>379</v>
@@ -9881,7 +9881,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G328" t="n">
-        <v>27.5818023681641</v>
+        <v>27.5818004608154</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -10200,7 +10200,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G339" t="n">
-        <v>26.866418838501</v>
+        <v>26.8664207458496</v>
       </c>
       <c r="H339" t="n">
         <v>1080</v>
@@ -10229,7 +10229,7 @@
         <v>34</v>
       </c>
       <c r="G340" t="n">
-        <v>27.0253944396973</v>
+        <v>27.0253982543945</v>
       </c>
       <c r="H340" t="n">
         <v>782</v>
@@ -10287,7 +10287,7 @@
         <v>34</v>
       </c>
       <c r="G342" t="n">
-        <v>27.0253944396973</v>
+        <v>27.0253982543945</v>
       </c>
       <c r="H342" t="n">
         <v>296</v>
@@ -10316,7 +10316,7 @@
         <v>34</v>
       </c>
       <c r="G343" t="n">
-        <v>27.0253944396973</v>
+        <v>27.0253982543945</v>
       </c>
       <c r="H343" t="n">
         <v>1116</v>
@@ -10345,7 +10345,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G344" t="n">
-        <v>26.9459075927734</v>
+        <v>26.9459095001221</v>
       </c>
       <c r="H344" t="n">
         <v>207</v>
@@ -10432,7 +10432,7 @@
         <v>34</v>
       </c>
       <c r="G347" t="n">
-        <v>27.0253944396973</v>
+        <v>27.0253982543945</v>
       </c>
       <c r="H347" t="n">
         <v>403</v>
@@ -10461,7 +10461,7 @@
         <v>34</v>
       </c>
       <c r="G348" t="n">
-        <v>27.0253944396973</v>
+        <v>27.0253982543945</v>
       </c>
       <c r="H348" t="n">
         <v>754</v>
@@ -10490,7 +10490,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G349" t="n">
-        <v>26.707447052002</v>
+        <v>26.7074489593506</v>
       </c>
       <c r="H349" t="n">
         <v>7509</v>
@@ -10519,7 +10519,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G350" t="n">
-        <v>26.866418838501</v>
+        <v>26.8664207458496</v>
       </c>
       <c r="H350" t="n">
         <v>55</v>
@@ -10577,7 +10577,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>26.1510429382324</v>
+        <v>26.1510448455811</v>
       </c>
       <c r="H352" t="n">
         <v>199</v>
@@ -10664,7 +10664,7 @@
         <v>32.5</v>
       </c>
       <c r="G355" t="n">
-        <v>25.8330955505371</v>
+        <v>25.8330974578857</v>
       </c>
       <c r="H355" t="n">
         <v>4783</v>
@@ -10867,7 +10867,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G362" t="n">
-        <v>23.6074771881104</v>
+        <v>23.6074733734131</v>
       </c>
       <c r="H362" t="n">
         <v>467</v>
@@ -11128,7 +11128,7 @@
         <v>28</v>
       </c>
       <c r="G371" t="n">
-        <v>22.2562065124512</v>
+        <v>22.2562084197998</v>
       </c>
       <c r="H371" t="n">
         <v>5395</v>
@@ -11186,7 +11186,7 @@
         <v>28</v>
       </c>
       <c r="G373" t="n">
-        <v>22.2562065124512</v>
+        <v>22.2562084197998</v>
       </c>
       <c r="H373" t="n">
         <v>2214</v>
@@ -11244,7 +11244,7 @@
         <v>27</v>
       </c>
       <c r="G375" t="n">
-        <v>21.4613418579102</v>
+        <v>21.4613437652588</v>
       </c>
       <c r="H375" t="n">
         <v>1525</v>
@@ -11273,7 +11273,7 @@
         <v>27</v>
       </c>
       <c r="G376" t="n">
-        <v>21.4613418579102</v>
+        <v>21.4613437652588</v>
       </c>
       <c r="H376" t="n">
         <v>903</v>
@@ -11331,7 +11331,7 @@
         <v>27</v>
       </c>
       <c r="G378" t="n">
-        <v>21.4613418579102</v>
+        <v>21.4613437652588</v>
       </c>
       <c r="H378" t="n">
         <v>29935</v>
@@ -11360,7 +11360,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G379" t="n">
-        <v>21.6203174591064</v>
+        <v>21.6203155517578</v>
       </c>
       <c r="H379" t="n">
         <v>3312</v>
@@ -11389,7 +11389,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G380" t="n">
-        <v>21.7792892456055</v>
+        <v>21.7792873382568</v>
       </c>
       <c r="H380" t="n">
         <v>1996</v>
@@ -11418,7 +11418,7 @@
         <v>27</v>
       </c>
       <c r="G381" t="n">
-        <v>21.4613418579102</v>
+        <v>21.4613437652588</v>
       </c>
       <c r="H381" t="n">
         <v>946</v>
@@ -11476,7 +11476,7 @@
         <v>26.7000007629395</v>
       </c>
       <c r="G383" t="n">
-        <v>21.2228851318359</v>
+        <v>21.2228813171387</v>
       </c>
       <c r="H383" t="n">
         <v>1395</v>
@@ -11563,7 +11563,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G386" t="n">
-        <v>20.3485336303711</v>
+        <v>20.3485317230225</v>
       </c>
       <c r="H386" t="n">
         <v>1178</v>
@@ -11650,7 +11650,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>20.5869903564453</v>
+        <v>20.5869884490967</v>
       </c>
       <c r="H389" t="n">
         <v>1005</v>
@@ -11737,7 +11737,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G392" t="n">
-        <v>20.3485336303711</v>
+        <v>20.3485317230225</v>
       </c>
       <c r="H392" t="n">
         <v>654</v>
@@ -11766,7 +11766,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>20.3485336303711</v>
+        <v>20.3485317230225</v>
       </c>
       <c r="H393" t="n">
         <v>583</v>
@@ -11795,7 +11795,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G394" t="n">
-        <v>20.4280204772949</v>
+        <v>20.4280185699463</v>
       </c>
       <c r="H394" t="n">
         <v>674</v>
@@ -11911,7 +11911,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G398" t="n">
-        <v>19.2357215881348</v>
+        <v>19.2357234954834</v>
       </c>
       <c r="H398" t="n">
         <v>494</v>
@@ -11940,7 +11940,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G399" t="n">
-        <v>18.9177742004395</v>
+        <v>18.9177761077881</v>
       </c>
       <c r="H399" t="n">
         <v>7009</v>
@@ -11998,7 +11998,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G401" t="n">
-        <v>19.31520652771</v>
+        <v>19.3152084350586</v>
       </c>
       <c r="H401" t="n">
         <v>4009</v>
@@ -12027,7 +12027,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G402" t="n">
-        <v>18.9972591400146</v>
+        <v>18.9972610473633</v>
       </c>
       <c r="H402" t="n">
         <v>1449</v>
@@ -12056,7 +12056,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G403" t="n">
-        <v>19.1562347412109</v>
+        <v>19.1562366485596</v>
       </c>
       <c r="H403" t="n">
         <v>920</v>
@@ -12085,7 +12085,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G404" t="n">
-        <v>18.9972591400146</v>
+        <v>18.9972610473633</v>
       </c>
       <c r="H404" t="n">
         <v>1062</v>
@@ -12230,7 +12230,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G409" t="n">
-        <v>17.5665054321289</v>
+        <v>17.5665073394775</v>
       </c>
       <c r="H409" t="n">
         <v>4448</v>
@@ -12259,7 +12259,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G410" t="n">
-        <v>17.4075317382812</v>
+        <v>17.4075298309326</v>
       </c>
       <c r="H410" t="n">
         <v>522</v>
@@ -12288,7 +12288,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G411" t="n">
-        <v>18.9972591400146</v>
+        <v>18.9972610473633</v>
       </c>
       <c r="H411" t="n">
         <v>9367</v>
@@ -12317,7 +12317,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G412" t="n">
-        <v>18.9972591400146</v>
+        <v>18.9972610473633</v>
       </c>
       <c r="H412" t="n">
         <v>278</v>
@@ -12346,7 +12346,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>18.7588024139404</v>
+        <v>18.7588043212891</v>
       </c>
       <c r="H413" t="n">
         <v>898</v>
@@ -12375,7 +12375,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G414" t="n">
-        <v>18.8382892608643</v>
+        <v>18.8382873535156</v>
       </c>
       <c r="H414" t="n">
         <v>3279</v>
@@ -12404,7 +12404,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G415" t="n">
-        <v>18.3613681793213</v>
+        <v>18.3613719940186</v>
       </c>
       <c r="H415" t="n">
         <v>3296</v>
@@ -12433,7 +12433,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>18.0434246063232</v>
+        <v>18.0434265136719</v>
       </c>
       <c r="H416" t="n">
         <v>1957</v>
@@ -12462,7 +12462,7 @@
         <v>22</v>
       </c>
       <c r="G417" t="n">
-        <v>17.4870185852051</v>
+        <v>17.4870204925537</v>
       </c>
       <c r="H417" t="n">
         <v>15218</v>
@@ -12491,7 +12491,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G418" t="n">
-        <v>17.2485599517822</v>
+        <v>17.2485618591309</v>
       </c>
       <c r="H418" t="n">
         <v>2600</v>
@@ -12520,7 +12520,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G419" t="n">
-        <v>17.2485599517822</v>
+        <v>17.2485618591309</v>
       </c>
       <c r="H419" t="n">
         <v>1727</v>
@@ -12607,7 +12607,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G422" t="n">
-        <v>16.056266784668</v>
+        <v>16.0562686920166</v>
       </c>
       <c r="H422" t="n">
         <v>16513</v>
@@ -12636,7 +12636,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G423" t="n">
-        <v>16.6126670837402</v>
+        <v>16.6126689910889</v>
       </c>
       <c r="H423" t="n">
         <v>5251</v>
@@ -12665,7 +12665,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G424" t="n">
-        <v>16.3742084503174</v>
+        <v>16.374210357666</v>
       </c>
       <c r="H424" t="n">
         <v>1326</v>
@@ -12723,7 +12723,7 @@
         <v>20</v>
       </c>
       <c r="G426" t="n">
-        <v>15.8972911834717</v>
+        <v>15.8972902297974</v>
       </c>
       <c r="H426" t="n">
         <v>3491</v>
@@ -12752,7 +12752,7 @@
         <v>20</v>
       </c>
       <c r="G427" t="n">
-        <v>15.8972911834717</v>
+        <v>15.8972902297974</v>
       </c>
       <c r="H427" t="n">
         <v>14751</v>
@@ -12781,7 +12781,7 @@
         <v>20</v>
       </c>
       <c r="G428" t="n">
-        <v>15.8972911834717</v>
+        <v>15.8972902297974</v>
       </c>
       <c r="H428" t="n">
         <v>2023</v>
@@ -12897,7 +12897,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G432" t="n">
-        <v>16.8511295318604</v>
+        <v>16.851131439209</v>
       </c>
       <c r="H432" t="n">
         <v>1865</v>
@@ -12955,7 +12955,7 @@
         <v>20.5</v>
       </c>
       <c r="G434" t="n">
-        <v>16.2947216033936</v>
+        <v>16.2947235107422</v>
       </c>
       <c r="H434" t="n">
         <v>2791</v>
@@ -12984,7 +12984,7 @@
         <v>20.5</v>
       </c>
       <c r="G435" t="n">
-        <v>16.2947216033936</v>
+        <v>16.2947235107422</v>
       </c>
       <c r="H435" t="n">
         <v>25692</v>
@@ -13071,7 +13071,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G438" t="n">
-        <v>16.6126670837402</v>
+        <v>16.6126689910889</v>
       </c>
       <c r="H438" t="n">
         <v>15823</v>
@@ -13216,7 +13216,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G443" t="n">
-        <v>16.8511295318604</v>
+        <v>16.851131439209</v>
       </c>
       <c r="H443" t="n">
         <v>7517</v>
@@ -13245,7 +13245,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G444" t="n">
-        <v>17.6459941864014</v>
+        <v>17.64599609375</v>
       </c>
       <c r="H444" t="n">
         <v>6729</v>
@@ -13274,7 +13274,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G445" t="n">
-        <v>18.0434246063232</v>
+        <v>18.0434265136719</v>
       </c>
       <c r="H445" t="n">
         <v>3143</v>
@@ -13390,7 +13390,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G449" t="n">
-        <v>18.9177742004395</v>
+        <v>18.9177761077881</v>
       </c>
       <c r="H449" t="n">
         <v>7589</v>
@@ -13419,7 +13419,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G450" t="n">
-        <v>18.9177742004395</v>
+        <v>18.9177761077881</v>
       </c>
       <c r="H450" t="n">
         <v>4613</v>
@@ -13564,7 +13564,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G455" t="n">
-        <v>18.8382892608643</v>
+        <v>18.8382873535156</v>
       </c>
       <c r="H455" t="n">
         <v>1707</v>
@@ -13622,7 +13622,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G457" t="n">
-        <v>18.9972591400146</v>
+        <v>18.9972610473633</v>
       </c>
       <c r="H457" t="n">
         <v>6301</v>
@@ -13680,7 +13680,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G459" t="n">
-        <v>18.4408569335938</v>
+        <v>18.4408588409424</v>
       </c>
       <c r="H459" t="n">
         <v>1927</v>
@@ -13738,7 +13738,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G461" t="n">
-        <v>18.2023983001709</v>
+        <v>18.2023963928223</v>
       </c>
       <c r="H461" t="n">
         <v>743</v>
@@ -13854,7 +13854,7 @@
         <v>22.5</v>
       </c>
       <c r="G465" t="n">
-        <v>17.8844509124756</v>
+        <v>17.8844528198242</v>
       </c>
       <c r="H465" t="n">
         <v>8120</v>
@@ -13883,7 +13883,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G466" t="n">
-        <v>18.0434246063232</v>
+        <v>18.0434265136719</v>
       </c>
       <c r="H466" t="n">
         <v>3574</v>
@@ -13912,7 +13912,7 @@
         <v>22.5</v>
       </c>
       <c r="G467" t="n">
-        <v>17.8844509124756</v>
+        <v>17.8844528198242</v>
       </c>
       <c r="H467" t="n">
         <v>274</v>
@@ -14028,7 +14028,7 @@
         <v>22</v>
       </c>
       <c r="G471" t="n">
-        <v>17.4870185852051</v>
+        <v>17.4870204925537</v>
       </c>
       <c r="H471" t="n">
         <v>1728</v>
@@ -14086,7 +14086,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G473" t="n">
-        <v>17.6459941864014</v>
+        <v>17.64599609375</v>
       </c>
       <c r="H473" t="n">
         <v>647</v>
@@ -14115,7 +14115,7 @@
         <v>22</v>
       </c>
       <c r="G474" t="n">
-        <v>17.4870185852051</v>
+        <v>17.4870204925537</v>
       </c>
       <c r="H474" t="n">
         <v>1509</v>
@@ -14144,7 +14144,7 @@
         <v>22.5</v>
       </c>
       <c r="G475" t="n">
-        <v>17.8844509124756</v>
+        <v>17.8844528198242</v>
       </c>
       <c r="H475" t="n">
         <v>1005</v>
@@ -14173,7 +14173,7 @@
         <v>22.5</v>
       </c>
       <c r="G476" t="n">
-        <v>17.8844509124756</v>
+        <v>17.8844528198242</v>
       </c>
       <c r="H476" t="n">
         <v>2510</v>
@@ -14231,7 +14231,7 @@
         <v>22.5</v>
       </c>
       <c r="G478" t="n">
-        <v>17.8844509124756</v>
+        <v>17.8844528198242</v>
       </c>
       <c r="H478" t="n">
         <v>1276</v>
@@ -14376,7 +14376,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G483" t="n">
-        <v>18.2023983001709</v>
+        <v>18.2023963928223</v>
       </c>
       <c r="H483" t="n">
         <v>4379</v>
@@ -14405,7 +14405,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G484" t="n">
-        <v>18.7588024139404</v>
+        <v>18.7588043212891</v>
       </c>
       <c r="H484" t="n">
         <v>27488</v>
@@ -14434,7 +14434,7 @@
         <v>23.5</v>
       </c>
       <c r="G485" t="n">
-        <v>18.6793155670166</v>
+        <v>18.6793174743652</v>
       </c>
       <c r="H485" t="n">
         <v>8828</v>
@@ -14463,7 +14463,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>18.9177742004395</v>
+        <v>18.9177761077881</v>
       </c>
       <c r="H486" t="n">
         <v>1116</v>
@@ -14492,7 +14492,7 @@
         <v>23.5</v>
       </c>
       <c r="G487" t="n">
-        <v>18.6793155670166</v>
+        <v>18.6793174743652</v>
       </c>
       <c r="H487" t="n">
         <v>5247</v>
@@ -14521,7 +14521,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G488" t="n">
-        <v>18.9972591400146</v>
+        <v>18.9972610473633</v>
       </c>
       <c r="H488" t="n">
         <v>9602</v>
@@ -14637,7 +14637,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>18.3613681793213</v>
+        <v>18.3613719940186</v>
       </c>
       <c r="H492" t="n">
         <v>1587</v>
@@ -14666,7 +14666,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G493" t="n">
-        <v>18.4408569335938</v>
+        <v>18.4408588409424</v>
       </c>
       <c r="H493" t="n">
         <v>726</v>
@@ -14724,7 +14724,7 @@
         <v>22.5</v>
       </c>
       <c r="G495" t="n">
-        <v>17.8844509124756</v>
+        <v>17.8844528198242</v>
       </c>
       <c r="H495" t="n">
         <v>1729</v>
@@ -14782,7 +14782,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G497" t="n">
-        <v>17.5665054321289</v>
+        <v>17.5665073394775</v>
       </c>
       <c r="H497" t="n">
         <v>1702</v>
@@ -14811,7 +14811,7 @@
         <v>22</v>
       </c>
       <c r="G498" t="n">
-        <v>17.4870185852051</v>
+        <v>17.4870204925537</v>
       </c>
       <c r="H498" t="n">
         <v>2724</v>
@@ -14927,7 +14927,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G502" t="n">
-        <v>17.5665054321289</v>
+        <v>17.5665073394775</v>
       </c>
       <c r="H502" t="n">
         <v>2130</v>
@@ -14956,7 +14956,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>17.5665054321289</v>
+        <v>17.5665073394775</v>
       </c>
       <c r="H503" t="n">
         <v>7496</v>
@@ -15101,7 +15101,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G508" t="n">
-        <v>18.0434246063232</v>
+        <v>18.0434265136719</v>
       </c>
       <c r="H508" t="n">
         <v>886</v>
@@ -15217,7 +15217,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G512" t="n">
-        <v>17.9607887268066</v>
+        <v>17.9607906341553</v>
       </c>
       <c r="H512" t="n">
         <v>1659</v>
@@ -15246,7 +15246,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G513" t="n">
-        <v>17.8787746429443</v>
+        <v>17.878776550293</v>
       </c>
       <c r="H513" t="n">
         <v>1292</v>
@@ -15420,7 +15420,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>17.3046875</v>
+        <v>17.3046894073486</v>
       </c>
       <c r="H519" t="n">
         <v>759</v>
@@ -15623,7 +15623,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G526" t="n">
-        <v>17.8787746429443</v>
+        <v>17.878776550293</v>
       </c>
       <c r="H526" t="n">
         <v>511</v>
@@ -15652,7 +15652,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G527" t="n">
-        <v>17.8787746429443</v>
+        <v>17.878776550293</v>
       </c>
       <c r="H527" t="n">
         <v>190</v>
@@ -15710,7 +15710,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G529" t="n">
-        <v>18.2068290710449</v>
+        <v>18.2068309783936</v>
       </c>
       <c r="H529" t="n">
         <v>1591</v>
@@ -15855,7 +15855,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G534" t="n">
-        <v>19.0269546508789</v>
+        <v>19.0269565582275</v>
       </c>
       <c r="H534" t="n">
         <v>12571</v>
@@ -15884,7 +15884,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>19.3550052642822</v>
+        <v>19.3550071716309</v>
       </c>
       <c r="H535" t="n">
         <v>6266</v>
@@ -15913,7 +15913,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G536" t="n">
-        <v>19.3550052642822</v>
+        <v>19.3550071716309</v>
       </c>
       <c r="H536" t="n">
         <v>1787</v>
@@ -16000,7 +16000,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>19.4370193481445</v>
+        <v>19.4370174407959</v>
       </c>
       <c r="H539" t="n">
         <v>6199</v>
@@ -16116,7 +16116,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G543" t="n">
-        <v>19.0269546508789</v>
+        <v>19.0269565582275</v>
       </c>
       <c r="H543" t="n">
         <v>1643</v>
@@ -16232,7 +16232,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G547" t="n">
-        <v>18.2068290710449</v>
+        <v>18.2068309783936</v>
       </c>
       <c r="H547" t="n">
         <v>4868</v>
@@ -16261,7 +16261,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>17.9607887268066</v>
+        <v>17.9607906341553</v>
       </c>
       <c r="H548" t="n">
         <v>2398</v>
@@ -16928,7 +16928,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G571" t="n">
-        <v>17.8787746429443</v>
+        <v>17.878776550293</v>
       </c>
       <c r="H571" t="n">
         <v>550</v>
@@ -17769,7 +17769,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G600" t="n">
-        <v>17.9607887268066</v>
+        <v>17.9607906341553</v>
       </c>
       <c r="H600" t="n">
         <v>5743</v>
@@ -17798,7 +17798,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G601" t="n">
-        <v>16.6485862731934</v>
+        <v>16.6485843658447</v>
       </c>
       <c r="H601" t="n">
         <v>22789</v>
@@ -17885,7 +17885,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G604" t="n">
-        <v>16.5665760040283</v>
+        <v>16.566577911377</v>
       </c>
       <c r="H604" t="n">
         <v>1273</v>
@@ -17914,7 +17914,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G605" t="n">
-        <v>16.5665760040283</v>
+        <v>16.566577911377</v>
       </c>
       <c r="H605" t="n">
         <v>1933</v>
@@ -17943,7 +17943,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G606" t="n">
-        <v>16.5665760040283</v>
+        <v>16.566577911377</v>
       </c>
       <c r="H606" t="n">
         <v>2565</v>
@@ -17972,7 +17972,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G607" t="n">
-        <v>16.5665760040283</v>
+        <v>16.566577911377</v>
       </c>
       <c r="H607" t="n">
         <v>875</v>
@@ -18030,7 +18030,7 @@
         <v>19.75</v>
       </c>
       <c r="G609" t="n">
-        <v>16.1975135803223</v>
+        <v>16.1975173950195</v>
       </c>
       <c r="H609" t="n">
         <v>5046</v>
@@ -18175,7 +18175,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G614" t="n">
-        <v>16.2385215759277</v>
+        <v>16.2385196685791</v>
       </c>
       <c r="H614" t="n">
         <v>2123</v>
@@ -18233,7 +18233,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G616" t="n">
-        <v>16.5665760040283</v>
+        <v>16.566577911377</v>
       </c>
       <c r="H616" t="n">
         <v>4471</v>
@@ -18262,7 +18262,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G617" t="n">
-        <v>16.6485862731934</v>
+        <v>16.6485843658447</v>
       </c>
       <c r="H617" t="n">
         <v>4776</v>
@@ -18291,7 +18291,7 @@
         <v>19.7999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>16.2385215759277</v>
+        <v>16.2385196685791</v>
       </c>
       <c r="H618" t="n">
         <v>3322</v>
@@ -18436,7 +18436,7 @@
         <v>19.75</v>
       </c>
       <c r="G623" t="n">
-        <v>16.1975135803223</v>
+        <v>16.1975173950195</v>
       </c>
       <c r="H623" t="n">
         <v>1916</v>
@@ -18494,7 +18494,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G625" t="n">
-        <v>15.459400177002</v>
+        <v>15.4594020843506</v>
       </c>
       <c r="H625" t="n">
         <v>17116</v>
@@ -18523,7 +18523,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G626" t="n">
-        <v>15.459400177002</v>
+        <v>15.4594020843506</v>
       </c>
       <c r="H626" t="n">
         <v>4871</v>
@@ -18552,7 +18552,7 @@
         <v>19</v>
       </c>
       <c r="G627" t="n">
-        <v>15.5824203491211</v>
+        <v>15.5824213027954</v>
       </c>
       <c r="H627" t="n">
         <v>3868</v>
@@ -18581,7 +18581,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G628" t="n">
-        <v>15.5414142608643</v>
+        <v>15.5414133071899</v>
       </c>
       <c r="H628" t="n">
         <v>2723</v>
@@ -18610,7 +18610,7 @@
         <v>19</v>
       </c>
       <c r="G629" t="n">
-        <v>15.5824203491211</v>
+        <v>15.5824213027954</v>
       </c>
       <c r="H629" t="n">
         <v>2109</v>
@@ -18639,7 +18639,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G630" t="n">
-        <v>15.6234254837036</v>
+        <v>15.6234264373779</v>
       </c>
       <c r="H630" t="n">
         <v>4009</v>
@@ -18668,7 +18668,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G631" t="n">
-        <v>15.3363847732544</v>
+        <v>15.3363819122314</v>
       </c>
       <c r="H631" t="n">
         <v>2902</v>
@@ -18697,7 +18697,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G632" t="n">
-        <v>15.4183940887451</v>
+        <v>15.4183931350708</v>
       </c>
       <c r="H632" t="n">
         <v>1676</v>
@@ -18726,7 +18726,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G633" t="n">
-        <v>15.5004072189331</v>
+        <v>15.5004081726074</v>
       </c>
       <c r="H633" t="n">
         <v>3297</v>
@@ -18755,7 +18755,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G634" t="n">
-        <v>15.4183940887451</v>
+        <v>15.4183931350708</v>
       </c>
       <c r="H634" t="n">
         <v>7342</v>
@@ -18813,7 +18813,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>15.6234254837036</v>
+        <v>15.6234264373779</v>
       </c>
       <c r="H636" t="n">
         <v>6023</v>
@@ -18842,7 +18842,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G637" t="n">
-        <v>15.6234254837036</v>
+        <v>15.6234264373779</v>
       </c>
       <c r="H637" t="n">
         <v>1596</v>
@@ -18871,7 +18871,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>15.5004072189331</v>
+        <v>15.5004081726074</v>
       </c>
       <c r="H638" t="n">
         <v>3150</v>
@@ -18900,7 +18900,7 @@
         <v>19</v>
       </c>
       <c r="G639" t="n">
-        <v>15.5824203491211</v>
+        <v>15.5824213027954</v>
       </c>
       <c r="H639" t="n">
         <v>2084</v>
@@ -18929,7 +18929,7 @@
         <v>19</v>
       </c>
       <c r="G640" t="n">
-        <v>15.5824203491211</v>
+        <v>15.5824213027954</v>
       </c>
       <c r="H640" t="n">
         <v>3268</v>
@@ -18958,7 +18958,7 @@
         <v>19</v>
       </c>
       <c r="G641" t="n">
-        <v>15.5824203491211</v>
+        <v>15.5824213027954</v>
       </c>
       <c r="H641" t="n">
         <v>1572</v>
@@ -19103,7 +19103,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G646" t="n">
-        <v>16.6485862731934</v>
+        <v>16.6485843658447</v>
       </c>
       <c r="H646" t="n">
         <v>9521</v>
@@ -19161,7 +19161,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>16.8946228027344</v>
+        <v>16.894624710083</v>
       </c>
       <c r="H648" t="n">
         <v>6135</v>
@@ -19190,7 +19190,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G649" t="n">
-        <v>17.140661239624</v>
+        <v>17.1406631469727</v>
       </c>
       <c r="H649" t="n">
         <v>6947</v>
@@ -19219,7 +19219,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>17.0586490631104</v>
+        <v>17.0586471557617</v>
       </c>
       <c r="H650" t="n">
         <v>4387</v>
@@ -19335,7 +19335,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G654" t="n">
-        <v>16.8946228027344</v>
+        <v>16.894624710083</v>
       </c>
       <c r="H654" t="n">
         <v>426</v>
@@ -19451,7 +19451,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G658" t="n">
-        <v>17.7147521972656</v>
+        <v>17.714750289917</v>
       </c>
       <c r="H658" t="n">
         <v>9712</v>
@@ -19509,7 +19509,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>17.4687099456787</v>
+        <v>17.4687118530273</v>
       </c>
       <c r="H660" t="n">
         <v>1613</v>
@@ -19567,7 +19567,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G662" t="n">
-        <v>17.4687099456787</v>
+        <v>17.4687118530273</v>
       </c>
       <c r="H662" t="n">
         <v>2438</v>
@@ -19654,7 +19654,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G665" t="n">
-        <v>17.3046875</v>
+        <v>17.3046894073486</v>
       </c>
       <c r="H665" t="n">
         <v>2352</v>
@@ -19683,7 +19683,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>17.4687099456787</v>
+        <v>17.4687118530273</v>
       </c>
       <c r="H666" t="n">
         <v>926</v>
@@ -19712,7 +19712,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G667" t="n">
-        <v>17.0586490631104</v>
+        <v>17.0586471557617</v>
       </c>
       <c r="H667" t="n">
         <v>2724</v>
@@ -19741,7 +19741,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G668" t="n">
-        <v>17.3046875</v>
+        <v>17.3046894073486</v>
       </c>
       <c r="H668" t="n">
         <v>815</v>
@@ -19770,7 +19770,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G669" t="n">
-        <v>17.0586490631104</v>
+        <v>17.0586471557617</v>
       </c>
       <c r="H669" t="n">
         <v>1234</v>
@@ -19799,7 +19799,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G670" t="n">
-        <v>17.0586490631104</v>
+        <v>17.0586471557617</v>
       </c>
       <c r="H670" t="n">
         <v>752</v>
@@ -19886,7 +19886,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G673" t="n">
-        <v>16.8946228027344</v>
+        <v>16.894624710083</v>
       </c>
       <c r="H673" t="n">
         <v>1156</v>
@@ -19915,7 +19915,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G674" t="n">
-        <v>17.140661239624</v>
+        <v>17.1406631469727</v>
       </c>
       <c r="H674" t="n">
         <v>520</v>
@@ -19944,7 +19944,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>17.0586490631104</v>
+        <v>17.0586471557617</v>
       </c>
       <c r="H675" t="n">
         <v>1749</v>
@@ -20002,7 +20002,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G677" t="n">
-        <v>17.0586490631104</v>
+        <v>17.0586471557617</v>
       </c>
       <c r="H677" t="n">
         <v>604</v>
@@ -20031,7 +20031,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G678" t="n">
-        <v>16.8946228027344</v>
+        <v>16.894624710083</v>
       </c>
       <c r="H678" t="n">
         <v>2221</v>
@@ -20060,7 +20060,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G679" t="n">
-        <v>16.8946228027344</v>
+        <v>16.894624710083</v>
       </c>
       <c r="H679" t="n">
         <v>4007</v>
@@ -20118,7 +20118,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G681" t="n">
-        <v>17.140661239624</v>
+        <v>17.1406631469727</v>
       </c>
       <c r="H681" t="n">
         <v>763</v>
@@ -20176,7 +20176,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G683" t="n">
-        <v>17.8787746429443</v>
+        <v>17.878776550293</v>
       </c>
       <c r="H683" t="n">
         <v>6727</v>
@@ -20379,7 +20379,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G690" t="n">
-        <v>17.0586490631104</v>
+        <v>17.0586471557617</v>
       </c>
       <c r="H690" t="n">
         <v>187</v>
@@ -20408,7 +20408,7 @@
         <v>20.5</v>
       </c>
       <c r="G691" t="n">
-        <v>16.8126106262207</v>
+        <v>16.8126125335693</v>
       </c>
       <c r="H691" t="n">
         <v>1369</v>
@@ -20437,7 +20437,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G692" t="n">
-        <v>16.6485862731934</v>
+        <v>16.6485843658447</v>
       </c>
       <c r="H692" t="n">
         <v>1683</v>
@@ -20466,7 +20466,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>16.6485862731934</v>
+        <v>16.6485843658447</v>
       </c>
       <c r="H693" t="n">
         <v>2674</v>
@@ -20495,7 +20495,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G694" t="n">
-        <v>16.6485862731934</v>
+        <v>16.6485843658447</v>
       </c>
       <c r="H694" t="n">
         <v>120</v>
@@ -20524,7 +20524,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G695" t="n">
-        <v>16.5665760040283</v>
+        <v>16.566577911377</v>
       </c>
       <c r="H695" t="n">
         <v>1097</v>
@@ -20669,7 +20669,7 @@
         <v>19.25</v>
       </c>
       <c r="G700" t="n">
-        <v>15.7874536514282</v>
+        <v>15.7874526977539</v>
       </c>
       <c r="H700" t="n">
         <v>3945</v>
@@ -20698,7 +20698,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G701" t="n">
-        <v>15.0903425216675</v>
+        <v>15.0903434753418</v>
       </c>
       <c r="H701" t="n">
         <v>4572</v>
@@ -20727,7 +20727,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G702" t="n">
-        <v>15.0083332061768</v>
+        <v>15.0083322525024</v>
       </c>
       <c r="H702" t="n">
         <v>349</v>
@@ -20756,7 +20756,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G703" t="n">
-        <v>14.8443059921265</v>
+        <v>14.8443069458008</v>
       </c>
       <c r="H703" t="n">
         <v>2786</v>
@@ -20785,7 +20785,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G704" t="n">
-        <v>15.0083332061768</v>
+        <v>15.0083322525024</v>
       </c>
       <c r="H704" t="n">
         <v>2211</v>
@@ -20843,7 +20843,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G706" t="n">
-        <v>14.7212886810303</v>
+        <v>14.721287727356</v>
       </c>
       <c r="H706" t="n">
         <v>2844</v>
@@ -20901,7 +20901,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G708" t="n">
-        <v>14.229211807251</v>
+        <v>14.2292108535767</v>
       </c>
       <c r="H708" t="n">
         <v>1701</v>
@@ -20959,7 +20959,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G710" t="n">
-        <v>12.6709671020508</v>
+        <v>12.6709680557251</v>
       </c>
       <c r="H710" t="n">
         <v>3678</v>
@@ -20988,7 +20988,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>11.6048030853271</v>
+        <v>11.6048021316528</v>
       </c>
       <c r="H711" t="n">
         <v>2777</v>
@@ -21046,7 +21046,7 @@
         <v>14.75</v>
       </c>
       <c r="G713" t="n">
-        <v>12.0968790054321</v>
+        <v>12.0968780517578</v>
       </c>
       <c r="H713" t="n">
         <v>1260</v>
@@ -21075,7 +21075,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>11.153733253479</v>
+        <v>11.1537322998047</v>
       </c>
       <c r="H714" t="n">
         <v>1224</v>
@@ -21104,7 +21104,7 @@
         <v>14.75</v>
       </c>
       <c r="G715" t="n">
-        <v>12.0968790054321</v>
+        <v>12.0968780517578</v>
       </c>
       <c r="H715" t="n">
         <v>1071</v>
@@ -21133,7 +21133,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>11.153733253479</v>
+        <v>11.1537322998047</v>
       </c>
       <c r="H716" t="n">
         <v>558</v>
@@ -21162,7 +21162,7 @@
         <v>13.5</v>
       </c>
       <c r="G717" t="n">
-        <v>11.0717191696167</v>
+        <v>11.071720123291</v>
       </c>
       <c r="H717" t="n">
         <v>538</v>
@@ -21278,7 +21278,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>10.5386381149292</v>
+        <v>10.5386371612549</v>
       </c>
       <c r="H721" t="n">
         <v>655</v>
@@ -21307,7 +21307,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G722" t="n">
-        <v>10.9076948165894</v>
+        <v>10.907693862915</v>
       </c>
       <c r="H722" t="n">
         <v>4997</v>
@@ -21336,7 +21336,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>10.5386381149292</v>
+        <v>10.5386371612549</v>
       </c>
       <c r="H723" t="n">
         <v>3859</v>
@@ -21423,7 +21423,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>10.3336057662964</v>
+        <v>10.3336048126221</v>
       </c>
       <c r="H726" t="n">
         <v>1049</v>
@@ -21452,7 +21452,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G727" t="n">
-        <v>10.4156188964844</v>
+        <v>10.4156179428101</v>
       </c>
       <c r="H727" t="n">
         <v>1497</v>
@@ -21481,7 +21481,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G728" t="n">
-        <v>10.0875663757324</v>
+        <v>10.0875673294067</v>
       </c>
       <c r="H728" t="n">
         <v>1910</v>
@@ -21597,7 +21597,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>10.3336057662964</v>
+        <v>10.3336048126221</v>
       </c>
       <c r="H732" t="n">
         <v>5385</v>
@@ -21684,7 +21684,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G735" t="n">
-        <v>10.497631072998</v>
+        <v>10.4976301193237</v>
       </c>
       <c r="H735" t="n">
         <v>7117</v>
@@ -21742,7 +21742,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>10.7026634216309</v>
+        <v>10.7026624679565</v>
       </c>
       <c r="H737" t="n">
         <v>8882</v>
@@ -21771,7 +21771,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>12.2609043121338</v>
+        <v>12.2609052658081</v>
       </c>
       <c r="H738" t="n">
         <v>16838</v>
@@ -21800,7 +21800,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>11.7688293457031</v>
+        <v>11.7688283920288</v>
       </c>
       <c r="H739" t="n">
         <v>12484</v>
@@ -21829,7 +21829,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>11.7688293457031</v>
+        <v>11.7688283920288</v>
       </c>
       <c r="H740" t="n">
         <v>3570</v>
@@ -21858,7 +21858,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G741" t="n">
-        <v>11.7278232574463</v>
+        <v>11.7278213500977</v>
       </c>
       <c r="H741" t="n">
         <v>4602</v>
@@ -21887,7 +21887,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>11.6048030853271</v>
+        <v>11.6048021316528</v>
       </c>
       <c r="H742" t="n">
         <v>3261</v>
@@ -21916,7 +21916,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>11.6048030853271</v>
+        <v>11.6048021316528</v>
       </c>
       <c r="H743" t="n">
         <v>2653</v>
@@ -21945,7 +21945,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G744" t="n">
-        <v>11.7278232574463</v>
+        <v>11.7278213500977</v>
       </c>
       <c r="H744" t="n">
         <v>5199</v>
@@ -21974,7 +21974,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>11.5637969970703</v>
+        <v>11.563796043396</v>
       </c>
       <c r="H745" t="n">
         <v>2919</v>
@@ -22032,7 +22032,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G747" t="n">
-        <v>11.8508396148682</v>
+        <v>11.8508415222168</v>
       </c>
       <c r="H747" t="n">
         <v>3116</v>
@@ -22061,7 +22061,7 @@
         <v>14</v>
       </c>
       <c r="G748" t="n">
-        <v>11.481782913208</v>
+        <v>11.4817848205566</v>
       </c>
       <c r="H748" t="n">
         <v>2932</v>
@@ -22148,7 +22148,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>11.3587646484375</v>
+        <v>11.3587636947632</v>
       </c>
       <c r="H751" t="n">
         <v>401</v>
@@ -22177,7 +22177,7 @@
         <v>13.5</v>
       </c>
       <c r="G752" t="n">
-        <v>11.0717191696167</v>
+        <v>11.071720123291</v>
       </c>
       <c r="H752" t="n">
         <v>1046</v>
@@ -22235,7 +22235,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>10.3336057662964</v>
+        <v>10.3336048126221</v>
       </c>
       <c r="H754" t="n">
         <v>4207</v>
@@ -22293,7 +22293,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G756" t="n">
-        <v>10.3746128082275</v>
+        <v>10.3746109008789</v>
       </c>
       <c r="H756" t="n">
         <v>1446</v>
@@ -22322,7 +22322,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G757" t="n">
-        <v>10.497631072998</v>
+        <v>10.4976301193237</v>
       </c>
       <c r="H757" t="n">
         <v>683</v>
@@ -22380,7 +22380,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G759" t="n">
-        <v>10.497631072998</v>
+        <v>10.4976301193237</v>
       </c>
       <c r="H759" t="n">
         <v>1720</v>
@@ -22409,7 +22409,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G760" t="n">
-        <v>10.4156188964844</v>
+        <v>10.4156179428101</v>
       </c>
       <c r="H760" t="n">
         <v>2262</v>
@@ -22438,7 +22438,7 @@
         <v>13.5</v>
       </c>
       <c r="G761" t="n">
-        <v>11.0717191696167</v>
+        <v>11.071720123291</v>
       </c>
       <c r="H761" t="n">
         <v>4874</v>
@@ -22496,7 +22496,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G763" t="n">
-        <v>12.2609043121338</v>
+        <v>12.2609052658081</v>
       </c>
       <c r="H763" t="n">
         <v>6623</v>
@@ -22583,7 +22583,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G766" t="n">
-        <v>11.9328546524048</v>
+        <v>11.9328527450562</v>
       </c>
       <c r="H766" t="n">
         <v>1916</v>
@@ -22670,7 +22670,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G769" t="n">
-        <v>12.2609043121338</v>
+        <v>12.2609052658081</v>
       </c>
       <c r="H769" t="n">
         <v>2050</v>
@@ -22757,7 +22757,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>12.4249296188354</v>
+        <v>12.4249286651611</v>
       </c>
       <c r="H772" t="n">
         <v>4778</v>
@@ -22815,7 +22815,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G774" t="n">
-        <v>14.393235206604</v>
+        <v>14.3932342529297</v>
       </c>
       <c r="H774" t="n">
         <v>15355</v>
@@ -22844,7 +22844,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G775" t="n">
-        <v>14.475248336792</v>
+        <v>14.4752492904663</v>
       </c>
       <c r="H775" t="n">
         <v>5461</v>
@@ -22873,7 +22873,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G776" t="n">
-        <v>13.4500885009766</v>
+        <v>13.4500894546509</v>
       </c>
       <c r="H776" t="n">
         <v>4519</v>
@@ -23047,7 +23047,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G782" t="n">
-        <v>12.9580135345459</v>
+        <v>12.9580116271973</v>
       </c>
       <c r="H782" t="n">
         <v>819</v>
@@ -23076,7 +23076,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G783" t="n">
-        <v>12.6709671020508</v>
+        <v>12.6709680557251</v>
       </c>
       <c r="H783" t="n">
         <v>379</v>
@@ -23308,7 +23308,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G791" t="n">
-        <v>13.0810317993164</v>
+        <v>13.0810327529907</v>
       </c>
       <c r="H791" t="n">
         <v>1933</v>
@@ -23482,7 +23482,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>13.0400247573853</v>
+        <v>13.0400257110596</v>
       </c>
       <c r="H797" t="n">
         <v>1010</v>
@@ -23598,7 +23598,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G801" t="n">
-        <v>13.3680753707886</v>
+        <v>13.3680763244629</v>
       </c>
       <c r="H801" t="n">
         <v>2946</v>
@@ -23627,7 +23627,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G802" t="n">
-        <v>13.3680753707886</v>
+        <v>13.3680763244629</v>
       </c>
       <c r="H802" t="n">
         <v>2515</v>
@@ -23656,7 +23656,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>13.3680753707886</v>
+        <v>13.3680763244629</v>
       </c>
       <c r="H803" t="n">
         <v>128</v>
@@ -23714,7 +23714,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G805" t="n">
-        <v>13.0810317993164</v>
+        <v>13.0810327529907</v>
       </c>
       <c r="H805" t="n">
         <v>88</v>
@@ -23743,7 +23743,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>13.0400247573853</v>
+        <v>13.0400257110596</v>
       </c>
       <c r="H806" t="n">
         <v>1344</v>
@@ -23917,7 +23917,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>12.7529821395874</v>
+        <v>12.7529811859131</v>
       </c>
       <c r="H812" t="n">
         <v>350</v>
@@ -23946,7 +23946,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>12.6299600601196</v>
+        <v>12.6299610137939</v>
       </c>
       <c r="H813" t="n">
         <v>510</v>
@@ -23975,7 +23975,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G814" t="n">
-        <v>12.6299600601196</v>
+        <v>12.6299610137939</v>
       </c>
       <c r="H814" t="n">
         <v>0</v>
@@ -24120,7 +24120,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G819" t="n">
-        <v>12.8349924087524</v>
+        <v>12.8349933624268</v>
       </c>
       <c r="H819" t="n">
         <v>460</v>
@@ -24149,7 +24149,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G820" t="n">
-        <v>12.8349924087524</v>
+        <v>12.8349933624268</v>
       </c>
       <c r="H820" t="n">
         <v>925</v>
@@ -24178,7 +24178,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>12.8349924087524</v>
+        <v>12.8349933624268</v>
       </c>
       <c r="H821" t="n">
         <v>0</v>
@@ -24207,7 +24207,7 @@
         <v>15.75</v>
       </c>
       <c r="G822" t="n">
-        <v>12.9170055389404</v>
+        <v>12.9170064926147</v>
       </c>
       <c r="H822" t="n">
         <v>30</v>
@@ -24236,7 +24236,7 @@
         <v>15.25</v>
       </c>
       <c r="G823" t="n">
-        <v>12.5069427490234</v>
+        <v>12.5069417953491</v>
       </c>
       <c r="H823" t="n">
         <v>729</v>
@@ -24265,7 +24265,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G824" t="n">
-        <v>12.8349924087524</v>
+        <v>12.8349933624268</v>
       </c>
       <c r="H824" t="n">
         <v>378</v>
@@ -24352,7 +24352,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G827" t="n">
-        <v>12.6299600601196</v>
+        <v>12.6299610137939</v>
       </c>
       <c r="H827" t="n">
         <v>15</v>
@@ -24410,7 +24410,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>12.6709671020508</v>
+        <v>12.6709680557251</v>
       </c>
       <c r="H829" t="n">
         <v>2591</v>
@@ -24468,7 +24468,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G831" t="n">
-        <v>12.9580135345459</v>
+        <v>12.9580116271973</v>
       </c>
       <c r="H831" t="n">
         <v>423</v>
@@ -24497,7 +24497,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G832" t="n">
-        <v>12.8349924087524</v>
+        <v>12.8349933624268</v>
       </c>
       <c r="H832" t="n">
         <v>2211</v>
@@ -24526,7 +24526,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G833" t="n">
-        <v>12.9580135345459</v>
+        <v>12.9580116271973</v>
       </c>
       <c r="H833" t="n">
         <v>25</v>
@@ -24555,7 +24555,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G834" t="n">
-        <v>13.0810317993164</v>
+        <v>13.0810327529907</v>
       </c>
       <c r="H834" t="n">
         <v>916</v>
@@ -24584,7 +24584,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G835" t="n">
-        <v>13.0400247573853</v>
+        <v>13.0400257110596</v>
       </c>
       <c r="H835" t="n">
         <v>4585</v>
@@ -24787,7 +24787,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G842" t="n">
-        <v>13.3680753707886</v>
+        <v>13.3680763244629</v>
       </c>
       <c r="H842" t="n">
         <v>890</v>
@@ -24816,7 +24816,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G843" t="n">
-        <v>13.3680753707886</v>
+        <v>13.3680763244629</v>
       </c>
       <c r="H843" t="n">
         <v>644</v>
@@ -24845,7 +24845,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G844" t="n">
-        <v>13.3680753707886</v>
+        <v>13.3680763244629</v>
       </c>
       <c r="H844" t="n">
         <v>0</v>
@@ -24874,7 +24874,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G845" t="n">
-        <v>13.6961269378662</v>
+        <v>13.6961259841919</v>
       </c>
       <c r="H845" t="n">
         <v>706</v>
@@ -24903,7 +24903,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>13.5731077194214</v>
+        <v>13.5731086730957</v>
       </c>
       <c r="H846" t="n">
         <v>332</v>
@@ -24990,7 +24990,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G849" t="n">
-        <v>12.6709671020508</v>
+        <v>12.6709680557251</v>
       </c>
       <c r="H849" t="n">
         <v>1517</v>
@@ -25077,7 +25077,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>12.6299600601196</v>
+        <v>12.6299610137939</v>
       </c>
       <c r="H852" t="n">
         <v>7688</v>
@@ -25135,7 +25135,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G854" t="n">
-        <v>13.6961269378662</v>
+        <v>13.6961259841919</v>
       </c>
       <c r="H854" t="n">
         <v>4189</v>
@@ -25193,7 +25193,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G856" t="n">
-        <v>14.229211807251</v>
+        <v>14.2292108535767</v>
       </c>
       <c r="H856" t="n">
         <v>4704</v>
@@ -25222,7 +25222,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G857" t="n">
-        <v>14.4342422485352</v>
+        <v>14.4342412948608</v>
       </c>
       <c r="H857" t="n">
         <v>643</v>
@@ -25251,7 +25251,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G858" t="n">
-        <v>14.2702159881592</v>
+        <v>14.2702169418335</v>
       </c>
       <c r="H858" t="n">
         <v>1566</v>
@@ -25280,7 +25280,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G859" t="n">
-        <v>14.5162563323975</v>
+        <v>14.5162553787231</v>
       </c>
       <c r="H859" t="n">
         <v>708</v>
@@ -25309,7 +25309,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>14.475248336792</v>
+        <v>14.4752492904663</v>
       </c>
       <c r="H860" t="n">
         <v>632</v>
@@ -25338,7 +25338,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G861" t="n">
-        <v>14.1882028579712</v>
+        <v>14.1882038116455</v>
       </c>
       <c r="H861" t="n">
         <v>2534</v>
@@ -25367,7 +25367,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G862" t="n">
-        <v>14.5982685089111</v>
+        <v>14.5982656478882</v>
       </c>
       <c r="H862" t="n">
         <v>2852</v>
@@ -25396,7 +25396,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G863" t="n">
-        <v>14.4342422485352</v>
+        <v>14.4342412948608</v>
       </c>
       <c r="H863" t="n">
         <v>4831</v>
@@ -25425,7 +25425,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G864" t="n">
-        <v>14.475248336792</v>
+        <v>14.4752492904663</v>
       </c>
       <c r="H864" t="n">
         <v>3572</v>
@@ -25454,7 +25454,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G865" t="n">
-        <v>14.5982685089111</v>
+        <v>14.5982656478882</v>
       </c>
       <c r="H865" t="n">
         <v>2262</v>
@@ -25541,7 +25541,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>14.1061916351318</v>
+        <v>14.1061925888062</v>
       </c>
       <c r="H868" t="n">
         <v>2660</v>
@@ -25570,7 +25570,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G869" t="n">
-        <v>14.229211807251</v>
+        <v>14.2292108535767</v>
       </c>
       <c r="H869" t="n">
         <v>1134</v>
@@ -25657,7 +25657,7 @@
         <v>17</v>
       </c>
       <c r="G872" t="n">
-        <v>13.9421653747559</v>
+        <v>13.9421663284302</v>
       </c>
       <c r="H872" t="n">
         <v>2985</v>
@@ -25686,7 +25686,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G873" t="n">
-        <v>13.7781391143799</v>
+        <v>13.7781400680542</v>
       </c>
       <c r="H873" t="n">
         <v>820</v>
@@ -25715,7 +25715,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G874" t="n">
-        <v>14.1882028579712</v>
+        <v>14.1882038116455</v>
       </c>
       <c r="H874" t="n">
         <v>325</v>
@@ -25802,7 +25802,7 @@
         <v>17</v>
       </c>
       <c r="G877" t="n">
-        <v>13.9421653747559</v>
+        <v>13.9421663284302</v>
       </c>
       <c r="H877" t="n">
         <v>2600</v>
@@ -25918,7 +25918,7 @@
         <v>17</v>
       </c>
       <c r="G881" t="n">
-        <v>13.9421653747559</v>
+        <v>13.9421663284302</v>
       </c>
       <c r="H881" t="n">
         <v>1780</v>
@@ -25947,7 +25947,7 @@
         <v>17</v>
       </c>
       <c r="G882" t="n">
-        <v>13.9421653747559</v>
+        <v>13.9421663284302</v>
       </c>
       <c r="H882" t="n">
         <v>1743</v>
@@ -25976,7 +25976,7 @@
         <v>17</v>
       </c>
       <c r="G883" t="n">
-        <v>13.9421653747559</v>
+        <v>13.9421663284302</v>
       </c>
       <c r="H883" t="n">
         <v>6738</v>
@@ -26005,7 +26005,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G884" t="n">
-        <v>14.4342422485352</v>
+        <v>14.4342412948608</v>
       </c>
       <c r="H884" t="n">
         <v>4887</v>
@@ -26034,7 +26034,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G885" t="n">
-        <v>14.5162563323975</v>
+        <v>14.5162553787231</v>
       </c>
       <c r="H885" t="n">
         <v>1090</v>
@@ -26092,7 +26092,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G887" t="n">
-        <v>14.5982685089111</v>
+        <v>14.5982656478882</v>
       </c>
       <c r="H887" t="n">
         <v>4610</v>
@@ -26121,7 +26121,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>14.8443059921265</v>
+        <v>14.8443069458008</v>
       </c>
       <c r="H888" t="n">
         <v>2964</v>
@@ -26150,7 +26150,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>14.9263200759888</v>
+        <v>14.9263172149658</v>
       </c>
       <c r="H889" t="n">
         <v>2167</v>
@@ -26179,7 +26179,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G890" t="n">
-        <v>15.3363847732544</v>
+        <v>15.3363819122314</v>
       </c>
       <c r="H890" t="n">
         <v>11840</v>
@@ -26266,7 +26266,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G893" t="n">
-        <v>16.6485862731934</v>
+        <v>16.6485843658447</v>
       </c>
       <c r="H893" t="n">
         <v>8649</v>
@@ -26295,7 +26295,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>16.4845581054688</v>
+        <v>16.4845600128174</v>
       </c>
       <c r="H894" t="n">
         <v>3196</v>
@@ -26324,7 +26324,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G895" t="n">
-        <v>17.4687099456787</v>
+        <v>17.4687118530273</v>
       </c>
       <c r="H895" t="n">
         <v>8208</v>
@@ -26353,7 +26353,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>17.4687099456787</v>
+        <v>17.4687118530273</v>
       </c>
       <c r="H896" t="n">
         <v>7593</v>
@@ -26382,7 +26382,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G897" t="n">
-        <v>18.2068290710449</v>
+        <v>18.2068309783936</v>
       </c>
       <c r="H897" t="n">
         <v>4287</v>
@@ -26585,7 +26585,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>18.2068290710449</v>
+        <v>18.2068309783936</v>
       </c>
       <c r="H904" t="n">
         <v>2051</v>
@@ -26643,7 +26643,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G906" t="n">
-        <v>17.7147521972656</v>
+        <v>17.714750289917</v>
       </c>
       <c r="H906" t="n">
         <v>8791</v>
@@ -27136,7 +27136,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G923" t="n">
-        <v>18.9449405670166</v>
+        <v>18.9449443817139</v>
       </c>
       <c r="H923" t="n">
         <v>1918</v>
@@ -27165,7 +27165,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G924" t="n">
-        <v>18.9449405670166</v>
+        <v>18.9449443817139</v>
       </c>
       <c r="H924" t="n">
         <v>5571</v>
@@ -27194,7 +27194,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>18.9449405670166</v>
+        <v>18.9449443817139</v>
       </c>
       <c r="H925" t="n">
         <v>3393</v>
@@ -27223,7 +27223,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>18.9449405670166</v>
+        <v>18.9449443817139</v>
       </c>
       <c r="H926" t="n">
         <v>3955</v>
@@ -27252,7 +27252,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G927" t="n">
-        <v>19.0269546508789</v>
+        <v>19.0269565582275</v>
       </c>
       <c r="H927" t="n">
         <v>2862</v>
@@ -27426,7 +27426,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G933" t="n">
-        <v>19.7650699615479</v>
+        <v>19.7650737762451</v>
       </c>
       <c r="H933" t="n">
         <v>4398</v>
@@ -27455,7 +27455,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G934" t="n">
-        <v>19.7650699615479</v>
+        <v>19.7650737762451</v>
       </c>
       <c r="H934" t="n">
         <v>6151</v>
@@ -27484,7 +27484,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G935" t="n">
-        <v>20.1751327514648</v>
+        <v>20.1751346588135</v>
       </c>
       <c r="H935" t="n">
         <v>2991</v>
@@ -27513,7 +27513,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G936" t="n">
-        <v>20.0111064910889</v>
+        <v>20.0111083984375</v>
       </c>
       <c r="H936" t="n">
         <v>714</v>
@@ -27542,7 +27542,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G937" t="n">
-        <v>20.1751327514648</v>
+        <v>20.1751346588135</v>
       </c>
       <c r="H937" t="n">
         <v>1420</v>
@@ -27571,7 +27571,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G938" t="n">
-        <v>20.1751327514648</v>
+        <v>20.1751346588135</v>
       </c>
       <c r="H938" t="n">
         <v>4081</v>
@@ -27716,7 +27716,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G943" t="n">
-        <v>20.1751327514648</v>
+        <v>20.1751346588135</v>
       </c>
       <c r="H943" t="n">
         <v>940</v>
@@ -27745,7 +27745,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G944" t="n">
-        <v>20.6672115325928</v>
+        <v>20.6672096252441</v>
       </c>
       <c r="H944" t="n">
         <v>3195</v>
@@ -27919,7 +27919,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>21.4053268432617</v>
+        <v>21.4053249359131</v>
       </c>
       <c r="H950" t="n">
         <v>1757</v>
@@ -28064,7 +28064,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G955" t="n">
-        <v>20.8312377929688</v>
+        <v>20.8312358856201</v>
       </c>
       <c r="H955" t="n">
         <v>1664</v>
@@ -28209,7 +28209,7 @@
         <v>24.5</v>
       </c>
       <c r="G960" t="n">
-        <v>20.0931186676025</v>
+        <v>20.0931205749512</v>
       </c>
       <c r="H960" t="n">
         <v>395</v>
@@ -28267,7 +28267,7 @@
         <v>24.5</v>
       </c>
       <c r="G962" t="n">
-        <v>20.0931186676025</v>
+        <v>20.0931205749512</v>
       </c>
       <c r="H962" t="n">
         <v>476</v>
@@ -28296,7 +28296,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G963" t="n">
-        <v>20.7492256164551</v>
+        <v>20.7492218017578</v>
       </c>
       <c r="H963" t="n">
         <v>2984</v>
@@ -28412,7 +28412,7 @@
         <v>24.5</v>
       </c>
       <c r="G967" t="n">
-        <v>20.0931186676025</v>
+        <v>20.0931205749512</v>
       </c>
       <c r="H967" t="n">
         <v>634</v>
@@ -28441,7 +28441,7 @@
         <v>24.5</v>
       </c>
       <c r="G968" t="n">
-        <v>20.0931186676025</v>
+        <v>20.0931205749512</v>
       </c>
       <c r="H968" t="n">
         <v>1198</v>
@@ -28789,7 +28789,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G980" t="n">
-        <v>20.6672115325928</v>
+        <v>20.6672096252441</v>
       </c>
       <c r="H980" t="n">
         <v>250</v>
@@ -28818,7 +28818,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G981" t="n">
-        <v>20.7492256164551</v>
+        <v>20.7492218017578</v>
       </c>
       <c r="H981" t="n">
         <v>239</v>
@@ -28963,7 +28963,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G986" t="n">
-        <v>20.8312377929688</v>
+        <v>20.8312358856201</v>
       </c>
       <c r="H986" t="n">
         <v>829</v>
@@ -29079,7 +29079,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G990" t="n">
-        <v>21.0772762298584</v>
+        <v>21.0772743225098</v>
       </c>
       <c r="H990" t="n">
         <v>229</v>
@@ -29108,7 +29108,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G991" t="n">
-        <v>20.6672115325928</v>
+        <v>20.6672096252441</v>
       </c>
       <c r="H991" t="n">
         <v>6130</v>
@@ -29195,7 +29195,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G994" t="n">
-        <v>19.7650699615479</v>
+        <v>19.7650737762451</v>
       </c>
       <c r="H994" t="n">
         <v>3593</v>
@@ -29253,7 +29253,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G996" t="n">
-        <v>19.6010417938232</v>
+        <v>19.6010456085205</v>
       </c>
       <c r="H996" t="n">
         <v>2860</v>
@@ -29311,7 +29311,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G998" t="n">
-        <v>19.0269546508789</v>
+        <v>19.0269565582275</v>
       </c>
       <c r="H998" t="n">
         <v>6069</v>
@@ -29369,7 +29369,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1000" t="n">
-        <v>18.9449405670166</v>
+        <v>18.9449443817139</v>
       </c>
       <c r="H1000" t="n">
         <v>8055</v>
@@ -29514,7 +29514,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1005" t="n">
-        <v>20.0111064910889</v>
+        <v>20.0111083984375</v>
       </c>
       <c r="H1005" t="n">
         <v>493</v>
@@ -29572,7 +29572,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1007" t="n">
-        <v>21.0772762298584</v>
+        <v>21.0772743225098</v>
       </c>
       <c r="H1007" t="n">
         <v>8574</v>
@@ -29659,7 +29659,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1010" t="n">
-        <v>20.8312377929688</v>
+        <v>20.8312358856201</v>
       </c>
       <c r="H1010" t="n">
         <v>1592</v>
@@ -29688,7 +29688,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1011" t="n">
-        <v>20.6672115325928</v>
+        <v>20.6672096252441</v>
       </c>
       <c r="H1011" t="n">
         <v>573</v>
@@ -29717,7 +29717,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1012" t="n">
-        <v>20.7492256164551</v>
+        <v>20.7492218017578</v>
       </c>
       <c r="H1012" t="n">
         <v>2078</v>
@@ -29746,7 +29746,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1013" t="n">
-        <v>20.8312377929688</v>
+        <v>20.8312358856201</v>
       </c>
       <c r="H1013" t="n">
         <v>700</v>
@@ -29804,7 +29804,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1015" t="n">
-        <v>20.9952621459961</v>
+        <v>20.9952602386475</v>
       </c>
       <c r="H1015" t="n">
         <v>456</v>
@@ -29833,7 +29833,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1016" t="n">
-        <v>21.0772762298584</v>
+        <v>21.0772743225098</v>
       </c>
       <c r="H1016" t="n">
         <v>179</v>
@@ -29891,7 +29891,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1018" t="n">
-        <v>20.6672115325928</v>
+        <v>20.6672096252441</v>
       </c>
       <c r="H1018" t="n">
         <v>96</v>
@@ -29949,7 +29949,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1020" t="n">
-        <v>20.9952621459961</v>
+        <v>20.9952602386475</v>
       </c>
       <c r="H1020" t="n">
         <v>1748</v>
@@ -29978,7 +29978,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1021" t="n">
-        <v>21.0772762298584</v>
+        <v>21.0772743225098</v>
       </c>
       <c r="H1021" t="n">
         <v>6170</v>
@@ -30065,7 +30065,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1024" t="n">
-        <v>21.0103073120117</v>
+        <v>21.0103092193604</v>
       </c>
       <c r="H1024" t="n">
         <v>1349</v>
@@ -30152,7 +30152,7 @@
         <v>25.5</v>
       </c>
       <c r="G1027" t="n">
-        <v>21.3451328277588</v>
+        <v>21.3451347351074</v>
       </c>
       <c r="H1027" t="n">
         <v>1679</v>
@@ -30239,7 +30239,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>21.0103073120117</v>
+        <v>21.0103092193604</v>
       </c>
       <c r="H1030" t="n">
         <v>1310</v>
@@ -30268,7 +30268,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1031" t="n">
-        <v>21.2614269256592</v>
+        <v>21.2614288330078</v>
       </c>
       <c r="H1031" t="n">
         <v>641</v>
@@ -30326,7 +30326,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>21.8473720550537</v>
+        <v>21.8473739624023</v>
       </c>
       <c r="H1033" t="n">
         <v>4959</v>
@@ -30355,7 +30355,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1034" t="n">
-        <v>21.8473720550537</v>
+        <v>21.8473739624023</v>
       </c>
       <c r="H1034" t="n">
         <v>5723</v>
@@ -30732,7 +30732,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>22.0984897613525</v>
+        <v>22.0984916687012</v>
       </c>
       <c r="H1047" t="n">
         <v>1862</v>
@@ -30877,7 +30877,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1052" t="n">
-        <v>21.8473720550537</v>
+        <v>21.8473739624023</v>
       </c>
       <c r="H1052" t="n">
         <v>230</v>
@@ -30964,7 +30964,7 @@
         <v>24</v>
       </c>
       <c r="G1055" t="n">
-        <v>20.0895366668701</v>
+        <v>20.0895385742188</v>
       </c>
       <c r="H1055" t="n">
         <v>6882</v>
@@ -31080,7 +31080,7 @@
         <v>24</v>
       </c>
       <c r="G1059" t="n">
-        <v>20.0895366668701</v>
+        <v>20.0895385742188</v>
       </c>
       <c r="H1059" t="n">
         <v>657</v>
@@ -31196,7 +31196,7 @@
         <v>24</v>
       </c>
       <c r="G1063" t="n">
-        <v>20.0895366668701</v>
+        <v>20.0895385742188</v>
       </c>
       <c r="H1063" t="n">
         <v>293</v>
@@ -31312,7 +31312,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1067" t="n">
-        <v>21.2614269256592</v>
+        <v>21.2614288330078</v>
       </c>
       <c r="H1067" t="n">
         <v>1938</v>
@@ -31370,7 +31370,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>21.8473720550537</v>
+        <v>21.8473739624023</v>
       </c>
       <c r="H1069" t="n">
         <v>1934</v>
@@ -31573,7 +31573,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1076" t="n">
-        <v>20.591775894165</v>
+        <v>20.5917778015137</v>
       </c>
       <c r="H1076" t="n">
         <v>5487</v>
@@ -31776,7 +31776,7 @@
         <v>25.5</v>
       </c>
       <c r="G1083" t="n">
-        <v>21.3451328277588</v>
+        <v>21.3451347351074</v>
       </c>
       <c r="H1083" t="n">
         <v>975</v>
@@ -31834,7 +31834,7 @@
         <v>25.5</v>
       </c>
       <c r="G1085" t="n">
-        <v>21.3451328277588</v>
+        <v>21.3451347351074</v>
       </c>
       <c r="H1085" t="n">
         <v>5249</v>
@@ -31921,7 +31921,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1088" t="n">
-        <v>21.2614269256592</v>
+        <v>21.2614288330078</v>
       </c>
       <c r="H1088" t="n">
         <v>19553</v>
@@ -32211,7 +32211,7 @@
         <v>25.5</v>
       </c>
       <c r="G1098" t="n">
-        <v>21.3451328277588</v>
+        <v>21.3451347351074</v>
       </c>
       <c r="H1098" t="n">
         <v>1242</v>
@@ -32240,7 +32240,7 @@
         <v>25.5</v>
       </c>
       <c r="G1099" t="n">
-        <v>21.3451328277588</v>
+        <v>21.3451347351074</v>
       </c>
       <c r="H1099" t="n">
         <v>0</v>
@@ -32472,7 +32472,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1107" t="n">
-        <v>22.6844348907471</v>
+        <v>22.6844367980957</v>
       </c>
       <c r="H1107" t="n">
         <v>2122</v>
@@ -32501,7 +32501,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1108" t="n">
-        <v>21.8473720550537</v>
+        <v>21.8473739624023</v>
       </c>
       <c r="H1108" t="n">
         <v>2719</v>
@@ -32530,7 +32530,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1109" t="n">
-        <v>22.0984897613525</v>
+        <v>22.0984916687012</v>
       </c>
       <c r="H1109" t="n">
         <v>1523</v>
@@ -32617,7 +32617,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1112" t="n">
-        <v>22.0984897613525</v>
+        <v>22.0984916687012</v>
       </c>
       <c r="H1112" t="n">
         <v>4368</v>
@@ -32849,7 +32849,7 @@
         <v>27</v>
       </c>
       <c r="G1120" t="n">
-        <v>22.6007308959961</v>
+        <v>22.6007289886475</v>
       </c>
       <c r="H1120" t="n">
         <v>4240</v>
@@ -32907,7 +32907,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1122" t="n">
-        <v>22.4333152770996</v>
+        <v>22.4333171844482</v>
       </c>
       <c r="H1122" t="n">
         <v>211</v>
@@ -32936,7 +32936,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1123" t="n">
-        <v>22.0984897613525</v>
+        <v>22.0984916687012</v>
       </c>
       <c r="H1123" t="n">
         <v>175</v>
@@ -33052,7 +33052,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1127" t="n">
-        <v>22.4333152770996</v>
+        <v>22.4333171844482</v>
       </c>
       <c r="H1127" t="n">
         <v>670</v>
@@ -33168,7 +33168,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1131" t="n">
-        <v>22.4333152770996</v>
+        <v>22.4333171844482</v>
       </c>
       <c r="H1131" t="n">
         <v>1670</v>
@@ -33313,7 +33313,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1136" t="n">
-        <v>22.6844348907471</v>
+        <v>22.6844367980957</v>
       </c>
       <c r="H1136" t="n">
         <v>1323</v>
@@ -33342,7 +33342,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1137" t="n">
-        <v>22.6844348907471</v>
+        <v>22.6844367980957</v>
       </c>
       <c r="H1137" t="n">
         <v>614</v>
@@ -33400,7 +33400,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1139" t="n">
-        <v>22.6844348907471</v>
+        <v>22.6844367980957</v>
       </c>
       <c r="H1139" t="n">
         <v>1592</v>
@@ -33458,7 +33458,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1141" t="n">
-        <v>22.6844348907471</v>
+        <v>22.6844367980957</v>
       </c>
       <c r="H1141" t="n">
         <v>729</v>
@@ -33487,7 +33487,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1142" t="n">
-        <v>22.4333152770996</v>
+        <v>22.4333171844482</v>
       </c>
       <c r="H1142" t="n">
         <v>513</v>
@@ -33516,7 +33516,7 @@
         <v>27.1000003814697</v>
       </c>
       <c r="G1143" t="n">
-        <v>22.6844348907471</v>
+        <v>22.6844367980957</v>
       </c>
       <c r="H1143" t="n">
         <v>135</v>
@@ -33603,7 +33603,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1146" t="n">
-        <v>22.4333152770996</v>
+        <v>22.4333171844482</v>
       </c>
       <c r="H1146" t="n">
         <v>1275</v>
@@ -33777,7 +33777,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>22.0984897613525</v>
+        <v>22.0984916687012</v>
       </c>
       <c r="H1152" t="n">
         <v>901</v>
@@ -33864,7 +33864,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1155" t="n">
-        <v>22.0984897613525</v>
+        <v>22.0984916687012</v>
       </c>
       <c r="H1155" t="n">
         <v>1742</v>
@@ -34038,7 +34038,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1161" t="n">
-        <v>21.8473720550537</v>
+        <v>21.8473739624023</v>
       </c>
       <c r="H1161" t="n">
         <v>1419</v>
@@ -34299,7 +34299,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>21.2614269256592</v>
+        <v>21.2614288330078</v>
       </c>
       <c r="H1170" t="n">
         <v>992</v>
@@ -34415,7 +34415,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1174" t="n">
-        <v>22.4333152770996</v>
+        <v>22.4333171844482</v>
       </c>
       <c r="H1174" t="n">
         <v>6007</v>
@@ -34879,7 +34879,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1190" t="n">
-        <v>20.591775894165</v>
+        <v>20.5917778015137</v>
       </c>
       <c r="H1190" t="n">
         <v>1003</v>
@@ -34937,7 +34937,7 @@
         <v>25</v>
       </c>
       <c r="G1192" t="n">
-        <v>20.9265995025635</v>
+        <v>20.9266014099121</v>
       </c>
       <c r="H1192" t="n">
         <v>789</v>
@@ -34995,7 +34995,7 @@
         <v>25</v>
       </c>
       <c r="G1194" t="n">
-        <v>20.9265995025635</v>
+        <v>20.9266014099121</v>
       </c>
       <c r="H1194" t="n">
         <v>422</v>
@@ -35140,7 +35140,7 @@
         <v>25.5</v>
       </c>
       <c r="G1199" t="n">
-        <v>21.3451328277588</v>
+        <v>21.3451347351074</v>
       </c>
       <c r="H1199" t="n">
         <v>889</v>
@@ -35256,7 +35256,7 @@
         <v>25</v>
       </c>
       <c r="G1203" t="n">
-        <v>20.9265995025635</v>
+        <v>20.9266014099121</v>
       </c>
       <c r="H1203" t="n">
         <v>2856</v>
@@ -35285,7 +35285,7 @@
         <v>25</v>
       </c>
       <c r="G1204" t="n">
-        <v>20.9265995025635</v>
+        <v>20.9266014099121</v>
       </c>
       <c r="H1204" t="n">
         <v>0</v>
@@ -35401,7 +35401,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1208" t="n">
-        <v>20.591775894165</v>
+        <v>20.5917778015137</v>
       </c>
       <c r="H1208" t="n">
         <v>395</v>
@@ -35488,7 +35488,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1211" t="n">
-        <v>20.3406543731689</v>
+        <v>20.3406562805176</v>
       </c>
       <c r="H1211" t="n">
         <v>134</v>
@@ -35517,7 +35517,7 @@
         <v>24</v>
       </c>
       <c r="G1212" t="n">
-        <v>20.0895366668701</v>
+        <v>20.0895385742188</v>
       </c>
       <c r="H1212" t="n">
         <v>1734</v>
@@ -35633,7 +35633,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1216" t="n">
-        <v>19.5873012542725</v>
+        <v>19.5872993469238</v>
       </c>
       <c r="H1216" t="n">
         <v>2114</v>
@@ -35662,7 +35662,7 @@
         <v>24</v>
       </c>
       <c r="G1217" t="n">
-        <v>20.0895366668701</v>
+        <v>20.0895385742188</v>
       </c>
       <c r="H1217" t="n">
         <v>5601</v>
@@ -35691,7 +35691,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1218" t="n">
-        <v>20.3406543731689</v>
+        <v>20.3406562805176</v>
       </c>
       <c r="H1218" t="n">
         <v>1092</v>
@@ -35720,7 +35720,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1219" t="n">
-        <v>19.5873012542725</v>
+        <v>19.5872993469238</v>
       </c>
       <c r="H1219" t="n">
         <v>1361</v>
@@ -35749,7 +35749,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1220" t="n">
-        <v>18.4991188049316</v>
+        <v>18.499116897583</v>
       </c>
       <c r="H1220" t="n">
         <v>1096</v>
@@ -35865,7 +35865,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1224" t="n">
-        <v>17.9131717681885</v>
+        <v>17.9131698608398</v>
       </c>
       <c r="H1224" t="n">
         <v>20932</v>
@@ -35894,7 +35894,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1225" t="n">
-        <v>17.9131717681885</v>
+        <v>17.9131698608398</v>
       </c>
       <c r="H1225" t="n">
         <v>730</v>
@@ -35952,7 +35952,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1227" t="n">
-        <v>18.3317031860352</v>
+        <v>18.3317012786865</v>
       </c>
       <c r="H1227" t="n">
         <v>2353</v>
@@ -35981,7 +35981,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1228" t="n">
-        <v>18.3317031860352</v>
+        <v>18.3317012786865</v>
       </c>
       <c r="H1228" t="n">
         <v>67</v>
@@ -36068,7 +36068,7 @@
         <v>21.2999992370605</v>
       </c>
       <c r="G1231" t="n">
-        <v>17.8294639587402</v>
+        <v>17.8294658660889</v>
       </c>
       <c r="H1231" t="n">
         <v>1342</v>
@@ -36097,7 +36097,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1232" t="n">
-        <v>18.1642913818359</v>
+        <v>18.1642894744873</v>
       </c>
       <c r="H1232" t="n">
         <v>1517</v>
@@ -36155,7 +36155,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>18.3317031860352</v>
+        <v>18.3317012786865</v>
       </c>
       <c r="H1234" t="n">
         <v>190</v>
@@ -36213,7 +36213,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1236" t="n">
-        <v>19.5873012542725</v>
+        <v>19.5872993469238</v>
       </c>
       <c r="H1236" t="n">
         <v>1877</v>
@@ -36300,7 +36300,7 @@
         <v>24</v>
       </c>
       <c r="G1239" t="n">
-        <v>20.0895366668701</v>
+        <v>20.0895385742188</v>
       </c>
       <c r="H1239" t="n">
         <v>444</v>
@@ -36329,7 +36329,7 @@
         <v>24</v>
       </c>
       <c r="G1240" t="n">
-        <v>20.0895366668701</v>
+        <v>20.0895385742188</v>
       </c>
       <c r="H1240" t="n">
         <v>527</v>
@@ -36358,7 +36358,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1241" t="n">
-        <v>20.3406543731689</v>
+        <v>20.3406562805176</v>
       </c>
       <c r="H1241" t="n">
         <v>314</v>
@@ -36387,7 +36387,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1242" t="n">
-        <v>19.5873012542725</v>
+        <v>19.5872993469238</v>
       </c>
       <c r="H1242" t="n">
         <v>2087</v>
@@ -36416,7 +36416,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1243" t="n">
-        <v>19.5873012542725</v>
+        <v>19.5872993469238</v>
       </c>
       <c r="H1243" t="n">
         <v>118</v>
@@ -36445,7 +36445,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>19.5873012542725</v>
+        <v>19.5872993469238</v>
       </c>
       <c r="H1244" t="n">
         <v>0</v>
@@ -36474,7 +36474,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>19.5873012542725</v>
+        <v>19.5872993469238</v>
       </c>
       <c r="H1245" t="n">
         <v>759</v>
@@ -36735,7 +36735,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G1254" t="n">
-        <v>21.8473720550537</v>
+        <v>21.8473739624023</v>
       </c>
       <c r="H1254" t="n">
         <v>8460</v>
@@ -36938,7 +36938,7 @@
         <v>25</v>
       </c>
       <c r="G1261" t="n">
-        <v>20.9265995025635</v>
+        <v>20.9266014099121</v>
       </c>
       <c r="H1261" t="n">
         <v>160</v>
@@ -37083,7 +37083,7 @@
         <v>25.5</v>
       </c>
       <c r="G1266" t="n">
-        <v>21.3451328277588</v>
+        <v>21.3451347351074</v>
       </c>
       <c r="H1266" t="n">
         <v>70</v>
@@ -37112,7 +37112,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>21.2614269256592</v>
+        <v>21.2614288330078</v>
       </c>
       <c r="H1267" t="n">
         <v>804</v>
@@ -37141,7 +37141,7 @@
         <v>25</v>
       </c>
       <c r="G1268" t="n">
-        <v>20.9265995025635</v>
+        <v>20.9266014099121</v>
       </c>
       <c r="H1268" t="n">
         <v>3623</v>
@@ -37228,7 +37228,7 @@
         <v>25</v>
       </c>
       <c r="G1271" t="n">
-        <v>20.9265995025635</v>
+        <v>20.9266014099121</v>
       </c>
       <c r="H1271" t="n">
         <v>365</v>
@@ -37257,7 +37257,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1272" t="n">
-        <v>21.2614269256592</v>
+        <v>21.2614288330078</v>
       </c>
       <c r="H1272" t="n">
         <v>291</v>
@@ -37286,7 +37286,7 @@
         <v>25.5</v>
       </c>
       <c r="G1273" t="n">
-        <v>21.3451328277588</v>
+        <v>21.3451347351074</v>
       </c>
       <c r="H1273" t="n">
         <v>64</v>
@@ -37518,7 +37518,7 @@
         <v>25.5</v>
       </c>
       <c r="G1281" t="n">
-        <v>21.3451328277588</v>
+        <v>21.3451347351074</v>
       </c>
       <c r="H1281" t="n">
         <v>733</v>
@@ -37605,7 +37605,7 @@
         <v>25.5</v>
       </c>
       <c r="G1284" t="n">
-        <v>22.198938369751</v>
+        <v>22.1989402770996</v>
       </c>
       <c r="H1284" t="n">
         <v>1702</v>
@@ -37663,7 +37663,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>21.4154472351074</v>
+        <v>21.4154491424561</v>
       </c>
       <c r="H1286" t="n">
         <v>2031</v>
@@ -37721,7 +37721,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1288" t="n">
         <v>356</v>
@@ -37750,7 +37750,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1289" t="n">
-        <v>20.5449028015137</v>
+        <v>20.544900894165</v>
       </c>
       <c r="H1289" t="n">
         <v>1627</v>
@@ -37837,7 +37837,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1292" t="n">
-        <v>20.5449028015137</v>
+        <v>20.544900894165</v>
       </c>
       <c r="H1292" t="n">
         <v>300</v>
@@ -37982,7 +37982,7 @@
         <v>23.5</v>
       </c>
       <c r="G1297" t="n">
-        <v>20.4578456878662</v>
+        <v>20.4578475952148</v>
       </c>
       <c r="H1297" t="n">
         <v>300</v>
@@ -38011,7 +38011,7 @@
         <v>23.5</v>
       </c>
       <c r="G1298" t="n">
-        <v>20.4578456878662</v>
+        <v>20.4578475952148</v>
       </c>
       <c r="H1298" t="n">
         <v>0</v>
@@ -38040,7 +38040,7 @@
         <v>23.5</v>
       </c>
       <c r="G1299" t="n">
-        <v>20.4578456878662</v>
+        <v>20.4578475952148</v>
       </c>
       <c r="H1299" t="n">
         <v>32</v>
@@ -38069,7 +38069,7 @@
         <v>23.5</v>
       </c>
       <c r="G1300" t="n">
-        <v>20.4578456878662</v>
+        <v>20.4578475952148</v>
       </c>
       <c r="H1300" t="n">
         <v>0</v>
@@ -38214,7 +38214,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1305" t="n">
-        <v>20.5449028015137</v>
+        <v>20.544900894165</v>
       </c>
       <c r="H1305" t="n">
         <v>486</v>
@@ -38243,7 +38243,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1306" t="n">
-        <v>20.2837371826172</v>
+        <v>20.2837352752686</v>
       </c>
       <c r="H1306" t="n">
         <v>455</v>
@@ -38272,7 +38272,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>20.2837371826172</v>
+        <v>20.2837352752686</v>
       </c>
       <c r="H1307" t="n">
         <v>53</v>
@@ -38301,7 +38301,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1308" t="n">
         <v>458</v>
@@ -38330,7 +38330,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1309" t="n">
-        <v>19.9355201721191</v>
+        <v>19.9355182647705</v>
       </c>
       <c r="H1309" t="n">
         <v>263</v>
@@ -38359,7 +38359,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1310" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1310" t="n">
         <v>1124</v>
@@ -38388,7 +38388,7 @@
         <v>23.5</v>
       </c>
       <c r="G1311" t="n">
-        <v>20.4578456878662</v>
+        <v>20.4578475952148</v>
       </c>
       <c r="H1311" t="n">
         <v>2</v>
@@ -38417,7 +38417,7 @@
         <v>23.5</v>
       </c>
       <c r="G1312" t="n">
-        <v>20.4578456878662</v>
+        <v>20.4578475952148</v>
       </c>
       <c r="H1312" t="n">
         <v>0</v>
@@ -38446,7 +38446,7 @@
         <v>23.5</v>
       </c>
       <c r="G1313" t="n">
-        <v>20.4578456878662</v>
+        <v>20.4578475952148</v>
       </c>
       <c r="H1313" t="n">
         <v>71</v>
@@ -38475,7 +38475,7 @@
         <v>23.5</v>
       </c>
       <c r="G1314" t="n">
-        <v>20.4578456878662</v>
+        <v>20.4578475952148</v>
       </c>
       <c r="H1314" t="n">
         <v>0</v>
@@ -38823,7 +38823,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1326" t="n">
-        <v>21.1542816162109</v>
+        <v>21.1542835235596</v>
       </c>
       <c r="H1326" t="n">
         <v>220</v>
@@ -39171,7 +39171,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1338" t="n">
-        <v>20.5449028015137</v>
+        <v>20.544900894165</v>
       </c>
       <c r="H1338" t="n">
         <v>60</v>
@@ -39838,7 +39838,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1361" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1361" t="n">
         <v>1502</v>
@@ -39867,7 +39867,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1362" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1362" t="n">
         <v>0</v>
@@ -39896,7 +39896,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1363" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1363" t="n">
         <v>0</v>
@@ -39925,7 +39925,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1364" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1364" t="n">
         <v>200</v>
@@ -39954,7 +39954,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1365" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1365" t="n">
         <v>0</v>
@@ -40012,7 +40012,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1367" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1367" t="n">
         <v>785</v>
@@ -40099,7 +40099,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1370" t="n">
-        <v>20.2837371826172</v>
+        <v>20.2837352752686</v>
       </c>
       <c r="H1370" t="n">
         <v>518</v>
@@ -40128,7 +40128,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1371" t="n">
-        <v>20.2837371826172</v>
+        <v>20.2837352752686</v>
       </c>
       <c r="H1371" t="n">
         <v>0</v>
@@ -40273,7 +40273,7 @@
         <v>21</v>
       </c>
       <c r="G1376" t="n">
-        <v>18.2814807891846</v>
+        <v>18.2814788818359</v>
       </c>
       <c r="H1376" t="n">
         <v>2281</v>
@@ -40302,7 +40302,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1377" t="n">
-        <v>17.67209815979</v>
+        <v>17.6720962524414</v>
       </c>
       <c r="H1377" t="n">
         <v>4089</v>
@@ -40389,7 +40389,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1380" t="n">
-        <v>17.67209815979</v>
+        <v>17.6720962524414</v>
       </c>
       <c r="H1380" t="n">
         <v>252</v>
@@ -40418,7 +40418,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1381" t="n">
-        <v>17.67209815979</v>
+        <v>17.6720962524414</v>
       </c>
       <c r="H1381" t="n">
         <v>0</v>
@@ -40824,7 +40824,7 @@
         <v>19.9500007629395</v>
       </c>
       <c r="G1395" t="n">
-        <v>17.3674068450928</v>
+        <v>17.3674087524414</v>
       </c>
       <c r="H1395" t="n">
         <v>749</v>
@@ -40882,7 +40882,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G1397" t="n">
-        <v>19.4131908416748</v>
+        <v>19.4131889343262</v>
       </c>
       <c r="H1397" t="n">
         <v>5217</v>
@@ -40969,7 +40969,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1400" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1400" t="n">
         <v>5707</v>
@@ -40998,7 +40998,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1401" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1401" t="n">
         <v>0</v>
@@ -41027,7 +41027,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1402" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1402" t="n">
         <v>0</v>
@@ -41056,7 +41056,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1403" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1403" t="n">
         <v>320</v>
@@ -41085,7 +41085,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1404" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1404" t="n">
         <v>348</v>
@@ -41114,7 +41114,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1405" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1405" t="n">
         <v>0</v>
@@ -41143,7 +41143,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1406" t="n">
-        <v>20.3707942962646</v>
+        <v>20.370792388916</v>
       </c>
       <c r="H1406" t="n">
         <v>0</v>
@@ -41172,7 +41172,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1407" t="n">
-        <v>19.8484649658203</v>
+        <v>19.8484630584717</v>
       </c>
       <c r="H1407" t="n">
         <v>354</v>
@@ -41201,7 +41201,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1408" t="n">
-        <v>19.9355201721191</v>
+        <v>19.9355182647705</v>
       </c>
       <c r="H1408" t="n">
         <v>144</v>
@@ -41230,7 +41230,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1409" t="n">
-        <v>19.9355201721191</v>
+        <v>19.9355182647705</v>
       </c>
       <c r="H1409" t="n">
         <v>87</v>
@@ -41317,7 +41317,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G1412" t="n">
-        <v>19.3261394500732</v>
+        <v>19.3261375427246</v>
       </c>
       <c r="H1412" t="n">
         <v>1566</v>
@@ -41346,7 +41346,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1413" t="n">
-        <v>19.5002460479736</v>
+        <v>19.500244140625</v>
       </c>
       <c r="H1413" t="n">
         <v>22690</v>
@@ -41375,7 +41375,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1414" t="n">
-        <v>19.5002460479736</v>
+        <v>19.500244140625</v>
       </c>
       <c r="H1414" t="n">
         <v>613</v>
@@ -41404,7 +41404,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1415" t="n">
-        <v>19.9355201721191</v>
+        <v>19.9355182647705</v>
       </c>
       <c r="H1415" t="n">
         <v>226</v>
@@ -41433,7 +41433,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>19.9355201721191</v>
+        <v>19.9355182647705</v>
       </c>
       <c r="H1416" t="n">
         <v>250</v>
@@ -41462,7 +41462,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1417" t="n">
-        <v>19.7614097595215</v>
+        <v>19.7614078521729</v>
       </c>
       <c r="H1417" t="n">
         <v>450</v>
@@ -41578,7 +41578,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1421" t="n">
-        <v>20.2837371826172</v>
+        <v>20.2837352752686</v>
       </c>
       <c r="H1421" t="n">
         <v>83</v>
@@ -41607,7 +41607,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1422" t="n">
-        <v>20.2837371826172</v>
+        <v>20.2837352752686</v>
       </c>
       <c r="H1422" t="n">
         <v>52</v>
@@ -41636,7 +41636,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1423" t="n">
-        <v>20.2837371826172</v>
+        <v>20.2837352752686</v>
       </c>
       <c r="H1423" t="n">
         <v>0</v>
@@ -41694,7 +41694,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1425" t="n">
-        <v>20.2837371826172</v>
+        <v>20.2837352752686</v>
       </c>
       <c r="H1425" t="n">
         <v>135</v>
@@ -41723,7 +41723,7 @@
         <v>23.2999992370605</v>
       </c>
       <c r="G1426" t="n">
-        <v>20.2837371826172</v>
+        <v>20.2837352752686</v>
       </c>
       <c r="H1426" t="n">
         <v>1201</v>
@@ -42042,7 +42042,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1437" t="n">
-        <v>21.4154472351074</v>
+        <v>21.4154491424561</v>
       </c>
       <c r="H1437" t="n">
         <v>633</v>
@@ -42245,7 +42245,7 @@
         <v>25</v>
       </c>
       <c r="G1444" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1444" t="n">
         <v>393</v>
@@ -42274,7 +42274,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>21.1542816162109</v>
+        <v>21.1542835235596</v>
       </c>
       <c r="H1445" t="n">
         <v>114</v>
@@ -42361,7 +42361,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1448" t="n">
-        <v>21.2413368225098</v>
+        <v>21.2413387298584</v>
       </c>
       <c r="H1448" t="n">
         <v>1199</v>
@@ -42390,7 +42390,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1449" t="n">
-        <v>21.2413368225098</v>
+        <v>21.2413387298584</v>
       </c>
       <c r="H1449" t="n">
         <v>68</v>
@@ -42419,7 +42419,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1450" t="n">
-        <v>21.2413368225098</v>
+        <v>21.2413387298584</v>
       </c>
       <c r="H1450" t="n">
         <v>0</v>
@@ -42448,7 +42448,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1451" t="n">
-        <v>21.2413368225098</v>
+        <v>21.2413387298584</v>
       </c>
       <c r="H1451" t="n">
         <v>837</v>
@@ -42622,7 +42622,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>21.1542816162109</v>
+        <v>21.1542835235596</v>
       </c>
       <c r="H1457" t="n">
         <v>176</v>
@@ -42651,7 +42651,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1458" t="n">
-        <v>21.1542816162109</v>
+        <v>21.1542835235596</v>
       </c>
       <c r="H1458" t="n">
         <v>1226</v>
@@ -42738,7 +42738,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1461" t="n">
-        <v>21.1542816162109</v>
+        <v>21.1542835235596</v>
       </c>
       <c r="H1461" t="n">
         <v>559</v>
@@ -42825,7 +42825,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1464" t="n">
-        <v>21.2413368225098</v>
+        <v>21.2413387298584</v>
       </c>
       <c r="H1464" t="n">
         <v>961</v>
@@ -42854,7 +42854,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1465" t="n">
-        <v>21.2413368225098</v>
+        <v>21.2413387298584</v>
       </c>
       <c r="H1465" t="n">
         <v>2323</v>
@@ -42883,7 +42883,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>21.4154472351074</v>
+        <v>21.4154491424561</v>
       </c>
       <c r="H1466" t="n">
         <v>842</v>
@@ -42912,7 +42912,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1467" t="n">
-        <v>21.5025024414062</v>
+        <v>21.5025043487549</v>
       </c>
       <c r="H1467" t="n">
         <v>26</v>
@@ -43028,7 +43028,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1471" t="n">
-        <v>21.5025024414062</v>
+        <v>21.5025043487549</v>
       </c>
       <c r="H1471" t="n">
         <v>326</v>
@@ -43057,7 +43057,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1472" t="n">
-        <v>21.5025024414062</v>
+        <v>21.5025043487549</v>
       </c>
       <c r="H1472" t="n">
         <v>165</v>
@@ -43086,7 +43086,7 @@
         <v>25</v>
       </c>
       <c r="G1473" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1473" t="n">
         <v>620</v>
@@ -43115,7 +43115,7 @@
         <v>25</v>
       </c>
       <c r="G1474" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1474" t="n">
         <v>1366</v>
@@ -43144,7 +43144,7 @@
         <v>25</v>
       </c>
       <c r="G1475" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1475" t="n">
         <v>130</v>
@@ -43173,7 +43173,7 @@
         <v>25</v>
       </c>
       <c r="G1476" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1476" t="n">
         <v>0</v>
@@ -43202,7 +43202,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G1477" t="n">
-        <v>21.5025024414062</v>
+        <v>21.5025043487549</v>
       </c>
       <c r="H1477" t="n">
         <v>140</v>
@@ -43376,7 +43376,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1483" t="n">
-        <v>21.4154472351074</v>
+        <v>21.4154491424561</v>
       </c>
       <c r="H1483" t="n">
         <v>1200</v>
@@ -43405,7 +43405,7 @@
         <v>25</v>
       </c>
       <c r="G1484" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1484" t="n">
         <v>1038</v>
@@ -43434,7 +43434,7 @@
         <v>25</v>
       </c>
       <c r="G1485" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1485" t="n">
         <v>1154</v>
@@ -43463,7 +43463,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1486" t="n">
-        <v>21.4154472351074</v>
+        <v>21.4154491424561</v>
       </c>
       <c r="H1486" t="n">
         <v>55</v>
@@ -43521,7 +43521,7 @@
         <v>25</v>
       </c>
       <c r="G1488" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1488" t="n">
         <v>273</v>
@@ -43550,7 +43550,7 @@
         <v>25</v>
       </c>
       <c r="G1489" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1489" t="n">
         <v>58</v>
@@ -43579,7 +43579,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1490" t="n">
-        <v>21.4154472351074</v>
+        <v>21.4154491424561</v>
       </c>
       <c r="H1490" t="n">
         <v>578</v>
@@ -43608,7 +43608,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1491" t="n">
-        <v>21.4154472351074</v>
+        <v>21.4154491424561</v>
       </c>
       <c r="H1491" t="n">
         <v>0</v>
@@ -43811,7 +43811,7 @@
         <v>25</v>
       </c>
       <c r="G1498" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1498" t="n">
         <v>100</v>
@@ -43840,7 +43840,7 @@
         <v>25</v>
       </c>
       <c r="G1499" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1499" t="n">
         <v>0</v>
@@ -43869,7 +43869,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1500" t="n">
-        <v>21.4154472351074</v>
+        <v>21.4154491424561</v>
       </c>
       <c r="H1500" t="n">
         <v>380</v>
@@ -43898,7 +43898,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1501" t="n">
-        <v>21.4154472351074</v>
+        <v>21.4154491424561</v>
       </c>
       <c r="H1501" t="n">
         <v>0</v>
@@ -43985,7 +43985,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1504" t="n">
-        <v>21.4154472351074</v>
+        <v>21.4154491424561</v>
       </c>
       <c r="H1504" t="n">
         <v>1070</v>
@@ -44014,7 +44014,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1505" t="n">
-        <v>21.4154472351074</v>
+        <v>21.4154491424561</v>
       </c>
       <c r="H1505" t="n">
         <v>374</v>
@@ -44130,7 +44130,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1509" t="n">
-        <v>21.2413368225098</v>
+        <v>21.2413387298584</v>
       </c>
       <c r="H1509" t="n">
         <v>400</v>
@@ -44188,7 +44188,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1511" t="n">
-        <v>21.1542816162109</v>
+        <v>21.1542835235596</v>
       </c>
       <c r="H1511" t="n">
         <v>320</v>
@@ -44652,7 +44652,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1527" t="n">
-        <v>21.2413368225098</v>
+        <v>21.2413387298584</v>
       </c>
       <c r="H1527" t="n">
         <v>93</v>
@@ -44681,7 +44681,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1528" t="n">
-        <v>21.4154472351074</v>
+        <v>21.4154491424561</v>
       </c>
       <c r="H1528" t="n">
         <v>1426</v>
@@ -44768,7 +44768,7 @@
         <v>25</v>
       </c>
       <c r="G1531" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1531" t="n">
         <v>466</v>
@@ -44797,7 +44797,7 @@
         <v>25</v>
       </c>
       <c r="G1532" t="n">
-        <v>21.7636642456055</v>
+        <v>21.7636661529541</v>
       </c>
       <c r="H1532" t="n">
         <v>0</v>
@@ -44826,7 +44826,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1533" t="n">
-        <v>21.9377746582031</v>
+        <v>21.9377765655518</v>
       </c>
       <c r="H1533" t="n">
         <v>160</v>
@@ -44855,7 +44855,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1534" t="n">
-        <v>21.9377746582031</v>
+        <v>21.9377765655518</v>
       </c>
       <c r="H1534" t="n">
         <v>80</v>
@@ -44884,7 +44884,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1535" t="n">
-        <v>21.9377746582031</v>
+        <v>21.9377765655518</v>
       </c>
       <c r="H1535" t="n">
         <v>3220</v>
@@ -44971,7 +44971,7 @@
         <v>23.5</v>
       </c>
       <c r="G1538" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1538" t="n">
         <v>466</v>
@@ -45319,7 +45319,7 @@
         <v>23</v>
       </c>
       <c r="G1550" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1550" t="n">
         <v>647</v>
@@ -45348,7 +45348,7 @@
         <v>23</v>
       </c>
       <c r="G1551" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1551" t="n">
         <v>1110</v>
@@ -45377,7 +45377,7 @@
         <v>23</v>
       </c>
       <c r="G1552" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1552" t="n">
         <v>61</v>
@@ -45406,7 +45406,7 @@
         <v>23</v>
       </c>
       <c r="G1553" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1553" t="n">
         <v>195</v>
@@ -45435,7 +45435,7 @@
         <v>23</v>
       </c>
       <c r="G1554" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1554" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>23</v>
       </c>
       <c r="G1555" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1555" t="n">
         <v>140</v>
@@ -45493,7 +45493,7 @@
         <v>23</v>
       </c>
       <c r="G1556" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1556" t="n">
         <v>0</v>
@@ -45522,7 +45522,7 @@
         <v>23</v>
       </c>
       <c r="G1557" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1557" t="n">
         <v>296</v>
@@ -45551,7 +45551,7 @@
         <v>23</v>
       </c>
       <c r="G1558" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1558" t="n">
         <v>650</v>
@@ -45638,7 +45638,7 @@
         <v>23</v>
       </c>
       <c r="G1561" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1561" t="n">
         <v>990</v>
@@ -45667,7 +45667,7 @@
         <v>23</v>
       </c>
       <c r="G1562" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1562" t="n">
         <v>149</v>
@@ -45696,7 +45696,7 @@
         <v>23</v>
       </c>
       <c r="G1563" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1563" t="n">
         <v>0</v>
@@ -45725,7 +45725,7 @@
         <v>23</v>
       </c>
       <c r="G1564" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1564" t="n">
         <v>0</v>
@@ -45841,7 +45841,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1568" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1568" t="n">
         <v>1134</v>
@@ -45870,7 +45870,7 @@
         <v>23.5</v>
       </c>
       <c r="G1569" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1569" t="n">
         <v>401</v>
@@ -46044,7 +46044,7 @@
         <v>23</v>
       </c>
       <c r="G1575" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1575" t="n">
         <v>2883</v>
@@ -46073,7 +46073,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1576" t="n">
-        <v>20.6084499359131</v>
+        <v>20.6084480285645</v>
       </c>
       <c r="H1576" t="n">
         <v>332</v>
@@ -46102,7 +46102,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1577" t="n">
-        <v>20.8784294128418</v>
+        <v>20.8784275054932</v>
       </c>
       <c r="H1577" t="n">
         <v>345</v>
@@ -46131,7 +46131,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1578" t="n">
-        <v>20.8784294128418</v>
+        <v>20.8784275054932</v>
       </c>
       <c r="H1578" t="n">
         <v>1771</v>
@@ -46160,7 +46160,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1579" t="n">
-        <v>20.8784294128418</v>
+        <v>20.8784275054932</v>
       </c>
       <c r="H1579" t="n">
         <v>0</v>
@@ -46218,7 +46218,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1581" t="n">
-        <v>20.8784294128418</v>
+        <v>20.8784275054932</v>
       </c>
       <c r="H1581" t="n">
         <v>33</v>
@@ -46247,7 +46247,7 @@
         <v>23.5</v>
       </c>
       <c r="G1582" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1582" t="n">
         <v>52</v>
@@ -46276,7 +46276,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1583" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1583" t="n">
         <v>325</v>
@@ -46392,7 +46392,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1587" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1587" t="n">
         <v>77</v>
@@ -46450,7 +46450,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1589" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1589" t="n">
         <v>150</v>
@@ -46479,7 +46479,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1590" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1590" t="n">
         <v>0</v>
@@ -46595,7 +46595,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1594" t="n">
-        <v>20.6084499359131</v>
+        <v>20.6084480285645</v>
       </c>
       <c r="H1594" t="n">
         <v>495</v>
@@ -46624,7 +46624,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1595" t="n">
-        <v>20.6084499359131</v>
+        <v>20.6084480285645</v>
       </c>
       <c r="H1595" t="n">
         <v>0</v>
@@ -46682,7 +46682,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1597" t="n">
-        <v>20.6084499359131</v>
+        <v>20.6084480285645</v>
       </c>
       <c r="H1597" t="n">
         <v>593</v>
@@ -46740,7 +46740,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1599" t="n">
-        <v>20.6084499359131</v>
+        <v>20.6084480285645</v>
       </c>
       <c r="H1599" t="n">
         <v>1626</v>
@@ -46769,7 +46769,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1600" t="n">
-        <v>20.6084499359131</v>
+        <v>20.6084480285645</v>
       </c>
       <c r="H1600" t="n">
         <v>75676</v>
@@ -46798,7 +46798,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1601" t="n">
-        <v>20.6084499359131</v>
+        <v>20.6084480285645</v>
       </c>
       <c r="H1601" t="n">
         <v>0</v>
@@ -46827,7 +46827,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1602" t="n">
-        <v>20.6084499359131</v>
+        <v>20.6084480285645</v>
       </c>
       <c r="H1602" t="n">
         <v>0</v>
@@ -46856,7 +46856,7 @@
         <v>23</v>
       </c>
       <c r="G1603" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1603" t="n">
         <v>263</v>
@@ -47088,7 +47088,7 @@
         <v>23</v>
       </c>
       <c r="G1611" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1611" t="n">
         <v>3606</v>
@@ -47117,7 +47117,7 @@
         <v>23</v>
       </c>
       <c r="G1612" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1612" t="n">
         <v>255</v>
@@ -47146,7 +47146,7 @@
         <v>23</v>
       </c>
       <c r="G1613" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1613" t="n">
         <v>310</v>
@@ -47175,7 +47175,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1614" t="n">
-        <v>20.6084499359131</v>
+        <v>20.6084480285645</v>
       </c>
       <c r="H1614" t="n">
         <v>919</v>
@@ -47233,7 +47233,7 @@
         <v>23</v>
       </c>
       <c r="G1616" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1616" t="n">
         <v>796</v>
@@ -47262,7 +47262,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1617" t="n">
-        <v>20.6084499359131</v>
+        <v>20.6084480285645</v>
       </c>
       <c r="H1617" t="n">
         <v>853</v>
@@ -47349,7 +47349,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1620" t="n">
-        <v>20.6084499359131</v>
+        <v>20.6084480285645</v>
       </c>
       <c r="H1620" t="n">
         <v>3045</v>
@@ -47378,7 +47378,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1621" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1621" t="n">
         <v>7825</v>
@@ -47407,7 +47407,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1622" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1622" t="n">
         <v>351</v>
@@ -47436,7 +47436,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1623" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1623" t="n">
         <v>0</v>
@@ -47494,7 +47494,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1625" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1625" t="n">
         <v>2773</v>
@@ -47523,7 +47523,7 @@
         <v>23.5</v>
       </c>
       <c r="G1626" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1626" t="n">
         <v>400</v>
@@ -47552,7 +47552,7 @@
         <v>23.5</v>
       </c>
       <c r="G1627" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1627" t="n">
         <v>0</v>
@@ -47581,7 +47581,7 @@
         <v>23.5</v>
       </c>
       <c r="G1628" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1628" t="n">
         <v>340</v>
@@ -47610,7 +47610,7 @@
         <v>23.5</v>
       </c>
       <c r="G1629" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1629" t="n">
         <v>50</v>
@@ -47929,7 +47929,7 @@
         <v>23.5</v>
       </c>
       <c r="G1640" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1640" t="n">
         <v>1571</v>
@@ -47958,7 +47958,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1641" t="n">
-        <v>20.8784294128418</v>
+        <v>20.8784275054932</v>
       </c>
       <c r="H1641" t="n">
         <v>1058</v>
@@ -47987,7 +47987,7 @@
         <v>23.5</v>
       </c>
       <c r="G1642" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1642" t="n">
         <v>1711</v>
@@ -48016,7 +48016,7 @@
         <v>23.5</v>
       </c>
       <c r="G1643" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1643" t="n">
         <v>1245</v>
@@ -48045,7 +48045,7 @@
         <v>23.5</v>
       </c>
       <c r="G1644" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1644" t="n">
         <v>182</v>
@@ -48074,7 +48074,7 @@
         <v>23.5</v>
       </c>
       <c r="G1645" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1645" t="n">
         <v>66</v>
@@ -48103,7 +48103,7 @@
         <v>23.5</v>
       </c>
       <c r="G1646" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1646" t="n">
         <v>1382</v>
@@ -48132,7 +48132,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1647" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1647" t="n">
         <v>947</v>
@@ -48335,7 +48335,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1654" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1654" t="n">
         <v>1702</v>
@@ -48625,7 +48625,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1664" t="n">
-        <v>21.958345413208</v>
+        <v>21.9583473205566</v>
       </c>
       <c r="H1664" t="n">
         <v>1260</v>
@@ -48654,7 +48654,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1665" t="n">
-        <v>21.958345413208</v>
+        <v>21.9583473205566</v>
       </c>
       <c r="H1665" t="n">
         <v>500</v>
@@ -48828,7 +48828,7 @@
         <v>24</v>
       </c>
       <c r="G1671" t="n">
-        <v>21.5983734130859</v>
+        <v>21.5983753204346</v>
       </c>
       <c r="H1671" t="n">
         <v>162</v>
@@ -48857,7 +48857,7 @@
         <v>24</v>
       </c>
       <c r="G1672" t="n">
-        <v>21.5983734130859</v>
+        <v>21.5983753204346</v>
       </c>
       <c r="H1672" t="n">
         <v>600</v>
@@ -49147,7 +49147,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1682" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1682" t="n">
         <v>1547</v>
@@ -49176,7 +49176,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1683" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1683" t="n">
         <v>1374</v>
@@ -49205,7 +49205,7 @@
         <v>24</v>
       </c>
       <c r="G1684" t="n">
-        <v>21.5983734130859</v>
+        <v>21.5983753204346</v>
       </c>
       <c r="H1684" t="n">
         <v>2208</v>
@@ -49234,7 +49234,7 @@
         <v>24</v>
       </c>
       <c r="G1685" t="n">
-        <v>21.5983734130859</v>
+        <v>21.5983753204346</v>
       </c>
       <c r="H1685" t="n">
         <v>0</v>
@@ -49321,7 +49321,7 @@
         <v>24</v>
       </c>
       <c r="G1688" t="n">
-        <v>21.5983734130859</v>
+        <v>21.5983753204346</v>
       </c>
       <c r="H1688" t="n">
         <v>2536</v>
@@ -49379,7 +49379,7 @@
         <v>23.5</v>
       </c>
       <c r="G1690" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1690" t="n">
         <v>1628</v>
@@ -49408,7 +49408,7 @@
         <v>23.5</v>
       </c>
       <c r="G1691" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1691" t="n">
         <v>1309</v>
@@ -49437,7 +49437,7 @@
         <v>23.5</v>
       </c>
       <c r="G1692" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1692" t="n">
         <v>1060</v>
@@ -49466,7 +49466,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1693" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1693" t="n">
         <v>3192</v>
@@ -49524,7 +49524,7 @@
         <v>23</v>
       </c>
       <c r="G1695" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1695" t="n">
         <v>935</v>
@@ -49669,7 +49669,7 @@
         <v>24</v>
       </c>
       <c r="G1700" t="n">
-        <v>21.5983734130859</v>
+        <v>21.5983753204346</v>
       </c>
       <c r="H1700" t="n">
         <v>534</v>
@@ -49698,7 +49698,7 @@
         <v>24</v>
       </c>
       <c r="G1701" t="n">
-        <v>21.5983734130859</v>
+        <v>21.5983753204346</v>
       </c>
       <c r="H1701" t="n">
         <v>521</v>
@@ -49727,7 +49727,7 @@
         <v>24</v>
       </c>
       <c r="G1702" t="n">
-        <v>21.5983734130859</v>
+        <v>21.5983753204346</v>
       </c>
       <c r="H1702" t="n">
         <v>74</v>
@@ -49756,7 +49756,7 @@
         <v>24</v>
       </c>
       <c r="G1703" t="n">
-        <v>21.5983734130859</v>
+        <v>21.5983753204346</v>
       </c>
       <c r="H1703" t="n">
         <v>50</v>
@@ -49785,7 +49785,7 @@
         <v>24</v>
       </c>
       <c r="G1704" t="n">
-        <v>21.5983734130859</v>
+        <v>21.5983753204346</v>
       </c>
       <c r="H1704" t="n">
         <v>394</v>
@@ -50075,7 +50075,7 @@
         <v>23.5</v>
       </c>
       <c r="G1714" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1714" t="n">
         <v>577</v>
@@ -50133,7 +50133,7 @@
         <v>24</v>
       </c>
       <c r="G1716" t="n">
-        <v>21.5983734130859</v>
+        <v>21.5983753204346</v>
       </c>
       <c r="H1716" t="n">
         <v>403</v>
@@ -50191,7 +50191,7 @@
         <v>24</v>
       </c>
       <c r="G1718" t="n">
-        <v>21.5983734130859</v>
+        <v>21.5983753204346</v>
       </c>
       <c r="H1718" t="n">
         <v>430</v>
@@ -50220,7 +50220,7 @@
         <v>24</v>
       </c>
       <c r="G1719" t="n">
-        <v>21.5983734130859</v>
+        <v>21.5983753204346</v>
       </c>
       <c r="H1719" t="n">
         <v>164</v>
@@ -50249,7 +50249,7 @@
         <v>24</v>
       </c>
       <c r="G1720" t="n">
-        <v>21.5983734130859</v>
+        <v>21.5983753204346</v>
       </c>
       <c r="H1720" t="n">
         <v>160</v>
@@ -50423,7 +50423,7 @@
         <v>23.5</v>
       </c>
       <c r="G1726" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1726" t="n">
         <v>771</v>
@@ -50452,7 +50452,7 @@
         <v>23</v>
       </c>
       <c r="G1727" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1727" t="n">
         <v>2576</v>
@@ -50481,7 +50481,7 @@
         <v>23</v>
       </c>
       <c r="G1728" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1728" t="n">
         <v>1170</v>
@@ -50539,7 +50539,7 @@
         <v>23.5</v>
       </c>
       <c r="G1730" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1730" t="n">
         <v>380</v>
@@ -50568,7 +50568,7 @@
         <v>23.5</v>
       </c>
       <c r="G1731" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1731" t="n">
         <v>1534</v>
@@ -50597,7 +50597,7 @@
         <v>23.5</v>
       </c>
       <c r="G1732" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1732" t="n">
         <v>115</v>
@@ -50858,7 +50858,7 @@
         <v>23.5</v>
       </c>
       <c r="G1741" t="n">
-        <v>21.1484069824219</v>
+        <v>21.1484088897705</v>
       </c>
       <c r="H1741" t="n">
         <v>2603</v>
@@ -51061,7 +51061,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1748" t="n">
-        <v>20.8784294128418</v>
+        <v>20.8784275054932</v>
       </c>
       <c r="H1748" t="n">
         <v>842</v>
@@ -51090,7 +51090,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1749" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1749" t="n">
         <v>355</v>
@@ -51119,7 +51119,7 @@
         <v>23</v>
       </c>
       <c r="G1750" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1750" t="n">
         <v>751</v>
@@ -51148,7 +51148,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G1751" t="n">
-        <v>20.8784294128418</v>
+        <v>20.8784275054932</v>
       </c>
       <c r="H1751" t="n">
         <v>50</v>
@@ -51177,7 +51177,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1752" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1752" t="n">
         <v>150</v>
@@ -51235,7 +51235,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1754" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1754" t="n">
         <v>3008</v>
@@ -51293,7 +51293,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1756" t="n">
-        <v>21.0584163665771</v>
+        <v>21.0584144592285</v>
       </c>
       <c r="H1756" t="n">
         <v>3572</v>
@@ -51409,7 +51409,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1760" t="n">
-        <v>20.158483505249</v>
+        <v>20.1584815979004</v>
       </c>
       <c r="H1760" t="n">
         <v>820</v>
@@ -51438,7 +51438,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1761" t="n">
-        <v>20.158483505249</v>
+        <v>20.1584815979004</v>
       </c>
       <c r="H1761" t="n">
         <v>54</v>
@@ -51467,7 +51467,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1762" t="n">
-        <v>20.158483505249</v>
+        <v>20.1584815979004</v>
       </c>
       <c r="H1762" t="n">
         <v>4400</v>
@@ -51496,7 +51496,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1763" t="n">
-        <v>20.158483505249</v>
+        <v>20.1584815979004</v>
       </c>
       <c r="H1763" t="n">
         <v>1230</v>
@@ -51525,7 +51525,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1764" t="n">
-        <v>20.158483505249</v>
+        <v>20.1584815979004</v>
       </c>
       <c r="H1764" t="n">
         <v>300</v>
@@ -51583,7 +51583,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1766" t="n">
-        <v>20.158483505249</v>
+        <v>20.1584815979004</v>
       </c>
       <c r="H1766" t="n">
         <v>510</v>
@@ -51612,7 +51612,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1767" t="n">
-        <v>20.158483505249</v>
+        <v>20.1584815979004</v>
       </c>
       <c r="H1767" t="n">
         <v>0</v>
@@ -51815,7 +51815,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1774" t="n">
-        <v>20.158483505249</v>
+        <v>20.1584815979004</v>
       </c>
       <c r="H1774" t="n">
         <v>24</v>
@@ -51844,7 +51844,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1775" t="n">
-        <v>20.158483505249</v>
+        <v>20.1584815979004</v>
       </c>
       <c r="H1775" t="n">
         <v>0</v>
@@ -51960,7 +51960,7 @@
         <v>22</v>
       </c>
       <c r="G1779" t="n">
-        <v>19.7985095977783</v>
+        <v>19.7985076904297</v>
       </c>
       <c r="H1779" t="n">
         <v>403</v>
@@ -52134,7 +52134,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1785" t="n">
-        <v>20.158483505249</v>
+        <v>20.1584815979004</v>
       </c>
       <c r="H1785" t="n">
         <v>141</v>
@@ -52163,7 +52163,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1786" t="n">
-        <v>20.158483505249</v>
+        <v>20.1584815979004</v>
       </c>
       <c r="H1786" t="n">
         <v>11411</v>
@@ -52192,7 +52192,7 @@
         <v>23</v>
       </c>
       <c r="G1787" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1787" t="n">
         <v>7214</v>
@@ -52221,7 +52221,7 @@
         <v>23</v>
       </c>
       <c r="G1788" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1788" t="n">
         <v>252</v>
@@ -52250,7 +52250,7 @@
         <v>23</v>
       </c>
       <c r="G1789" t="n">
-        <v>20.6984424591064</v>
+        <v>20.6984405517578</v>
       </c>
       <c r="H1789" t="n">
         <v>64</v>
@@ -69847,7 +69847,7 @@
         <v>17.5</v>
       </c>
       <c r="E2396" t="n">
-        <v>17.5</v>
+        <v>17.3500003814697</v>
       </c>
       <c r="F2396" t="n">
         <v>17.3500003814697</v>
@@ -69859,6 +69859,35 @@
         <v>69</v>
       </c>
       <c r="I2396" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2397" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2397" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D2397" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="E2397" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F2397" t="n">
+        <v>17.3500003814697</v>
+      </c>
+      <c r="G2397" t="n">
+        <v>17.3500003814697</v>
+      </c>
+      <c r="H2397" t="n">
+        <v>16</v>
+      </c>
+      <c r="I2397" t="s">
         <v>9</v>
       </c>
     </row>
